--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_1.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_1.xlsx
@@ -618,1395 +618,1395 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01119</t>
+          <t>X ≈ -0.01118</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>9</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.86904687741103</v>
+        <v>1.902114124438292</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.537122861696083</v>
+        <v>1.57059173514574</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.9352321724548</v>
+        <v>-10.90335489497062</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.6027841494197901</v>
+        <v>-0.5669320738858019</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.9665033063677626</v>
+        <v>-0.9014206666333351</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.27091136433276</v>
+        <v>10.33922616475456</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.60483584007734</v>
+        <v>-12.53886339323879</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.230386663946831</v>
+        <v>9.296849854902362</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.274316169041583</v>
+        <v>9.340768094102174</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.506657540827327</v>
+        <v>8.57403789918736</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.782679215070061</v>
+        <v>8.849779397136636</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.506975549737405</v>
+        <v>8.574435597647877</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.388669998308011</v>
+        <v>7.457467937909179</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.169642123108325</v>
+        <v>7.238735932454446</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6.514691599279267</v>
+        <v>6.584587378873699</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>18.19492539847061</v>
+        <v>18.26420180230923</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>18.06645208196331</v>
+        <v>18.13591915708564</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>17.96736663465208</v>
+        <v>18.03698989976712</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>18.18861533151729</v>
+        <v>18.25802215729519</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>18.38081256204178</v>
+        <v>18.45003670394826</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.742396268282043</v>
+        <v>6.812276224699325</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.668491853976455</v>
+        <v>6.738499702414906</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>6.945192202925845</v>
+        <v>7.014918719801059</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376949577</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01039</t>
+          <t>X ≈ -0.01038</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>14</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.650109479649586</v>
+        <v>-3.617087062328984</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.21247614063549</v>
+        <v>10.24600899461139</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.782098496230304</v>
+        <v>8.819982072337048</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.9750659268548318</v>
+        <v>1.011397798974571</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.714137951842943</v>
+        <v>7.781866899689604</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.7979586260814955</v>
+        <v>0.8634035980876718</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>14.24259545518799</v>
+        <v>14.30872828777255</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>21.0778856058909</v>
+        <v>21.14441534238247</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>21.12537568773264</v>
+        <v>21.19189004403007</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13.24837072621299</v>
+        <v>13.31577353352301</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.52582309441665</v>
+        <v>13.59294415503056</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.25156287801084</v>
+        <v>13.31904218976655</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>19.25404661351373</v>
+        <v>19.32289028772148</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>19.03858942200336</v>
+        <v>19.10772482935528</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>18.38722310666285</v>
+        <v>18.45715630211266</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>18.986371232722</v>
+        <v>19.05564947515991</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>18.85817399252605</v>
+        <v>18.9276426732918</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>25.88936927306408</v>
+        <v>25.95900930775842</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>26.11303017811988</v>
+        <v>26.1824509927914</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>26.30764125733874</v>
+        <v>26.37687660352555</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>18.63639446981467</v>
+        <v>18.70628694542616</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>18.56607599033025</v>
+        <v>18.63609218912794</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>18.84636356166309</v>
+        <v>18.91609425827262</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>18.77610693400167</v>
+        <v>18.84596128170732</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.009585</t>
+          <t>X ≈ -0.009578</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>19</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-27.17765683420353</v>
+        <v>-27.14482481105204</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-17.05869872904967</v>
+        <v>-17.02537414193409</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.799083558411198</v>
+        <v>-2.764737195973481</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.953916747339605</v>
+        <v>6.992087802237329</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.35921596145959</v>
+        <v>1.425014168239258</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.688951994967638</v>
+        <v>-3.624884007565697</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.7772191149362371</v>
+        <v>0.8432671465619137</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.738145333813442</v>
+        <v>-4.671766410400302</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.69836249877843</v>
+        <v>-4.631989603468519</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.469980689892772</v>
+        <v>-5.402674646340827</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.44069381016717</v>
+        <v>-10.37368739558718</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-15.96626281277049</v>
+        <v>-15.89891229960379</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-17.09192854221324</v>
+        <v>-17.02323105455405</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.57637725727708</v>
+        <v>-1.507317567013189</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-17.98052649763954</v>
+        <v>-17.91071312338433</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-12.14183763278682</v>
+        <v>-12.07265062118315</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-17.53141095849153</v>
+        <v>-17.4620355448284</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-7.133924671023614</v>
+        <v>-7.0643569566206</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-6.920153490907289</v>
+        <v>-6.850792970869378</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.73543781262866</v>
+        <v>-6.666250721771341</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.53851718222869</v>
+        <v>-12.46865903721814</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.35821634155154</v>
+        <v>-7.288219208582078</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-7.085705925195256</v>
+        <v>-7.015984764248827</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-7.163742690058484</v>
+        <v>-7.093888342350006</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.008783</t>
+          <t>X ≈ -0.008776</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.570362804336469</v>
+        <v>-6.537371938989764</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.784571431721709</v>
+        <v>4.818058838483317</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.491249238436765</v>
+        <v>-2.456818860041103</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.645277437960196</v>
+        <v>2.682139183893362</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.13119495492262</v>
+        <v>8.199085241186708</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>20.02064066764419</v>
+        <v>20.09200615610169</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>19.25759614130754</v>
+        <v>19.32375570711822</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.278003437747444</v>
+        <v>7.344448723089485</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.321400954514957</v>
+        <v>7.387836113420136</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.553442649479926</v>
+        <v>6.620806698492956</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.829020086254033</v>
+        <v>6.896104913446983</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>18.27487900397324</v>
+        <v>18.34237619074082</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>23.0223300598046</v>
+        <v>23.09118563108694</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>16.94326252180316</v>
+        <v>17.0123878457546</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>16.29163076486041</v>
+        <v>16.36155414714258</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>16.89009336333211</v>
+        <v>16.95936316353611</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>16.76139428374246</v>
+        <v>16.83085540571982</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>10.79020163999486</v>
+        <v>10.85980718617883</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>11.00938363446664</v>
+        <v>11.07877570931402</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>17.07472783436302</v>
+        <v>17.14394884769212</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>16.53727638487288</v>
+        <v>16.60716565122627</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>10.58758501236876</v>
+        <v>10.65759478057249</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>16.74608697221699</v>
+        <v>16.81581662510426</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>16.67526659786721</v>
+        <v>16.74512094557316</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.00798</t>
+          <t>X ≈ -0.007974</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>17</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.569899415665105</v>
+        <v>-6.536912031101735</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.060608895460014</v>
+        <v>-1.027168458670872</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.491078292755105</v>
+        <v>-2.4566575931606</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.201530320990081</v>
+        <v>-3.16647763373463</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-15.26297895052312</v>
+        <v>-15.20232546699345</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.46891719215413</v>
+        <v>2.534902591180305</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.151333795676216</v>
+        <v>-4.085322843883851</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.277636036619924</v>
+        <v>7.344078775905103</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.321052885289831</v>
+        <v>7.387485667491418</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>18.26778331185339</v>
+        <v>18.33520583369987</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>18.54693610095086</v>
+        <v>18.614075285166</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.552436875231891</v>
+        <v>6.619880897636477</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.433551264249623</v>
+        <v>5.502334484431294</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.213830739592858</v>
+        <v>5.282911585104486</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>10.42493486357846</v>
+        <v>10.49483772353936</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>11.02164570778742</v>
+        <v>11.09089731334127</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.8483991351997986</v>
+        <v>-0.7789844965737913</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.9531958706274892</v>
+        <v>-0.8836173740464375</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>5.135823466867087</v>
+        <v>5.205203917782363</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>5.324157227980379</v>
+        <v>5.393360383374329</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.66015018860815</v>
+        <v>10.73003259418693</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>10.58751762641099</v>
+        <v>10.65752710425721</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>16.74603382422892</v>
+        <v>16.81576338013329</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>10.79291365669075</v>
+        <v>10.86276800439803</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.007178</t>
+          <t>X ≈ -0.007172</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.266018426107863</v>
+        <v>6.499044269785337</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.57666195756094</v>
+        <v>14.93039192626598</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>14.15713463123529</v>
+        <v>16.38650846041653</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>13.45183750097029</v>
+        <v>15.66229928565954</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>13.092706010444</v>
+        <v>12.39772131009262</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>13.28210970354444</v>
+        <v>14.23808993176586</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>9.502885843005423</v>
+        <v>7.618397263619123</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>12.24366080208773</v>
+        <v>10.27025795891392</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>12.28863155433194</v>
+        <v>10.31459248374637</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>11.52208928612595</v>
+        <v>9.548354057296905</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>2.744641985929341</v>
+        <v>1.036279833906462</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>5.486492369525841</v>
+        <v>6.619500365843706</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>7.387421317448663</v>
+        <v>8.433281859541388</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>1.126357261391156</v>
+        <v>2.350504154712574</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-2.551967717029093</v>
+        <v>-4.170830141524227</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-8.004912014769779</v>
+        <v>-9.447139336206043</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-5.117237536799372</v>
+        <v>-6.648658292392177</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-2.198640516110828</v>
+        <v>-3.819345130985248</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-1.983445175619082</v>
+        <v>-3.604878176513083</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-1.797284788004262</v>
+        <v>-3.419412766216468</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-5.367951328185548</v>
+        <v>-3.962422799847069</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>0.6113960330623414</v>
+        <v>1.839328933126573</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-2.143050265769368</v>
+        <v>-3.766210806608512</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-5.249867091972362</v>
+        <v>-3.843114348543821</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.006376</t>
+          <t>X ≈ -0.00637</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>43</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.739114534095641</v>
+        <v>-6.016172676644025</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-13.32140862885598</v>
+        <v>-13.29084885496825</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-17.09658145208896</v>
+        <v>-17.07110473217384</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-10.89203562153089</v>
+        <v>-10.86179554526786</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-4.329189086432486</v>
+        <v>-6.579349811022269</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-8.764221174967766</v>
+        <v>-11.01429408419392</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.329483977130188</v>
+        <v>4.396848920878973</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.895024674338046</v>
+        <v>-2.827329154293942</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-7.483829463767769</v>
+        <v>-5.100707395206236</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-11.5634155261826</v>
+        <v>-10.52307134448424</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-11.29300962936744</v>
+        <v>-10.25017713698954</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-6.940950134151436</v>
+        <v>-8.218471161471449</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-5.746314971395087</v>
+        <v>-7.047126731040244</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.287591405808016</v>
+        <v>-8.218601862916884</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-8.94679090063174</v>
+        <v>-6.557839582040621</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-6.036162832104687</v>
+        <v>-3.647134349431788</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-8.492266949799536</v>
+        <v>-6.102325667743429</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-3.9570570033748</v>
+        <v>-1.56622267185675</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-8.386336912082889</v>
+        <v>-5.994998565592077</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-10.52487365667423</v>
+        <v>-8.132991682764931</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-11.07073463489457</v>
+        <v>-11.00088812028978</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-8.82598576299123</v>
+        <v>-8.755998780906872</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-17.8534181005096</v>
+        <v>-15.45883981010128</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-13.28369373045016</v>
+        <v>-13.21383938274236</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.005574</t>
+          <t>X ≈ -0.005568</t>
         </is>
       </c>
       <c r="B13" t="n">
         <v>42</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>12.73555897786383</v>
+        <v>15.13716562708782</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>19.49109241816944</v>
+        <v>19.53366902780714</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>15.62178722037824</v>
+        <v>15.66897013042068</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.6781170611264784</v>
+        <v>0.7167402866493759</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3017561531923221</v>
+        <v>0.3683665744273341</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>5.239587066614099</v>
+        <v>7.678709508509172</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.070453295681155</v>
+        <v>4.50958690290242</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4.152250136987519</v>
+        <v>6.592510420999666</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.5481501133147617</v>
+        <v>-0.477759287450823</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.731962990521161</v>
+        <v>-3.662545578387316</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-5.826759591076694</v>
+        <v>-8.131783684915682</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.86228952977688</v>
+        <v>-10.79506909918678</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-12.03690717171309</v>
+        <v>-11.96865200140309</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.515800612196408</v>
+        <v>-7.442651473235912</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.086118375387663</v>
+        <v>-1.012102387216046</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.83878076115672</v>
+        <v>-2.765437773068435</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.981748457835124</v>
+        <v>-2.908191006486298</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.092838109142157</v>
+        <v>-3.019102398377349</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-8.588095144752259</v>
+        <v>-9.933811129108207</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-4.607328096922934</v>
+        <v>-9.739251600411372</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-7.530079983209369</v>
+        <v>-12.69396205080557</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-7.608450577981905</v>
+        <v>-12.77174068649727</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-4.955915816418148</v>
+        <v>-8.687739194799782</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-5.033416875522136</v>
+        <v>-7.344514908766698</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004771</t>
+          <t>X ≈ -0.004766</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>66</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.7546285087173601</v>
+        <v>-0.7181820528568679</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>9.45882307281336</v>
+        <v>7.989430376847459</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.4437990864463401</v>
+        <v>-0.1917283748033469</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>1.217586300291195</v>
+        <v>0.5950674185745157</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.862390076475982</v>
+        <v>4.782589146003424</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>5.568150153717873</v>
+        <v>4.973677834660911</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>3.269932289211908</v>
+        <v>2.68570280222751</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>9.025255273026403</v>
+        <v>8.442946556435132</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>8.418946464235532</v>
+        <v>6.976887714451834</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>7.63453992928131</v>
+        <v>6.19520161836472</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.381481493729154</v>
+        <v>3.450300656567137</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.100503305801084</v>
+        <v>1.658753370488874</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.96367950916175</v>
+        <v>1.417698377210023</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.280761041125274</v>
+        <v>-1.825868434683649</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.58717238274437</v>
+        <v>2.052254408196497</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-4.372140452530239</v>
+        <v>-4.91494458780911</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-2.996869123486505</v>
+        <v>-3.537416790356289</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-1.590731421711943</v>
+        <v>-2.130032368358798</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-2.88739427991176</v>
+        <v>-3.428533363634244</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-1.182634401191699</v>
+        <v>-0.2146339455359367</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-3.249837043238287</v>
+        <v>-2.27171884617411</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.2969000682089273</v>
+        <v>0.6819508570822066</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>5.43038889380977</v>
+        <v>5.501880115018807</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.356193514088254</v>
+        <v>5.426047861795176</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.003969</t>
+          <t>X ≈ -0.003965</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>8.281807625415503</v>
+        <v>7.704409403160227</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.9838785357795174</v>
+        <v>1.461130641025072</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5.521500378008199</v>
+        <v>4.957581364780957</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.793526545495489</v>
+        <v>8.191909444129365</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.464752354735793</v>
+        <v>0.9590098619340779</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.629195983782388</v>
+        <v>6.07339147140695</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>6.857530643733092</v>
+        <v>7.276139292568693</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.58178099922187</v>
+        <v>6.014763989664488</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.634525984916969</v>
+        <v>3.099291652121266</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.867780410237785</v>
+        <v>1.343892744692354</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>1.146221270418756</v>
+        <v>0.6313799147811565</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.862210015790922</v>
+        <v>2.328368580367602</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.733539782522875</v>
+        <v>4.170421324640841</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>3.516284391775109</v>
+        <v>2.962054697319793</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.859831167410576</v>
+        <v>2.306413541849928</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>5.451778682687568</v>
+        <v>4.876925757414739</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.319707139644038</v>
+        <v>4.744888640429437</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>2.219589381535769</v>
+        <v>1.675411568821929</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>3.434678155068447</v>
+        <v>2.880964993314898</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.622400100783352</v>
+        <v>2.079072604576091</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>4.079195821824044</v>
+        <v>3.516970068446334</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>7.003502801300463</v>
+        <v>6.41252391438794</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>5.278827514309192</v>
+        <v>4.706800607068004</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>5.204678362573098</v>
+        <v>4.630968353844729</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.003167</t>
+          <t>X ≈ -0.003163</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-2.535961639622386</v>
+        <v>-1.345251484549593</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.090081634295437</v>
+        <v>-3.237898720364832</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.3708233973911632</v>
+        <v>-0.02757112769747039</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-1.134251960938677</v>
+        <v>-0.7482629106030672</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.856796156872697</v>
+        <v>2.80176635016165</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.478771468166229</v>
+        <v>1.438848378693045</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7037029708032847</v>
+        <v>-0.1191735790828403</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.928924203680211</v>
+        <v>-1.956133735651122</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-1.103473677848555</v>
+        <v>-0.6959594619436373</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.4723121749470138</v>
+        <v>0.8627132305721901</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.8231905593298734</v>
+        <v>-0.4212644292568868</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.103535523104547</v>
+        <v>-0.7011951562301064</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>1.693484489604622</v>
+        <v>2.067017624892877</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.09943719513755411</v>
+        <v>0.2867116354031154</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-3.120408112956568</v>
+        <v>-2.713831638505035</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.6224024490247047</v>
+        <v>0.2226693627794631</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.060702663654418</v>
+        <v>2.428394430270885</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>2.42392192351749</v>
+        <v>2.32319607635705</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>3.42655283302571</v>
+        <v>4.101669552941601</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>2.826704436862691</v>
+        <v>3.511032365397348</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.7112626161660458</v>
+        <v>1.402101526391718</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.422588673828265</v>
+        <v>2.575890251021598</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>4.05863906843279</v>
+        <v>4.41286496350348</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>0.8345996224156238</v>
+        <v>1.212032710280376</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002364</t>
+          <t>X ≈ -0.002361</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.450047973802228</v>
+        <v>3.247508237947237</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.1636288569478737</v>
+        <v>0.7159607256656102</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-8.154738512366968</v>
+        <v>-7.312733861948765</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-7.774268747406538</v>
+        <v>-7.475131651518971</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.684997343940502</v>
+        <v>-8.362650766236477</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-6.315185823258709</v>
+        <v>-5.976888818432904</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-10.91756648928738</v>
+        <v>-10.59747516776448</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-9.556879706242761</v>
+        <v>-9.777686686758059</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8.420027632415717</v>
+        <v>-8.634812288547273</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-8.642963732022103</v>
+        <v>-8.856921978025468</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.633225174713843</v>
+        <v>-5.83146300180038</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-4.818240777975127</v>
+        <v>-5.00982644430357</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-5.94221109324009</v>
+        <v>-6.13072418014395</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.165263696607106</v>
+        <v>-6.351350190387492</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-5.72807786403974</v>
+        <v>-5.907499288271673</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-7.330696703025339</v>
+        <v>-6.970898293531135</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-8.016170756551169</v>
+        <v>-8.210579305610999</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-5.376776123071259</v>
+        <v>-5.558807081920314</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-7.356116428106773</v>
+        <v>-8.105377107918031</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-4.974037853141255</v>
+        <v>-5.71249017304828</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-4.420379215856791</v>
+        <v>-5.152131190884091</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-5.047333538993328</v>
+        <v>-5.227977152293313</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-5.871206004050514</v>
+        <v>-6.058474815501746</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-5.399717241822508</v>
+        <v>-5.029334693034535</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001562</t>
+          <t>X ≈ -0.001559</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.575904445471707</v>
+        <v>-2.509630506441404</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.152438291295077</v>
+        <v>-1.891525747798845</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.980404645037396</v>
+        <v>4.188183291848091</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.516008348915001</v>
+        <v>3.104907624375365</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.017936665683401</v>
+        <v>2.020566129282365</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.202737808962496</v>
+        <v>-1.176511635301146</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.678324379990336</v>
+        <v>0.6857947804725626</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.7792133321657815</v>
+        <v>1.160134829137341</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.578360796235813</v>
+        <v>1.953537518609075</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>2.701815448145013</v>
+        <v>3.06484044652467</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.598162255892532</v>
+        <v>2.963744431341993</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.469372979591945</v>
+        <v>-1.076317443614215</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3170811973963765</v>
+        <v>-0.3154506143148268</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.675987444906013</v>
+        <v>-1.664802340844808</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.8163197318374813</v>
+        <v>-0.4396809034894318</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.879917891755092</v>
+        <v>-2.859485614215295</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.39489606196242</v>
+        <v>-3.371202783101538</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.360607971305548</v>
+        <v>-2.346839862736424</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-0.2456528317292594</v>
+        <v>0.1303406080407612</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-2.337705634304591</v>
+        <v>-1.946335591535856</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-0.2219284912845367</v>
+        <v>0.1517362124306061</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.818493269856923</v>
+        <v>-1.433543711242557</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-3.064156189977766</v>
+        <v>-2.291144470458612</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.620416694461213</v>
+        <v>-1.234901251983779</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0007596</t>
+          <t>X ≈ -0.000757</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.688523007795915</v>
+        <v>-1.386145647175184</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.4290839103676021</v>
+        <v>-0.3947084083029395</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.67041273239758</v>
+        <v>-2.628376121268651</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.323871396586966</v>
+        <v>-2.281453987234578</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.488914453298712</v>
+        <v>-3.680798223083116</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.70486589928781</v>
+        <v>-1.900465041515169</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.014837292762053</v>
+        <v>-3.204209371243579</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.809614495600954</v>
+        <v>-2.156011831563205</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.300773972565871</v>
+        <v>-2.645778710727036</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.6788057720020717</v>
+        <v>-1.029816714659532</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-1.737085119222527</v>
+        <v>-2.085656562777274</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.9521111164991325</v>
+        <v>-1.146350459408161</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.812393356571647</v>
+        <v>1.719001069671272</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.008636076422597228</v>
+        <v>-0.3631926936042973</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.6660508374141187</v>
+        <v>0.04223178661394655</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>2.062679063486762</v>
+        <v>1.701297942294239</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>1.127626177625274</v>
+        <v>0.929177327841991</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.312739587031011</v>
+        <v>-0.5070524238888439</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>2.040610877544673</v>
+        <v>1.839442321669353</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.495192800837174</v>
+        <v>2.293378745245477</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.7766061721686981</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>1.502539890751287</v>
+        <v>0.6092235843548721</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>2.578940862544442</v>
+        <v>1.683698296836923</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>2.504143603214871</v>
+        <v>1.607866043613704</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 4.3e-05</t>
+          <t>X ≈ 4.485e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.835481111525205</v>
+        <v>2.903582359445025</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.707291293777892</v>
+        <v>2.9842595569324</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.893980326572098</v>
+        <v>2.171860703886537</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.422022692852096</v>
+        <v>2.615472343856297</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.6154586127539829</v>
+        <v>0.8293967625628866</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.07077050739516</v>
+        <v>3.298789676942349</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.214110006345258</v>
+        <v>2.322505231448815</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2835121448405999</v>
+        <v>0.382384532332928</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.802472929373423</v>
+        <v>2.918166801295236</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.825201633727318</v>
+        <v>1.939970768685967</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.482003768752989</v>
+        <v>1.71214409869846</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.68534644498358</v>
+        <v>3.930722642288366</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.321734479265423</v>
+        <v>1.560666485939265</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>1.723952627373585</v>
+        <v>2.174265901485605</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.6534153533914733</v>
+        <v>1.102787254917416</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.8333768118503997</v>
+        <v>1.279604204641139</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.2856753758876494</v>
+        <v>0.7300863736489376</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.8024280522381275</v>
+        <v>1.250677419161633</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.6033945600092778</v>
+        <v>0.8406901323608196</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.03881363375288771</v>
+        <v>0.1931837796579146</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.04065850934666315</v>
+        <v>0.4857654399881071</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.694331275808537</v>
+        <v>-1.260226659207994</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-1.212501137316671</v>
+        <v>-0.7769836795025853</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.911504210040981</v>
+        <v>-1.479120734396034</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0008456</t>
+          <t>X ≈ 0.0008469</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>439</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8524784478550558</v>
+        <v>-0.8193500895722607</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8508585103176287</v>
+        <v>0.8863328164735833</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1440318237050064</v>
+        <v>-0.1084603716550561</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.05400156932407185</v>
+        <v>-0.1443141964715835</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.9381321886448646</v>
+        <v>0.8739206844003746</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.3476743828818556</v>
+        <v>0.1624589203890636</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.7089016007517088</v>
+        <v>0.5169787737981864</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.110337383371956</v>
+        <v>1.048286570732273</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4716153703539092</v>
+        <v>0.4109014294179119</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.831328479724263</v>
+        <v>0.9011290263927663</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.013845014457445</v>
+        <v>2.082679535309758</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.186097722765275</v>
+        <v>1.123168781126836</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.877374405036257</v>
+        <v>1.815179382005638</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.07018112996738779</v>
+        <v>0.004511748495026779</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.910651115636348</v>
+        <v>1.843790683274619</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.641095298143725</v>
+        <v>2.57481213183928</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.874602907415209</v>
+        <v>3.80422690959157</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.723033511079741</v>
+        <v>1.655794216309417</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5737067325488425</v>
+        <v>0.5080745867677123</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.07825254771704948</v>
+        <v>0.1475264864982364</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.6735702290622854</v>
+        <v>0.7439913377154284</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.5980051525362526</v>
+        <v>0.6681453763063274</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.099799928156109</v>
+        <v>1.170410521590242</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.7969334878577854</v>
+        <v>0.8667878355651055</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001648</t>
+          <t>X ≈ 0.001649</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>327</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.590622956911446</v>
+        <v>-2.559296624812099</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.5015627877534214</v>
+        <v>-0.4666537034863083</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5087606817781207</v>
+        <v>0.5447413278042319</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.8067935107296762</v>
+        <v>-0.7716310027064495</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.768534277670334</v>
+        <v>-1.709349595424214</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.59657811968296</v>
+        <v>-1.532522379339717</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.23220302692215</v>
+        <v>-0.1660859857286638</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.008191743690567</v>
+        <v>1.078019509528261</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.4380283717772144</v>
+        <v>0.5078468017833444</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.2765336351184757</v>
+        <v>0.3470318401896293</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.76990819101421</v>
+        <v>1.839562189056039</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.402525834360311</v>
+        <v>2.473673959874255</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.2398280086429736</v>
+        <v>-0.1696009230759827</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.4613569778635593</v>
+        <v>0.5301162208406254</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7178434323105236</v>
+        <v>0.7875243940764136</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.432729154848396</v>
+        <v>-1.363731463859352</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.481953166852136</v>
+        <v>-2.410654033882309</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.4498437580431442</v>
+        <v>-0.3803989748961456</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.5396547207983318</v>
+        <v>-0.4707320404540098</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.5625238189403206</v>
+        <v>0.6323981731837094</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.808945353587077</v>
+        <v>-1.744288252401105</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.803528540551589</v>
+        <v>-2.73756540647075</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.224551483001271</v>
+        <v>-2.157280296435189</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-3.220398090026258</v>
+        <v>-3.150543742319009</v>
       </c>
     </row>
     <row r="23">
@@ -2016,817 +2016,817 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.554204774828349</v>
+        <v>1.57919235749042</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.969656113904442</v>
+        <v>-1.936392088460217</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.53735736194475</v>
+        <v>-2.492103984725269</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.5142723784926702</v>
+        <v>-0.4749969618729466</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.760950288014747</v>
+        <v>2.824088194162009</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-2.060816698832561</v>
+        <v>-1.991720021371478</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.855999258303463</v>
+        <v>-2.781630762095212</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.669728910385629</v>
+        <v>-2.597424267437319</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.670619086342484</v>
+        <v>-7.585654572403577</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-7.07787505107401</v>
+        <v>-6.993769001249056</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.542166413525202</v>
+        <v>-6.718212521017698</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.817392131034751</v>
+        <v>-6.992471410257338</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.73747730602139</v>
+        <v>-4.922116205251157</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.410373412537801</v>
+        <v>-2.876010526726631</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-5.093138448454376</v>
+        <v>-5.552533391176816</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-3.579297617481537</v>
+        <v>-4.04043617358046</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-4.64107138476259</v>
+        <v>-5.095774496707918</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.746415150404104</v>
+        <v>-4.92825595993844</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.689065630807598</v>
+        <v>-2.607329027477903</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.500940786548533</v>
+        <v>-2.421127547406776</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.209401130713594</v>
+        <v>-1.132667457294069</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.3710192831730339</v>
+        <v>-0.2910822260426258</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.471802829140259</v>
+        <v>-1.392754302551403</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-3.574123480744873</v>
+        <v>-3.762164537426052</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.003253</t>
+          <t>X ≈ 0.003252</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.147165212273237</v>
+        <v>-6.063630162287012</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.558281345068536</v>
+        <v>-1.531789872750444</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.306844148524888</v>
+        <v>3.313221941009282</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.102893364349057</v>
+        <v>6.083996885569924</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.62160139277286</v>
+        <v>3.672770503081779</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.505034416461264</v>
+        <v>-2.424329853676127</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.441142261996042</v>
+        <v>4.48320352371119</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.057987475730378</v>
+        <v>2.110303231339607</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.797229572400319</v>
+        <v>2.851846527442873</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.723567774522088</v>
+        <v>2.777812788106253</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.188258125511318</v>
+        <v>0.2606500009272494</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.601494167395614</v>
+        <v>-3.507812376065324</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.726801246297406</v>
+        <v>-4.630583050425216</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.551074273208066</v>
+        <v>-3.452332483487254</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-4.915890148039175</v>
+        <v>-4.80661797029412</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-5.722809045029564</v>
+        <v>-5.60921213675833</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.656408191556451</v>
+        <v>-1.553751578498975</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.762603699479712</v>
+        <v>-1.65820088982391</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.946446597976745</v>
+        <v>-2.840464774795578</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-2.051541174759407</v>
+        <v>-1.957085383104982</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.4953985375281746</v>
+        <v>-0.4077043470098616</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.543451239288451</v>
+        <v>-1.882151707020363</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-2.677126777031717</v>
+        <v>-3.006278393139745</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-2.753068116300106</v>
+        <v>-3.082110646362942</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.004055</t>
+          <t>X ≈ 0.004054</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>103</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.535627192806224</v>
+        <v>5.556040957156071</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.520898119691182</v>
+        <v>-3.484975152284512</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-3.0151387535618</v>
+        <v>-2.973887159010381</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1423271098926762</v>
+        <v>0.1722577186740679</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5.593776331731803</v>
+        <v>5.65944936162748</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.842938539406461</v>
+        <v>3.908413142392732</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.910671760524458</v>
+        <v>7.977063811674405</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.727486324016027</v>
+        <v>4.794221575931459</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.868439284348767</v>
+        <v>1.935145653156269</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.903865455559163</v>
+        <v>6.971491559099604</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.148242846915551</v>
+        <v>8.215569325502578</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>3.998567714509726</v>
+        <v>4.066238693123658</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.778707287012473</v>
+        <v>5.847707417257432</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.434711182075866</v>
+        <v>9.503989246908588</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>9.747153962712979</v>
+        <v>9.817219969002444</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>9.372873835809948</v>
+        <v>9.442266714421024</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>9.258855292494488</v>
+        <v>9.309705472876885</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.357755371544833</v>
+        <v>2.429652749134817</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.603004748068919</v>
+        <v>1.674170110384743</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.760922330097081</v>
+        <v>2.826288410577149</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.159469493914678</v>
+        <v>4.22940611534333</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.112640651864297</v>
+        <v>3.182686367526458</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.445668245530939</v>
+        <v>1.515413507193024</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.311474479077923</v>
+        <v>3.3813288267852</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.004857</t>
+          <t>X ≈ 0.004856</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>61</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-11.01244019079094</v>
+        <v>-10.93971142355451</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.08065411217889107</v>
+        <v>0.1048649093327541</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.979442349352482</v>
+        <v>-2.934815973567012</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4318808970924977</v>
+        <v>-0.4035913818240289</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-4.056340945405097</v>
+        <v>-3.99066791550942</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.236875573048472</v>
+        <v>-2.171400970062201</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-3.014070709431437</v>
+        <v>-2.94767865828149</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.02369483192111943</v>
+        <v>0.04304041999431263</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.659862252191679</v>
+        <v>1.726568620999181</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.515080847525468</v>
+        <v>2.582706951065909</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.424987627237449</v>
+        <v>4.492314105824477</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.419153251120463</v>
+        <v>7.486824229734395</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.92588054090097</v>
+        <v>7.994880671145928</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.708852734195652</v>
+        <v>7.778130799028375</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7.054250499487345</v>
+        <v>7.124316505776811</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>10.9149943188909</v>
+        <v>10.98438719750197</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>9.179275473936428</v>
+        <v>9.219251552256793</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>12.35298058243136</v>
+        <v>12.38983487795798</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>10.92975948306805</v>
+        <v>10.96801424412111</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>6.198770491803273</v>
+        <v>6.24929976738126</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>10.57360286969057</v>
+        <v>10.64353949111922</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>10.49764781404796</v>
+        <v>10.56769352971012</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>12.41176724282517</v>
+        <v>12.48151250448726</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>17.25385869044191</v>
+        <v>17.32371303814919</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005659</t>
+          <t>X ≈ 0.005658</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>51</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-8.529036098900747</v>
+        <v>-7.632190027409145</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-8.883692133025676</v>
+        <v>-9.848081590505458</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-4.446196264033013</v>
+        <v>-5.500924250140066</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-9.075414838239737</v>
+        <v>-10.07975433015194</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-9.426074233653424</v>
+        <v>-9.360401203757746</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.386063936918504</v>
+        <v>-3.320589333932233</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.117454387791092</v>
+        <v>-6.051062336641145</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.443978220984704</v>
+        <v>-4.377242969069272</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.391098519598387</v>
+        <v>-4.324392150790885</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.221020001159822</v>
+        <v>-3.153393897619381</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.89706816974595</v>
+        <v>-4.829741691158922</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-7.12169937905233</v>
+        <v>-7.054028400438398</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-8.251060727409524</v>
+        <v>-8.182060597164565</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.294230029674246</v>
+        <v>1.363508094506969</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.310238515194563</v>
+        <v>-1.240172508905097</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.7200485954432807</v>
+        <v>-0.6506557168322047</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.8496541306922012</v>
+        <v>-0.7797027239395788</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.927715394388926</v>
+        <v>4.981289268954399</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.143838557320741</v>
+        <v>5.192310520008498</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.291666666666657</v>
+        <v>7.327940389054802</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.6700348851197</v>
+        <v>10.73997150654835</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.025717741057306</v>
+        <v>3.095463002719391</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.949776401788782</v>
+        <v>3.019630749496059</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.006462</t>
+          <t>X ≈ 0.00646</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>43</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.152107004153628</v>
+        <v>2.185381296472457</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.463597502249279</v>
+        <v>-7.429924493635937</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.565900525025718</v>
+        <v>-6.530546101357231</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.666560360492632</v>
+        <v>-2.630366643073728</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.928566598302339</v>
+        <v>3.994239628198017</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.772998345784295</v>
+        <v>-9.707523742798024</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.615065208368165</v>
+        <v>-3.548673157218218</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.208819189434912</v>
+        <v>-6.14208393751948</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.524572172337209</v>
+        <v>-1.457865803529707</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.938672078985952</v>
+        <v>-6.871045975445512</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.346647020126717</v>
+        <v>-4.27932054153969</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.324789995434379</v>
+        <v>2.392460974048312</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.119833470992447</v>
+        <v>-1.050833340747488</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.343656738222528</v>
+        <v>-1.274378673389805</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.635210062423774</v>
+        <v>2.705276068713239</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.402595015246966</v>
+        <v>-1.33320213663589</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.7919327366127931</v>
+        <v>0.8530129743263615</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.964213470180155</v>
+        <v>-3.869894119612582</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.422508911899499</v>
+        <v>-1.34866922792299</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-3.561046511627907</v>
+        <v>-3.481955665894645</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-8.75540971132353</v>
+        <v>-8.685473089894877</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-6.505783371617312</v>
+        <v>-6.435737655955151</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-6.231008205135247</v>
+        <v>-6.161262943473162</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-6.306949544403651</v>
+        <v>-6.237095196696373</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.007264</t>
+          <t>X ≈ 0.007262</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.946192237950676</v>
+        <v>3.511295511573742</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>4.581938502893415</v>
+        <v>3.147630546539233</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.174951036771979</v>
+        <v>5.290196586055693</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-14.69223490258562</v>
+        <v>-16.73654998539868</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-4.758926512318212</v>
+        <v>-6.406416629851208</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>5.708642388222103</v>
+        <v>4.428418280163058</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-8.788391755783984</v>
+        <v>-10.55754013284911</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-9.066946401302545</v>
+        <v>-10.83575157760218</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-5.58166661186138</v>
+        <v>-7.228123390482551</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-13.22122080615848</v>
+        <v>-15.11165495191554</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-6.092047088170261</v>
+        <v>-7.737812486863895</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.4873082367793273</v>
+        <v>-0.9131680465865344</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.070042373471608</v>
+        <v>-2.04355215511378</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>2.556145711263483</v>
+        <v>1.279843848631046</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>1.908118804881227</v>
+        <v>0.6325336135573778</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>2.49954407695089</v>
+        <v>1.22330951466472</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>5.844057836853381</v>
+        <v>4.644700320385496</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5.739074420758101</v>
+        <v>4.557914720742332</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.941354140448027</v>
+        <v>-2.336809783729898</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-4.202586206896555</v>
+        <v>-5.705271916460177</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>2.150765108243426</v>
+        <v>0.8660219267164067</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-1.373465809468158</v>
+        <v>-2.781252606121264</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.349585219082947</v>
+        <v>1.064650677789359</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-1.174631982254496</v>
+        <v>-2.582610146862528</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.008067</t>
+          <t>X ≈ 0.008064</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>12.92763298021414</v>
+        <v>14.14402683614789</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>5.202204054263767</v>
+        <v>6.681705686724257</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1357979371561129</v>
+        <v>-1.800197582661504</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.5885216918264646</v>
+        <v>1.024476782583008</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.9380020031662895</v>
+        <v>0.70437258454551</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.7613637059489022</v>
+        <v>0.8808812543030768</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-8.892904301940689</v>
+        <v>-6.987239231641503</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-1.823310799311123</v>
+        <v>-0.1797363906803184</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.913331971364585</v>
+        <v>3.425522966771268</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-6.219177903342441</v>
+        <v>-4.443564511319352</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-5.9500817941218</v>
+        <v>-4.174733627327278</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-6.229175697596702</v>
+        <v>-4.453483030775274</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-7.358930073978719</v>
+        <v>-9.129959756828519</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-7.596076358697132</v>
+        <v>-5.818639006757806</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-0.8910699759022407</v>
+        <v>0.6246182558856717</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-0.3012730841755697</v>
+        <v>1.2137764196587</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-0.4139242831977583</v>
+        <v>1.08508804085119</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>3.184796004410714</v>
+        <v>4.549248270736797</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-4.006488240064876</v>
+        <v>-2.331032150392964</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-7.523148148148152</v>
+        <v>-5.692272241452002</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-11.77005226084981</v>
+        <v>-9.848263787569302</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.7348962053813111</v>
+        <v>0.7901759653073057</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-11.57123215001029</v>
+        <v>-9.649635036496349</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.5360623781676495</v>
+        <v>0.9888184245661407</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.008869</t>
+          <t>X ≈ 0.008866</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.343021451392104</v>
+        <v>1.376295743710934</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.86689355579536</v>
+        <v>10.90056656440871</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.353759289243136</v>
+        <v>-5.318404865574649</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.130409745293527</v>
+        <v>-1.094216027874623</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.472822387460383</v>
+        <v>-1.407149357564705</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.603866035070141</v>
+        <v>8.669340638056411</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17.73576180777805</v>
+        <v>17.802153858928</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.48958811464048</v>
+        <v>12.55632336655592</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.601580370139303</v>
+        <v>7.668286738946804</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.78012591175084</v>
+        <v>11.84775201529128</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.094485178866094</v>
+        <v>7.161811657453121</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.76777222777218</v>
+        <v>11.83544320638612</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>15.588042914047</v>
+        <v>15.65704304429196</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.465694849368248</v>
+        <v>-4.396416784535525</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-10.06938799316754</v>
+        <v>-9.999321986878073</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-4.529566038784168</v>
+        <v>-4.460173160173092</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-4.673183542456862</v>
+        <v>-4.586471249531542</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.2218330414477521</v>
+        <v>0.2915451895044043</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.4379562043795673</v>
+        <v>0.5074365704287302</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.625</v>
+        <v>5.646663332777663</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.081799591002046</v>
+        <v>5.151736212430698</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>15.00584453535937</v>
+        <v>15.07589025102153</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.28061970184157</v>
+        <v>10.35036496350365</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.20467836257317</v>
+        <v>10.27453271028045</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.00967</t>
+          <t>X ≈ 0.009668</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>13</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.2078661718889379</v>
+        <v>0.241140464207767</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-30.64490768644067</v>
+        <v>-30.61123467782733</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-16.73264127682083</v>
+        <v>-16.69728685315234</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-32.69488179498279</v>
+        <v>-32.65868807756388</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-17.81170437503803</v>
+        <v>-17.74603134514236</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-25.27464328169986</v>
+        <v>-25.20916867871359</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.242126390979649</v>
+        <v>-3.175734339829702</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.077662648801983</v>
+        <v>4.144397900717415</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.76928223349346</v>
+        <v>11.83598860230096</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.376399203676378</v>
+        <v>3.444025307216819</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.650758470791715</v>
+        <v>3.718084949378742</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.361312600443021</v>
+        <v>3.428983579056954</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.216117448208479</v>
+        <v>2.285117578453438</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.603583048126069</v>
+        <v>-5.534304983293346</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-6.241810353415914</v>
+        <v>-6.171744347126449</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.667454237541989</v>
+        <v>-5.598061358930913</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.827029696303235</v>
+        <v>-5.721626529034708</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>1.760294579909292</v>
+        <v>1.813284319939157</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1.976417742841107</v>
+        <v>2.029175700863483</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.528846153846153</v>
+        <v>-5.403026108216025</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-6.072046562844108</v>
+        <v>-6.002109941415455</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.148001618486553</v>
+        <v>-6.077955902824392</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-13.56553414431223</v>
+        <v>-13.49578888265015</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>1.743139901034581</v>
+        <v>1.812994248741859</v>
       </c>
     </row>
     <row r="33">
@@ -2839,158 +2839,158 @@
         <v>10</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.434990970968144</v>
+        <v>-9.401716678649315</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6646161230831638</v>
+        <v>0.6982891316965052</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>18.02926348508397</v>
+        <v>18.06461790875246</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.424165824064652</v>
+        <v>7.460359541483555</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>26.95020038686677</v>
+        <v>27.01587341676245</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>17.4634519563952</v>
+        <v>17.52892655938147</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.234064085210782</v>
+        <v>7.300456136360729</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.827099255959965</v>
+        <v>-2.760364004044533</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.111670147459051</v>
+        <v>-3.04496377865155</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.885505558228481</v>
+        <v>-3.81787945468804</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.611146291113144</v>
+        <v>-3.543819812526117</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.781544542414139</v>
+        <v>-3.713873563800206</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-14.68864445655347</v>
+        <v>-14.61964432630851</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.127392571935637</v>
+        <v>-5.058114507102914</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>3.996284884679248</v>
+        <v>4.066350890968714</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.808736238648443</v>
+        <v>4.878129117259519</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>10.3268164575431</v>
+        <v>4.635516328108139</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>10.22183304144782</v>
+        <v>4.313284319939214</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>10.43795620437964</v>
+        <v>4.52917570086354</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>10.62500000000007</v>
+        <v>4.716021510831567</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>10.08179959100205</v>
+        <v>10.1517362124307</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>10.00584453535937</v>
+        <v>10.07589025102153</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>10.28061970184149</v>
+        <v>10.35036496350358</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>10.2046783625731</v>
+        <v>10.27453271028038</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.01128</t>
+          <t>X ≈ 0.01127</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>12</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>29.65921192758248</v>
+        <v>29.6924862199013</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>20.99070307960482</v>
+        <v>21.02437608821816</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>19.55100261551874</v>
+        <v>19.58635703918723</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.50387596899231</v>
+        <v>10.54006968641121</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18.47193951730148</v>
+        <v>18.53761254719716</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.32577079697498</v>
+        <v>10.39124539996125</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.21957133158763</v>
+        <v>1.285963382737577</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.9410166860690055</v>
+        <v>1.007751937984438</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.315866084425025</v>
+        <v>9.382572453232527</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2086973403222743</v>
+        <v>0.2763234438627151</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.537296037296031</v>
+        <v>8.604967015909963</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.41280481880883</v>
+        <v>7.481804949053789</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.532516768737231</v>
+        <v>6.602582775026697</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.127576818358555</v>
+        <v>7.196969696969632</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>6.993483124209689</v>
+        <v>7.063052559992215</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.2218330414477</v>
+        <v>15.29154518950432</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>7.104622871046168</v>
+        <v>7.174103237095302</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.62499999999994</v>
+        <v>15.69428238039667</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.08179959100205</v>
+        <v>15.1517362124307</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>6.672511202026094</v>
+        <v>6.742556917688255</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>15.28061970184162</v>
+        <v>15.35036496350371</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>23.53801169590644</v>
+        <v>23.60786604361372</v>
       </c>
     </row>
   </sheetData>
@@ -3180,1477 +3180,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01159</t>
+          <t>X &gt; -0.01158</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3351</v>
+        <v>3355</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0126924107908124</v>
+        <v>-0.01336710158713572</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.08322976999634335</v>
+        <v>0.08243296025613489</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.09667284090426165</v>
+        <v>0.1122829651131525</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1409767303884735</v>
+        <v>0.1567462325482794</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.08915019979411909</v>
+        <v>0.1044669794533633</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.08534337043892748</v>
+        <v>0.100616692962447</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07151115739918623</v>
+        <v>0.07006777182417068</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.04754079259318189</v>
+        <v>0.04611839699765596</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01699502084809268</v>
+        <v>0.01560905066082796</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.06258540371999999</v>
+        <v>0.06112605591376763</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1164295761256753</v>
+        <v>0.1149119854703997</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06271976610959484</v>
+        <v>0.06125847220143044</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.05607271490249133</v>
+        <v>0.05459163948760448</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1178845321441315</v>
+        <v>-0.1191649625586564</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1043879931675207</v>
+        <v>-0.1057010141132082</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.08687192630745244</v>
+        <v>-0.08819236071689573</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1437017080317133</v>
+        <v>-0.1449585445090662</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.007355829651501722</v>
+        <v>0.005915912503489551</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.06250924371210687</v>
+        <v>0.06100799900013243</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.0288748137108783</v>
+        <v>0.02741724196266659</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.01957190571829415</v>
+        <v>-0.02098564581826423</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.04783873335514244</v>
+        <v>-0.04922145585954496</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.05350917644005904</v>
+        <v>-0.05487937499456308</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1414869612108447</v>
+        <v>-0.1427549201220089</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01079</t>
+          <t>X &gt; -0.01078</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3342</v>
+        <v>3346</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01775993131559517</v>
+        <v>-0.01851932245809707</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.07931443851061459</v>
+        <v>0.07843014227227485</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1263817412992978</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1429796771025025</v>
+        <v>0.1586927671441885</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.09199307279097013</v>
+        <v>0.1071725947596391</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0579136541178471</v>
+        <v>0.0730770978500459</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1056485371051394</v>
+        <v>0.1039830080720989</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.02281140514787694</v>
+        <v>0.02123597526389887</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.007934928384024431</v>
+        <v>-0.009473564817646718</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.03984553261468449</v>
+        <v>0.03822820576748143</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.09309138140680062</v>
+        <v>0.09141712393274304</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.03997940044452264</v>
+        <v>0.03835990850476634</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.03632604358273284</v>
+        <v>0.03467953946196189</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1375098283431981</v>
+        <v>-0.1389560886958705</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1222131626265295</v>
+        <v>-0.1236964102688773</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1361047736811756</v>
+        <v>-0.1375562422074026</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.192741619494889</v>
+        <v>-0.1941300625348674</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.04101044720218283</v>
+        <v>-0.04258368877724905</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.01369567256002568</v>
+        <v>0.01206205535857663</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.02054692169755157</v>
+        <v>-0.02213553005103819</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.03778187387089815</v>
+        <v>-0.03936560900853436</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.06592579956878808</v>
+        <v>-0.06747892460564486</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.07235666668969287</v>
+        <v>-0.07389556831589061</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1603725051707698</v>
+        <v>-0.1618091904966761</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.009986</t>
+          <t>X &gt; -0.009979</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3328</v>
+        <v>3332</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.002479614706018651</v>
+        <v>-0.003399289937632943</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03668695538869571</v>
+        <v>0.03570922272463406</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.08996947129659105</v>
+        <v>0.1054501179461766</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1394793142730109</v>
+        <v>0.1551099728928023</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.05992876140072667</v>
+        <v>0.07492598003303641</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.05480048416367111</v>
+        <v>0.06975639826921309</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.04617820752186219</v>
+        <v>0.04429920437587498</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.06576162334082625</v>
+        <v>-0.0675168792197951</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.09683707640854777</v>
+        <v>-0.09855492451868741</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.01571917673338419</v>
+        <v>-0.01755979981132327</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.0365834955948543</v>
+        <v>0.03468801876006467</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01559817428081089</v>
+        <v>-0.01744127755095803</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.04451773285327931</v>
+        <v>-0.04636336284164599</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2181785150934488</v>
+        <v>-0.2198244959145796</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2000773777016676</v>
+        <v>-0.2017672199847667</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2165478818811906</v>
+        <v>-0.2181999637089476</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.2728836923820026</v>
+        <v>-0.2744736454585066</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.1500925734292693</v>
+        <v>-0.1518340795189985</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.09609720096096197</v>
+        <v>-0.09789756202559374</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1313025210084007</v>
+        <v>-0.1330557490996753</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1163391060859169</v>
+        <v>-0.1181288550355717</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.1443056147907171</v>
+        <v>-0.146065357856628</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.151942629188774</v>
+        <v>-0.1536854415368509</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.240033175888442</v>
+        <v>-0.2416737723126658</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.009184</t>
+          <t>X &gt; -0.009177</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3309</v>
+        <v>3313</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1535579698120983</v>
+        <v>0.1522563348438908</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.134847223749027</v>
+        <v>0.1335542525853413</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1065581710742975</v>
+        <v>0.1219105945427614</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1003513870357082</v>
+        <v>0.1159000185440036</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.05246836345538242</v>
+        <v>0.06718324668685227</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.07629679637385323</v>
+        <v>0.09094509966096354</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.04198063204864155</v>
+        <v>0.03971713649132624</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.03893318861765493</v>
+        <v>-0.04111158459485154</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.07041550402261976</v>
+        <v>-0.07255575189567054</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.01559873464467643</v>
+        <v>0.01332374443379081</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09674314165393838</v>
+        <v>0.09437987896911437</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.07598920200546644</v>
+        <v>0.07363869510796661</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.05336706780487788</v>
+        <v>0.05099869153280423</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2103798520225908</v>
+        <v>-0.2124407445258498</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.09798353264913828</v>
+        <v>-0.1002067092197265</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1480738700144073</v>
+        <v>-0.1502148859872392</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1737866787657794</v>
+        <v>-0.1759032633009454</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.1099919962596374</v>
+        <v>-0.1121908755754646</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.05691404305555636</v>
+        <v>-0.05916981896250206</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.09338213099909609</v>
+        <v>-0.09558798439073257</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.04501200320084564</v>
+        <v>-0.04729876947521205</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.1028839454620751</v>
+        <v>-0.105105224091524</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.112129542871422</v>
+        <v>-0.1143302688439647</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.200277817541739</v>
+        <v>-0.2023764355089455</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.008382</t>
+          <t>X &gt; -0.008375</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3292</v>
+        <v>3296</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1882805254501676</v>
+        <v>0.1867598787319906</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.1108358897467383</v>
+        <v>0.109392669466331</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.119973336919287</v>
+        <v>0.1352110802004987</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.08720930232558288</v>
+        <v>0.1026639548877739</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.01074954448365162</v>
+        <v>0.02524079101134191</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.02669647392128383</v>
+        <v>-0.01221571282675171</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.05724946019236654</v>
+        <v>-0.05974544108776314</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.07671809829207632</v>
+        <v>-0.07920458375463113</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.108587095697942</v>
+        <v>-0.1110347147932345</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.01816291376120915</v>
+        <v>-0.02075611303557423</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.06197743446735871</v>
+        <v>0.05929816610925087</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.01799048409218074</v>
+        <v>-0.02058719610131021</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.0652454385329122</v>
+        <v>-0.06783722411417159</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.2989618448400364</v>
+        <v>-0.3012823968422182</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.1826200584868261</v>
+        <v>-0.185112635966739</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.2360595452777403</v>
+        <v>-0.2384621028688798</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2612405294227145</v>
+        <v>-0.2636201617758687</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1662809670422405</v>
+        <v>-0.1687818849959228</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.114060780758436</v>
+        <v>-0.1166167467479085</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1820388349514559</v>
+        <v>-0.1845054983911538</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1306435045973444</v>
+        <v>-0.1331986163052861</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1580898908700732</v>
+        <v>-0.1606167229019917</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.1991859465034054</v>
+        <v>-0.2016520216343523</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2874237030405098</v>
+        <v>-0.2897876780691391</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.007579</t>
+          <t>X &gt; -0.007573</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3275</v>
+        <v>3279</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2233611541521441</v>
+        <v>0.2216188059863882</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1169166718378847</v>
+        <v>0.1152851791273051</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.133526887363395</v>
+        <v>0.1486486427034421</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1042806225076802</v>
+        <v>0.1196128438803257</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.09003302064094498</v>
+        <v>0.1041882220531463</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.03965080440167412</v>
+        <v>-0.02542126670540767</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.03599772471046947</v>
+        <v>-0.03887480496469209</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.114893371664138</v>
+        <v>-0.1176906517980001</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1471531658282572</v>
+        <v>-0.1499108497425681</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.1130823292834862</v>
+        <v>-0.115922734900316</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.03397502273270447</v>
+        <v>-0.0368992145019007</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.05209651923981085</v>
+        <v>-0.05501475254946797</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.09378881073056533</v>
+        <v>-0.09671582095628395</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3275778674157195</v>
+        <v>-0.3302336922655442</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2376821756395344</v>
+        <v>-0.2404829184039485</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.2944964885760868</v>
+        <v>-0.2971992514128203</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.2581926832247916</v>
+        <v>-0.260948251531417</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.1621962179243894</v>
+        <v>-0.165075815061833</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1413120883033585</v>
+        <v>-0.1442077657466925</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.2106206160414814</v>
+        <v>-0.2134239857318079</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1866567848368774</v>
+        <v>-0.1895191196838724</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.2138686169139774</v>
+        <v>-0.216703470404795</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2871458659240034</v>
+        <v>-0.2898789389353738</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3449399580375925</v>
+        <v>-0.3476081863344476</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.006777</t>
+          <t>X &gt; -0.006771</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3242</v>
+        <v>3245</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1720324404030507</v>
+        <v>0.1558460892624538</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.009909853278969649</v>
+        <v>-0.03994244164395155</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.009218040319446175</v>
+        <v>-0.02148609806766899</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.03158284972837322</v>
+        <v>-0.04323810805202299</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.04231991232127541</v>
+        <v>-0.02461921245944154</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1752516979125431</v>
+        <v>-0.1748694579990939</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1330930849000467</v>
+        <v>-0.1191050824167235</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2406898823778363</v>
+        <v>-0.2265320239903588</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.273735798698489</v>
+        <v>-0.2595543361335118</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2315155998906704</v>
+        <v>-0.2171817213208769</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.06225829271600247</v>
+        <v>-0.04814361747444451</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1084732722716737</v>
+        <v>-0.1249480388438897</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1699393148113515</v>
+        <v>-0.1860902188413149</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3423773304788398</v>
+        <v>-0.3583215464403509</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.2141252901164421</v>
+        <v>-0.1993020846331959</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2160129252311194</v>
+        <v>-0.2013293090760016</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.2087329422722988</v>
+        <v>-0.1940200107334888</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.1414674511630878</v>
+        <v>-0.126787631166188</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1225611962979869</v>
+        <v>-0.1079480449559185</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.194470117067155</v>
+        <v>-0.1798327319455311</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1339168959008816</v>
+        <v>-0.1499879255003407</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2222689048378541</v>
+        <v>-0.2382458746328595</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.2682547970791873</v>
+        <v>-0.2534551227563639</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.2950131858537972</v>
+        <v>-0.3109834684561363</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.005975</t>
+          <t>X &gt; -0.005969</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3199</v>
+        <v>3202</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2246049067686187</v>
+        <v>0.2387307884923047</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.1690193268866409</v>
+        <v>0.138005395886637</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2204651815330365</v>
+        <v>0.2074750516095847</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1144001040657869</v>
+        <v>0.1020454552834735</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01530289933448614</v>
+        <v>0.06340496484792624</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.0598013423284911</v>
+        <v>-0.02930566695400927</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1930777093662286</v>
+        <v>-0.1797503110681049</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.2050111089941922</v>
+        <v>-0.1916056415409386</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1768198788491659</v>
+        <v>-0.1945419746281587</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.07919559462948911</v>
+        <v>-0.07878282881743104</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.08870210349406449</v>
+        <v>0.08886058032042143</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.0166331644064428</v>
+        <v>-0.01625925237512149</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.09498334318487167</v>
+        <v>-0.09395262670371807</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2355801422202717</v>
+        <v>-0.2527650025276458</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.0967434141389063</v>
+        <v>-0.1139126054362833</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.137780213134981</v>
+        <v>-0.1550552251486792</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.09738815880131568</v>
+        <v>-0.1146767430097455</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.09017943905146097</v>
+        <v>-0.1074573042612172</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.0114819978676195</v>
+        <v>-0.02889021472876863</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.05561192631907375</v>
+        <v>-0.0730289109320239</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>0.01309253291335466</v>
+        <v>-0.004270027818911615</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1066203193734623</v>
+        <v>-0.1238600610882656</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.03188029815842697</v>
+        <v>-0.04926038772956076</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1204232316751046</v>
+        <v>-0.1377096382517919</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.005172</t>
+          <t>X &gt; -0.005167</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3157</v>
+        <v>3160</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.05816205881613712</v>
+        <v>0.04071361658692041</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.08803707787543402</v>
+        <v>-0.1197850701072483</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.01556954465260674</v>
+        <v>0.001974167650708125</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.1069005436614319</v>
+        <v>0.09387546068936814</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.01149199130090039</v>
+        <v>0.05935167763199445</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1303031836891506</v>
+        <v>-0.1317539699190178</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2231912038901385</v>
+        <v>-0.2420769449246833</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2629791078320878</v>
+        <v>-0.2817742727519246</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1718797870380939</v>
+        <v>-0.1907776938881085</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.0306000195178413</v>
+        <v>-0.03115053910795496</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1674000417810362</v>
+        <v>0.1981223078963481</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1276549468845047</v>
+        <v>0.1270034101457966</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.06388925763812381</v>
+        <v>0.06387565612455859</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1387257678968652</v>
+        <v>-0.1572032203220317</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.08358099780300421</v>
+        <v>-0.1019746399822381</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1018467246912209</v>
+        <v>-0.1203602672332948</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.05901529451262633</v>
+        <v>-0.07754775596353625</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.05023276051365855</v>
+        <v>-0.06875822389638131</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1026192856829482</v>
+        <v>0.1027574683104575</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.004943055994942824</v>
+        <v>0.05544620076358342</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.1134451606222981</v>
+        <v>0.1643904357777402</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.006817699525015541</v>
+        <v>0.04424468140134508</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.03362793490046556</v>
+        <v>0.06555483692137187</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.05506189716716392</v>
+        <v>-0.04192298592216304</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.00437</t>
+          <t>X &gt; -0.004365</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3091</v>
+        <v>3094</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.04329088906735734</v>
+        <v>0.05690208270950592</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2918846255769694</v>
+        <v>-0.2927676879155854</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.00642585336876067</v>
+        <v>0.006106154658446883</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.08318483355545681</v>
+        <v>0.08318422952569193</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.0707335905889579</v>
+        <v>-0.0414025799350668</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2519783439184806</v>
+        <v>-0.2406610478447746</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.2977774706467642</v>
+        <v>-0.304531199388812</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.4613043971030848</v>
+        <v>-0.467886611060365</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.3553137995208075</v>
+        <v>-0.343675533885019</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1942684881754744</v>
+        <v>-0.1639686523572124</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.0987719680739616</v>
+        <v>0.1287481091205649</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.0641777577261422</v>
+        <v>0.09432871803763021</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.02332434123548666</v>
+        <v>0.03499643841556122</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1143406730948371</v>
+        <v>-0.1216079054714001</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1406077603769589</v>
+        <v>-0.1479278129556718</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.01066607569822509</v>
+        <v>-0.01808406647116811</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>0.003714680483255961</v>
+        <v>-0.003743180569252047</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.01733955066601567</v>
+        <v>-0.02478792863635704</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.166462991709885</v>
+        <v>0.1780855856046841</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.03030058177117212</v>
+        <v>0.06120744499621367</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.1852590155090041</v>
+        <v>0.2163565678426593</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.0006237699445748035</v>
+        <v>0.03064138224331714</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.08160539518301846</v>
+        <v>-0.05041073138968954</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1706047173363174</v>
+        <v>-0.1585636051688795</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003568</t>
+          <t>X &gt; -0.003564</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2991</v>
+        <v>2993</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2321526661432145</v>
+        <v>-0.2011661563033584</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.3345380244855747</v>
+        <v>-0.351953699015823</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1779631310725449</v>
+        <v>-0.1609833863446823</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.2080335453124746</v>
+        <v>-0.190447994555484</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.122070466059526</v>
+        <v>-0.07516190390058597</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4820410095052665</v>
+        <v>-0.4537313132789293</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5370054249891254</v>
+        <v>-0.5603440024919593</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6967803381370175</v>
+        <v>-0.6866462871957566</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4887086435341033</v>
+        <v>-0.4598598592397281</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2632102768218516</v>
+        <v>-0.2148520473127817</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.06375193121856881</v>
+        <v>0.1117865947965697</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.02937062937063217</v>
+        <v>0.0189401359810617</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1341552790014831</v>
+        <v>-0.1045551531343065</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2357256635619009</v>
+        <v>-0.2256673518068197</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.2409233380361968</v>
+        <v>-0.2307505583066245</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1932954557846784</v>
+        <v>-0.1832681600937747</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.1740182669978694</v>
+        <v>-0.1639876890626937</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.09212821439727037</v>
+        <v>-0.08216185086933336</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.0571946813334705</v>
+        <v>0.08687582276515116</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.05636272545089582</v>
+        <v>-0.006886233960536003</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.05507055658841153</v>
+        <v>0.104976025389945</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.2347971758705185</v>
+        <v>-0.1847178345113107</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2608241484258116</v>
+        <v>-0.2109447591826168</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.350319965745193</v>
+        <v>-0.3201883054229313</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002765</t>
+          <t>X &gt; -0.002762</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2864</v>
+        <v>2865</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1299935391767875</v>
+        <v>-0.1500516983572879</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2566909440226439</v>
+        <v>-0.2230179354093025</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.202298287886407</v>
+        <v>-0.1669438642179202</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1669617091447009</v>
+        <v>-0.1655264206448095</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2541640628166419</v>
+        <v>-0.2036948241518814</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5689904454914014</v>
+        <v>-0.5382863571087455</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.5800542343231569</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6421426737082498</v>
+        <v>-0.6299292214357877</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.4614477638700265</v>
+        <v>-0.449311604738476</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2958259721342316</v>
+        <v>-0.2629945797976916</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1030821324405125</v>
+        <v>0.1356017888904049</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.01826168260708982</v>
+        <v>0.0511137197168452</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2151993609194136</v>
+        <v>-0.2015748095348187</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2417691815402065</v>
+        <v>-0.2485589784605224</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.113236687751666</v>
+        <v>-0.1198136025420808</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.2294664173456979</v>
+        <v>-0.201404286770142</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2731137831266608</v>
+        <v>-0.2798079024220925</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.203698873445866</v>
+        <v>-0.1896263586127773</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.09221470597969983</v>
+        <v>-0.09249367024099087</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1842082316009765</v>
+        <v>-0.1640567682424958</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.02597265450518194</v>
+        <v>0.04702417054588182</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3082915902950205</v>
+        <v>-0.3080539025560682</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.4523645913521506</v>
+        <v>-0.4175233436516663</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.4028635368682458</v>
+        <v>-0.3886435549901321</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001963</t>
+          <t>X &gt; -0.00196</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2682</v>
+        <v>2684</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3729344621306154</v>
+        <v>-0.3791717983837799</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2630061192081783</v>
+        <v>-0.2863395217187517</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3373527638866989</v>
+        <v>0.3149443584308358</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3492686715278097</v>
+        <v>0.3274089544625838</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3179506490269546</v>
+        <v>0.3465179275311669</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.1790547412581276</v>
+        <v>-0.17152516280931</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.1086665166352816</v>
+        <v>0.09548719226138047</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.0371903471156827</v>
+        <v>-0.01303499594275337</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.07861992295895703</v>
+        <v>0.1026912357121219</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.2706091778656159</v>
+        <v>0.3165511948219901</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.4923468341191395</v>
+        <v>0.5380007185159741</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3464658018561408</v>
+        <v>0.3924066294365502</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1734345448532792</v>
+        <v>0.1982672307335278</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1601980077745395</v>
+        <v>0.1629928879175608</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.267785345836856</v>
+        <v>0.2704885990663541</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2524216930173466</v>
+        <v>0.2551077904369095</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.2523285618260829</v>
+        <v>0.2550168457065141</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.147345145730803</v>
+        <v>0.1724532654254745</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4007122565210963</v>
+        <v>0.4478684393788157</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.1408286778398562</v>
+        <v>0.2101110582365848</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3277012303462996</v>
+        <v>0.3976378517749524</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.0132988775137477</v>
+        <v>0.02372929722130124</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.08464306371937624</v>
+        <v>-0.03711640758427848</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.063778013265825</v>
+        <v>-0.07569083666448506</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001161</t>
+          <t>X &gt; -0.001158</t>
         </is>
       </c>
       <c r="B19" t="n">
         <v>2419</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.2421444226024221</v>
+        <v>-0.1457813239582819</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1663047296840645</v>
+        <v>-0.1104923328344114</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1674519673008277</v>
+        <v>-0.1093666450233073</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.004972460220315611</v>
+        <v>0.02313564006534818</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1331237278278508</v>
+        <v>0.1631269504893922</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.0677572436118794</v>
+        <v>-0.06142949715808754</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.04673182541478837</v>
+        <v>0.03081934981575785</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1259518881041188</v>
+        <v>-0.1415550470573521</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.08443582308148478</v>
+        <v>-0.1000678651426483</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.00628208027013244</v>
+        <v>0.01547775468093704</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2633970797055909</v>
+        <v>0.2722619488182048</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5438885383261152</v>
+        <v>0.5533044712548474</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2267646978965487</v>
+        <v>0.2545447127251919</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3598328874996213</v>
+        <v>0.3632267596091907</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.3856520822685923</v>
+        <v>0.3482872423806569</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.5929778363803635</v>
+        <v>0.5963096309631055</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.6488643518452619</v>
+        <v>0.652267032409334</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.4200163610183481</v>
+        <v>0.44844031749777</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.4709867576413345</v>
+        <v>0.4826534229689727</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.4103014037985204</v>
+        <v>0.4463484960992119</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.3874584096720142</v>
+        <v>0.4245762289664512</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.212456105607373</v>
+        <v>0.1833726817781098</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.2392973877919786</v>
+        <v>0.209811015591292</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.1054638111055581</v>
+        <v>0.05129996947839288</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003582</t>
+          <t>X &gt; -0.0003561</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.02237664872391321</v>
+        <v>0.08178062379431594</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.1182463367375348</v>
+        <v>-0.05834897260902494</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.2903022264136865</v>
+        <v>0.3527803968514576</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4308832682623276</v>
+        <v>0.4459444024124508</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.7955404905375474</v>
+        <v>0.8683480562084114</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.2316455129762858</v>
+        <v>0.275966945666724</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6066471555850299</v>
+        <v>0.6243300006950321</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.1819648919466488</v>
+        <v>0.2280248424679314</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.3208993690491582</v>
+        <v>0.366977911322202</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.1315744307590307</v>
+        <v>0.2072514464630686</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.6292554378469646</v>
+        <v>0.7048546307400798</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.8174845632183505</v>
+        <v>0.8651296175359846</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.06322313503475385</v>
+        <v>-0.01413001029574446</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4272203654981155</v>
+        <v>0.4964984303308384</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.3343713319388044</v>
+        <v>0.40443733822827</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3241914016919551</v>
+        <v>0.3935842803030312</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.5613059543676471</v>
+        <v>0.601464018325558</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.5540264952826348</v>
+        <v>0.6237386433392587</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.1839259161528943</v>
+        <v>0.23373178059488</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.02900586223741897</v>
+        <v>0.1074853143820604</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.3162890878266609</v>
+        <v>0.4746324942310878</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.02348097783703906</v>
+        <v>0.105244458458003</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.1885885093021287</v>
+        <v>-0.06059394060593348</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.3332189479403525</v>
+        <v>-0.2342735519505439</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0004442</t>
+          <t>X &gt; 0.0004458</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8451322131252397</v>
+        <v>-0.7818890448169782</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.9895893552330151</v>
+        <v>-0.989601040117229</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.2042421397260199</v>
+        <v>-0.203986035781007</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1831469317711054</v>
+        <v>-0.2180836384511906</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8510743773524325</v>
+        <v>0.88026988985456</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6438875947075928</v>
+        <v>-0.6492292768770511</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1109356430665116</v>
+        <v>0.1045690195250302</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.1506496162621502</v>
+        <v>0.180779927806384</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4443715561436079</v>
+        <v>-0.4138652058005405</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3907085582561365</v>
+        <v>-0.3230824547156956</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3662837836584103</v>
+        <v>0.3965532536461112</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.06691046365998687</v>
+        <v>-0.07315732103040773</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4903181894766391</v>
+        <v>-0.4961284267152877</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.02733236151604501</v>
+        <v>-0.01701634199066149</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.2359841161101386</v>
+        <v>0.1906931784237287</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.1671681338120052</v>
+        <v>0.1223999072947493</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.6463052754344076</v>
+        <v>0.5620965370476725</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.4774240957608455</v>
+        <v>0.4318513119533591</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.0545696229099164</v>
+        <v>0.04795986334510616</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.04992012779552368</v>
+        <v>0.08125556047335891</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.4012884088934214</v>
+        <v>0.4712250303220742</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.4917780391957578</v>
+        <v>0.5231745960695235</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.1271670164195697</v>
+        <v>0.1586716727688327</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1534947413318903</v>
+        <v>0.1467371831238253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001247</t>
+          <t>X &gt; 0.001248</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.8422629986711527</v>
+        <v>-0.7672838950411602</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.708411964642906</v>
+        <v>-1.720982001967457</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2277584464281617</v>
+        <v>-0.2412291677093279</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.233587157851403</v>
+        <v>-0.2468445487789452</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.817072260664375</v>
+        <v>0.8827452905600524</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.031161356417343</v>
+        <v>-0.965686753431072</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1226115592678241</v>
+        <v>-0.05621950811787713</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.2241750543439167</v>
+        <v>-0.1574398024284847</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.8021280158699469</v>
+        <v>-0.7354216470624451</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8679988248694741</v>
+        <v>-0.8003727213290333</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2772032095095369</v>
+        <v>-0.2608263535033899</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5562971129844385</v>
+        <v>-0.5395757569513862</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.415066453703652</v>
+        <v>-1.397251098143776</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.01059694394475486</v>
+        <v>-0.02540962060807317</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.4180895607510777</v>
+        <v>-0.4538093123662676</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.7990721020791227</v>
+        <v>-0.8337359422390378</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.6145689776257086</v>
+        <v>-0.7019312014485806</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.009072820008725557</v>
+        <v>-0.04533424311973988</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.1481894439330418</v>
+        <v>-0.1314276709200115</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.03885435168739093</v>
+        <v>0.05541813904801529</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.2949434631157217</v>
+        <v>0.3648800845443745</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.4502889798038794</v>
+        <v>0.4666540165633393</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.2527136314917655</v>
+        <v>-0.2357806848089581</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.09781274062974177</v>
+        <v>-0.1339930446041748</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.002049</t>
+          <t>X &gt; 0.00205</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.1249308702588863</v>
+        <v>-0.03388193930261707</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.203568402337844</v>
+        <v>-2.234330379443477</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.5299438352907231</v>
+        <v>-0.562896692156059</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.001592863969420932</v>
+        <v>-0.03206961707143563</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.877917101361312</v>
+        <v>1.94359013125699</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.7991773142744947</v>
+        <v>-0.733702711288224</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.07764743138456254</v>
+        <v>-0.01125538023461559</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.7298010806391062</v>
+        <v>-0.6630658287236741</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.310950021843126</v>
+        <v>-1.244243653035625</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.337587425140569</v>
+        <v>-1.269961321600128</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.117109643601459</v>
+        <v>-1.120434680683537</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.770268384981598</v>
+        <v>-1.772783087867523</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.897253369054773</v>
+        <v>-1.899681144761011</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1743447512766423</v>
+        <v>-0.2527650025276458</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.8841498979294258</v>
+        <v>-0.961839502612527</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.5390898483080449</v>
+        <v>-0.6168291392730296</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>0.1515974337632997</v>
+        <v>-0.002616600440035199</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.1717704632249735</v>
+        <v>0.09179487739451275</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.0124242894859492</v>
+        <v>0.007436570428701827</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.1760012515644505</v>
+        <v>-0.1807176196032643</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.158145022791778</v>
+        <v>1.228081644220431</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.785293156913326</v>
+        <v>1.778017910596063</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.5563089248992128</v>
+        <v>0.5506152763947654</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.183348375120154</v>
+        <v>1.100565250956222</v>
       </c>
     </row>
     <row r="24">
@@ -4660,735 +4660,735 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.7531592064380774</v>
+        <v>-0.639131847565757</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.291083861975871</v>
+        <v>-2.34612133888298</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.2211057083022467</v>
+        <v>0.1609711043673343</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1945976184767844</v>
+        <v>0.1341234314082982</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.547540891871989</v>
+        <v>1.613213921767667</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.3271501652243245</v>
+        <v>-0.2616755622380538</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.9618393728247483</v>
+        <v>1.028231423974695</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.004000496061522085</v>
+        <v>0.06273475585390997</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.068443404012669</v>
+        <v>1.135149772820171</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8100719107690111</v>
+        <v>0.8776980143094519</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.9126098720424238</v>
+        <v>0.9799363506294512</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1180520510417509</v>
+        <v>0.1857230296556835</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.8346178616034692</v>
+        <v>-0.7656177313585104</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.6622383857814143</v>
+        <v>0.7315164506141372</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.6905923701118084</v>
+        <v>0.760658376401274</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.5983671963654942</v>
+        <v>0.6677600749765702</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.944716629660064</v>
+        <v>1.908413384734494</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>2.011850253151714</v>
+        <v>1.975393986755236</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>1.023154138975094</v>
+        <v>0.9885362267860884</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.6938468158347675</v>
+        <v>0.6599181192283439</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.043933842292923</v>
+        <v>2.113870463721575</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.592051431911159</v>
+        <v>2.554375621073234</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.315102460462256</v>
+        <v>1.279796977273008</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.963299052228273</v>
+        <v>2.925135119918934</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003654</t>
+          <t>X &gt; 0.003653</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>438</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.9955824666865638</v>
+        <v>1.131880159295306</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.528659107183273</v>
+        <v>-2.611987548145414</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.7792935120438997</v>
+        <v>-0.8681884153582331</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.720877258038882</v>
+        <v>-1.808415162073693</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.8751285833607625</v>
+        <v>0.9408016132564399</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3789218979620799</v>
+        <v>0.4443965009483506</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.1661538012901289</v>
+        <v>-0.09976175014018196</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.672498879610508</v>
+        <v>-0.605763627695076</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5079693494212378</v>
+        <v>0.5746757182287396</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.189714804255452</v>
+        <v>0.2573409077958928</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.14744536977625</v>
+        <v>1.214771848363277</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.323932331904999</v>
+        <v>1.391603310518931</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.427231546219673</v>
+        <v>0.4962316764646317</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.028198197599906</v>
+        <v>2.097476262432629</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.508219122571717</v>
+        <v>2.578285128861182</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.647698306589454</v>
+        <v>2.71709118520053</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.11220458539691</v>
+        <v>3.0387549138267</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.235531671584738</v>
+        <v>3.161704642807344</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.310102323101027</v>
+        <v>2.238643859722558</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.583904109589042</v>
+        <v>1.514327938483284</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.867187718855924</v>
+        <v>2.937124340284576</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.93278517462884</v>
+        <v>4.002830890291001</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.609386825129242</v>
+        <v>2.679132086791327</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.816550508691812</v>
+        <v>4.886404856399089</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.004456</t>
+          <t>X &gt; 0.004455</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>335</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.4003118819412705</v>
+        <v>-0.2283842054200989</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.223582634680831</v>
+        <v>-2.343576434036976</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.09185452733839838</v>
+        <v>-0.2207646225338422</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.293743078626804</v>
+        <v>-2.417398167199131</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5756795303175082</v>
+        <v>-0.5100065004218308</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6861339649297733</v>
+        <v>-0.6206593619435026</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.649476287459997</v>
+        <v>-2.58308423631005</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.332792837740456</v>
+        <v>-2.266057585825024</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.08967560823455756</v>
+        <v>0.1563819770420594</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.874635993011061</v>
+        <v>-1.807009889470621</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-1.00503863065763</v>
+        <v>-0.9377121520706027</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5015817515817602</v>
+        <v>0.5692527301956929</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.218147562143479</v>
+        <v>-1.14914743189852</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.2490281827016503</v>
+        <v>-0.1797501178689274</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.2825167687372385</v>
+        <v>0.3525827750267041</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.5799577707395684</v>
+        <v>0.6493506493506445</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.222338845602728</v>
+        <v>1.110671607611266</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.505415130999992</v>
+        <v>3.386783284742471</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.527508443185532</v>
+        <v>2.412198475190607</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.222014925373138</v>
+        <v>1.110949047063393</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.469859292494583</v>
+        <v>2.539795913923236</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.18494901297138</v>
+        <v>4.254994728633541</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>2.967186866020675</v>
+        <v>3.036932127682761</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.279305228244731</v>
+        <v>5.349159575952008</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.005258</t>
+          <t>X &gt; 0.005257</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>274</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.962242230612844</v>
+        <v>2.1562543358434</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.736569647667856</v>
+        <v>-2.888667390042649</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.5510026155187475</v>
+        <v>0.383458488462594</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.708245243128964</v>
+        <v>-2.865727415038116</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.1992122445742623</v>
+        <v>0.2648852744699397</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.3408958696916713</v>
+        <v>-0.2754212667054006</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.568307456291166</v>
+        <v>-2.501915405141219</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.846862101809727</v>
+        <v>-2.780126849894295</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2598914913325387</v>
+        <v>-0.1931851225250369</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.851908720283788</v>
+        <v>-2.784282616743347</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.213913089532085</v>
+        <v>-2.146586610945057</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-1.038461538461533</v>
+        <v>-0.9707905598476003</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.253861847857763</v>
+        <v>-3.184861717612804</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-2.020673204346664</v>
+        <v>-1.951395139513942</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.225058988838512</v>
+        <v>-1.154992982549047</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.720908030126232</v>
+        <v>-1.651515151515156</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.5490959512160885</v>
+        <v>-0.6945231975835284</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.53570165458644</v>
+        <v>1.382454280413469</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.6569343065693474</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>0.1140510948905131</v>
+        <v>-0.03299034687599089</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.6657411968414664</v>
+        <v>0.7356778182701191</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.779567163096665</v>
+        <v>2.849612878758826</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.8645613076809866</v>
+        <v>0.9343065693430717</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.613437486660686</v>
+        <v>2.683291834367964</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.006061</t>
+          <t>X &gt; 0.006059</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>223</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.361592879963496</v>
+        <v>4.394867172282325</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.330725491823692</v>
+        <v>-1.297052483210351</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.693859758375879</v>
+        <v>1.729214182044366</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.252076411960125</v>
+        <v>-1.215882694541222</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.400510945872966</v>
+        <v>2.466183975768644</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.355532701736891</v>
+        <v>0.4210073047231617</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.756619144602844</v>
+        <v>-1.690227093452897</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.481602361549974</v>
+        <v>-2.414867109634542</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.6849137034726596</v>
+        <v>0.7516200722801614</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.7674931358682</v>
+        <v>-2.699867032327759</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.600276725895725</v>
+        <v>-1.532950247308698</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.3527722277722347</v>
+        <v>0.4204432063861674</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.778790087463555</v>
+        <v>-2.709512022630832</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.205578469357995</v>
+        <v>-1.13551246306853</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.949804134022337</v>
+        <v>-1.880411255411261</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.4803584303493409</v>
+        <v>-0.6750426781030114</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.759949633376003</v>
+        <v>0.5594023323615147</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.3692186835128055</v>
+        <v>-0.5639920009998676</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.527466367713004</v>
+        <v>-1.716431905317563</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.622236283437417</v>
+        <v>-1.552299662008764</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.889252607108318</v>
+        <v>1.959298322770479</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.3703058004962685</v>
+        <v>0.4400510621583535</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.536516927595521</v>
+        <v>2.606371275302799</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006863</t>
+          <t>X &gt; 0.006861</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>180</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.889414505851406</v>
+        <v>4.922688798170235</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.1343494884446486</v>
+        <v>0.16802249705799</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.66702471496626</v>
+        <v>3.702379138634747</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.914171913144024</v>
+        <v>-0.8779781957251203</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.035475428903737</v>
+        <v>2.101148458799415</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.775126229755841</v>
+        <v>2.840600832742112</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.312657029370015</v>
+        <v>-1.246264978220069</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.591211674888577</v>
+        <v>-1.524476422973144</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.212735329360569</v>
+        <v>1.279441698168071</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.771044832790068</v>
+        <v>-1.703418729249627</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.9441993778294275</v>
+        <v>-0.8768728992424002</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1183209056137215</v>
+        <v>-0.05064992699978887</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.347784499791473</v>
+        <v>-2.278784369546514</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.121627498671131</v>
+        <v>-3.052349433838408</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.123100174172521</v>
+        <v>-2.053034167883055</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.080526312396444</v>
+        <v>-2.011133433785368</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-0.7842946535680753</v>
+        <v>-1.04007819507224</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.888499708114423</v>
+        <v>1.617512040333104</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.1175993511759899</v>
+        <v>-0.3765413301237786</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.041666666666664</v>
+        <v>-1.294667895846366</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.0817995910020457</v>
+        <v>0.1517362124306985</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.894733424248322</v>
+        <v>3.964779139910483</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.947286368508237</v>
+        <v>2.017031630170322</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.649122807017541</v>
+        <v>4.718977154724818</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.007665</t>
+          <t>X &gt; 0.007663</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.878510173196574</v>
+        <v>5.182682298332743</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.7198232361845882</v>
+        <v>-0.3808526699517145</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.761528931308206</v>
+        <v>3.409886450951937</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.73194614443085</v>
+        <v>2.043337660267369</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.340360569933118</v>
+        <v>3.668331501445579</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.211735709255692</v>
+        <v>2.548108145059302</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.1230801035174451</v>
+        <v>0.468969918685282</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1554745420011159</v>
+        <v>0.1907584739322061</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.51762047038995</v>
+        <v>2.846624740814235</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.4279955859363085</v>
+        <v>0.7665195222940895</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.04446011620954238</v>
+        <v>0.3869843932141848</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.2346337872653592</v>
+        <v>0.1082349897661885</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.01701974259462</v>
+        <v>-2.322116619573599</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-4.212060764155275</v>
+        <v>-3.850385038503845</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.897307792666275</v>
+        <v>-2.54774402235892</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.960142479886997</v>
+        <v>-2.606951871657756</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-2.057289502721872</v>
+        <v>-2.087274237393402</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.148985359328549</v>
+        <v>1.075858914994569</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>0.04060521100208803</v>
+        <v>-0.01543924656476037</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4346026490066208</v>
+        <v>-0.4821882078385613</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.3155514023754336</v>
+        <v>0.02015726506228077</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>4.906506787015068</v>
+        <v>5.207469198390022</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>1.870023675351504</v>
+        <v>2.192470226661548</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>5.767592269857865</v>
+        <v>6.06400639449091</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.008468</t>
+          <t>X &gt; 0.008465</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>124</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.125878594249201</v>
+        <v>3.15915288656803</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.009296920395123</v>
+        <v>-1.975623911781781</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.55100261551874</v>
+        <v>4.586357039187227</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.237209302325581</v>
+        <v>2.273403019744485</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.271939517301533</v>
+        <v>4.33761254719721</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.859104130308317</v>
+        <v>2.924578733294588</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.08623799825429</v>
+        <v>2.152630049404237</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.207683352735728</v>
+        <v>0.2744186046511601</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.649199417758368</v>
+        <v>2.71590578656587</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.875364006988939</v>
+        <v>1.942990110529379</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.349723274104271</v>
+        <v>1.417049752691298</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.070629370629369</v>
+        <v>1.138300349243302</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.8538618478577717</v>
+        <v>-0.784861717612813</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.475218658892118</v>
+        <v>-3.405940594059395</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-3.334149897929429</v>
+        <v>-3.264083891639963</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-3.539089848308038</v>
+        <v>-3.469696969696962</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-2.415119026327929</v>
+        <v>-2.803614106674445</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.705704009189688</v>
+        <v>0.2915451895043759</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.9218271721215032</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>1.108870967741936</v>
+        <v>0.6942823803967286</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.17857378455043</v>
+        <v>2.248510405979083</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.134876793423949</v>
+        <v>6.20492250908611</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.79674873409963</v>
+        <v>4.866493995761715</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>7.140162233540842</v>
+        <v>7.210016581248119</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.00927</t>
+          <t>X &gt; 0.009266</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>104</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.468735737106343</v>
+        <v>3.502010029425172</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.485487396585597</v>
+        <v>-4.451814387972256</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.455764520280646</v>
+        <v>6.491118943949132</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.884828349944634</v>
+        <v>2.921022067363538</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.376701422063441</v>
+        <v>5.442374451959118</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.754342225546424</v>
+        <v>1.819816828532694</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.9232858112695155</v>
+        <v>-0.8568937601195685</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.154221409169025</v>
+        <v>-2.087486157253593</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.696818465377419</v>
+        <v>1.763524834184921</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.02939789777295942</v>
+        <v>0.03822820576748143</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.2449613693423771</v>
+        <v>0.3122878479294044</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.9865134865134877</v>
+        <v>-0.918842507899555</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-4.01576660976253</v>
+        <v>-3.946766479517571</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.284742468415935</v>
+        <v>-3.215464403583212</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-2.038911802691324</v>
+        <v>-1.968845796401858</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-3.348613657831855</v>
+        <v>-3.279220779220779</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-1.980875850149282</v>
+        <v>-2.460756963817303</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.7987561183708252</v>
+        <v>0.2915451895043759</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>1.01487928130264</v>
+        <v>0.5074365704287018</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>0.2403846153846132</v>
+        <v>-0.2580985719842204</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.620261129463586</v>
+        <v>1.690197750892239</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>4.428921458436371</v>
+        <v>4.498967174098532</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.742158163380026</v>
+        <v>3.811903425042111</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.550832208726938</v>
+        <v>6.620686556434215</v>
       </c>
     </row>
     <row r="33">
@@ -5401,76 +5401,76 @@
         <v>91</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.934574246423118</v>
+        <v>3.967848538741947</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.748427355177725</v>
+        <v>-0.7147543465643835</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>9.768393919866568</v>
+        <v>9.803748343535055</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.967644084934271</v>
+        <v>8.003837802353175</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.689330821649364</v>
+        <v>8.755003851545041</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.615625869438752</v>
+        <v>5.681100472425022</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.5920228713109239</v>
+        <v>-0.525630820160977</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-3.04449056030775</v>
+        <v>-2.977755308392318</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.2578950699322817</v>
+        <v>0.3246014387397835</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5159403408371475</v>
+        <v>-0.4483142372967066</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.2415810737218109</v>
+        <v>-0.1742545951347836</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.607631498935845</v>
+        <v>-1.539960520321912</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.906035760901254</v>
+        <v>-4.837035630656295</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.953479528457343</v>
+        <v>-2.88420146362462</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-1.438497724016379</v>
+        <v>-1.368431717726914</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-3.017350717873263</v>
+        <v>-2.947957839262187</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-1.43142530069872</v>
+        <v>-1.994918454500528</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.6613934810081901</v>
+        <v>0.07415388515654797</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.8775166439400053</v>
+        <v>0.2900452660808739</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>1.064560439560438</v>
+        <v>0.4768910760489007</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.719162228364681</v>
+        <v>2.789098849793334</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>5.939910469425364</v>
+        <v>6.009956185087525</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.214685635907493</v>
+        <v>6.284430897569578</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.23764539554012</v>
+        <v>7.307499743247398</v>
       </c>
     </row>
     <row r="34">
@@ -5483,158 +5483,158 @@
         <v>81</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.585137853508456</v>
+        <v>5.618412145827286</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.9228771673086982</v>
+        <v>-0.8892041586953567</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.748533479716272</v>
+        <v>8.783887903384759</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.034740166523115</v>
+        <v>8.070933883942018</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.434902480264498</v>
+        <v>6.500575510160175</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.152931290802151</v>
+        <v>4.218405893788422</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.558206446190148</v>
+        <v>-1.491814395040201</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.071328992943279</v>
+        <v>-3.004593741027847</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.6738907757830646</v>
+        <v>0.7405971445905664</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.09994463498636463</v>
+        <v>-0.03231853144592378</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.1744146321289719</v>
+        <v>0.2417411107159992</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.339247172580507</v>
+        <v>-1.271576193966574</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.698306292302213</v>
+        <v>-3.629306162057254</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.685095202102005</v>
+        <v>-2.615817137269282</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-2.109458539904729</v>
+        <v>-2.039392533615263</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-3.983534292752488</v>
+        <v>-3.914141414141412</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-2.883060085666848</v>
+        <v>-2.813490649884322</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.5189076992929955</v>
+        <v>-0.4491955512363717</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.3027845363611803</v>
+        <v>-0.2333041703120458</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.1157407407407476</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.810194652730438</v>
+        <v>1.880131274159091</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.437943300791538</v>
+        <v>5.507989016453699</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.712718467273667</v>
+        <v>5.782463728935753</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>6.871345029239755</v>
+        <v>6.941199376947033</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01168</t>
+          <t>X &gt; 0.01167</t>
         </is>
       </c>
       <c r="B35" t="n">
         <v>69</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.398342362365149</v>
+        <v>1.431616654683978</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.869843195228881</v>
+        <v>6.905197618897368</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.60532524435456</v>
+        <v>7.641518961773464</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.341504734692847</v>
+        <v>4.407177764588525</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.079393985380783</v>
+        <v>3.144868588367054</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-2.04129823362976</v>
+        <v>-1.974906182479813</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.769128241467158</v>
+        <v>-3.702392989551726</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.8290614518068509</v>
+        <v>-0.7623550829993491</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.1536215002574366</v>
+        <v>-0.08599539671699574</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1207377668578999</v>
+        <v>0.1880642454449273</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-3.056906861254681</v>
+        <v>-2.989235882640749</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-5.630673442060662</v>
+        <v>-5.561673311815703</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.40275489077618</v>
+        <v>-4.333476825943457</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-3.612410767494644</v>
+        <v>-3.542344761205179</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-5.915901442510936</v>
+        <v>-5.84650856389986</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-4.600719774341023</v>
+        <v>-4.531150338558497</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.256427828117467</v>
+        <v>-3.186715680060843</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-1.591029302866808</v>
+        <v>-1.521548936817673</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-2.853260869565219</v>
+        <v>-2.78397848916849</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4979105539254931</v>
+        <v>-0.4279739324968403</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5.223235839707264</v>
+        <v>5.293281555369425</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.048735643870543</v>
+        <v>4.118480905532628</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>3.972794304602075</v>
+        <v>4.042648652309353</v>
       </c>
     </row>
   </sheetData>
@@ -5824,1477 +5824,1477 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01159</t>
+          <t>X &lt; -0.01158</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>68</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.05093299995368739</v>
+        <v>-0.01765870763485822</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.733934601554537</v>
+        <v>-4.700261592941196</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-5.44899738448126</v>
+        <v>-6.138280641972187</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-7.633378932968533</v>
+        <v>-8.300510023733771</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-5.057472247404348</v>
+        <v>-5.737749771643365</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-4.870307634397562</v>
+        <v>-5.550783585545986</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.172585531157466</v>
+        <v>-4.106193480007519</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.980551941381918</v>
+        <v>-2.913816689466486</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.468447641065161</v>
+        <v>-1.401741272257659</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.712871287128714</v>
+        <v>-3.645245183588273</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.379688490601609</v>
+        <v>-6.312362012014582</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.717605923488279</v>
+        <v>-3.649934944874346</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.371508906681299</v>
+        <v>-3.302508776436341</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.230663694049049</v>
+        <v>5.299941758881772</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4.571732455011748</v>
+        <v>4.641798461301214</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3.696204269339013</v>
+        <v>3.765597147950089</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>6.503287045778322</v>
+        <v>6.572856481560848</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.9546375467875379</v>
+        <v>-0.884925398730914</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-3.679690854443962</v>
+        <v>-3.610210488394827</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-2.022058823529413</v>
+        <v>-1.952776443132684</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.3759172380608646</v>
+        <v>0.4458538594895174</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>1.770550417712379</v>
+        <v>1.84059613337454</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.045325584194508</v>
+        <v>2.115070845856593</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.381148950808388</v>
+        <v>6.451003298515666</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01079</t>
+          <t>X &lt; -0.01078</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>77</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.1720324404030507</v>
+        <v>0.2053067327218798</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-4.009296920395123</v>
+        <v>-3.975623911781781</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.098348033831911</v>
+        <v>-6.695694242864057</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-6.812141347025069</v>
+        <v>-7.408648262306798</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.580008534646524</v>
+        <v>-5.180336170751509</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.094142622938435</v>
+        <v>-3.711318702602838</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.165710053693765</v>
+        <v>-5.099318002543818</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.548160803108424</v>
+        <v>-1.481425551192991</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.2079434393844934</v>
+        <v>-0.1412370705769916</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.280480148855219</v>
+        <v>-2.212854045314778</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.603523479142481</v>
+        <v>-4.536197000555454</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.285214785214784</v>
+        <v>-2.217543806600851</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.111004705000632</v>
+        <v>-2.042004574755673</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.459846276172804</v>
+        <v>5.529124341005527</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4.800915037135503</v>
+        <v>4.870981043424969</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.395975086756884</v>
+        <v>5.46536796536796</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>7.859283990010567</v>
+        <v>7.928853425793093</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.260794080408786</v>
+        <v>1.33050622846541</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.120485354061991</v>
+        <v>-1.051004988012856</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.365259740259738</v>
+        <v>0.4345421206564666</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.12076062996308</v>
+        <v>1.190697251391732</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>2.343506873021774</v>
+        <v>2.413552588683935</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>2.618282039503903</v>
+        <v>2.688027301165988</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.43844459633933</v>
+        <v>6.508298944046608</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.009986</t>
+          <t>X &lt; -0.009979</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>91</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.4132518405333983</v>
+        <v>-0.3799775482145691</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.835383876916865</v>
+        <v>-1.801710868303523</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-3.800645736129603</v>
+        <v>-4.32668643907364</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.61334014822387</v>
+        <v>-6.126596980255513</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-2.681906636544618</v>
+        <v>-3.201517887585389</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-2.494742023537832</v>
+        <v>-3.01455170148801</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.168707056690756</v>
+        <v>-2.10231500554081</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>1.948342693395077</v>
+        <v>2.015077945310509</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.088759857318806</v>
+        <v>3.155466226126308</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1171222487471866</v>
+        <v>0.1847483522876274</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.806320681939681</v>
+        <v>-1.738994203352654</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1123876123876215</v>
+        <v>0.1800585910015542</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.185698591702668</v>
+        <v>1.254698721947626</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.557748374074897</v>
+        <v>7.62702643890762</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.898817135037596</v>
+        <v>6.968883141327062</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.493877184658977</v>
+        <v>7.563270063270053</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>9.557585688312258</v>
+        <v>9.627155124094784</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>5.056997876612584</v>
+        <v>5.126710024669208</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.075318841742202</v>
+        <v>3.144799207791337</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.36126373626373</v>
+        <v>4.430546116660459</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.818063327265776</v>
+        <v>3.887999948694429</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>4.841009370524269</v>
+        <v>4.91105508618643</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.115784537006398</v>
+        <v>5.185529798668483</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.33654649444123</v>
+        <v>8.406400842148507</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.009184</t>
+          <t>X &lt; -0.009177</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>110</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-5.025472757102143</v>
+        <v>-4.992198464783314</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.459747370845577</v>
+        <v>-4.426074362232235</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-3.630815566299439</v>
+        <v>-4.062291609461425</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.435517970401698</v>
+        <v>-3.874344728003265</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-1.982605937243925</v>
+        <v>-2.408333398748731</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-2.704532233328038</v>
+        <v>-3.122268113552252</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.659216547200252</v>
+        <v>-1.592824496050305</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.7895015345539136</v>
+        <v>0.8562367864693456</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.740108508667461</v>
+        <v>1.806814877474963</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.8519087202837881</v>
+        <v>-0.7842826167433472</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.304822180441185</v>
+        <v>-3.237495701854158</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.674825174825173</v>
+        <v>-2.607154196211241</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.981134575130497</v>
+        <v>-1.912134444885538</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>5.979326795653328</v>
+        <v>6.048604860486051</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.593122829343308</v>
+        <v>2.663188835632774</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>4.097273788055588</v>
+        <v>4.166666666666664</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.872271002997579</v>
+        <v>4.941840438780105</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>2.949105768720486</v>
+        <v>3.01881791677711</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.347047113470481</v>
+        <v>1.416527479519615</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.443181818181813</v>
+        <v>2.512464198578542</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>0.9908905000929593</v>
+        <v>1.060827121521612</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.73311726263217</v>
+        <v>2.803162978294331</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.0078924291143</v>
+        <v>3.077637690776385</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.659223817118551</v>
+        <v>5.729078164825829</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.008382</t>
+          <t>X &lt; -0.008375</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>127</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.236621405750796</v>
+        <v>-5.203347113431967</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.228046920395123</v>
+        <v>-3.194373911781781</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.480493447473393</v>
+        <v>-3.851142960812773</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-2.61948361106024</v>
+        <v>-3.001596980255513</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.6225486716748421</v>
+        <v>-0.9936374528027869</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.352017516135092</v>
+        <v>-0.02542126670540767</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.153954533687362</v>
+        <v>1.220346584837309</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.662801462971949</v>
+        <v>1.729536714887381</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.491719102797745</v>
+        <v>2.558425471605247</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.1430805424220054</v>
+        <v>0.2107066459624463</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.944764914872103</v>
+        <v>-1.877438436285075</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.1383459060624403</v>
+        <v>0.206016884676373</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.376059411984755</v>
+        <v>1.445059542229714</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.453915199375594</v>
+        <v>7.523193264208317</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.432779235928841</v>
+        <v>4.502845242218307</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>5.815240860353363</v>
+        <v>5.884633738964439</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.468548741007609</v>
+        <v>6.538118176790135</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>4.001360600502871</v>
+        <v>4.071072748559494</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.642680613828389</v>
+        <v>2.712160979877524</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.404527559055119</v>
+        <v>4.473809939451847</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.073925575254016</v>
+        <v>3.143862196682669</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.785372094414555</v>
+        <v>3.855417810076716</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>4.847548835699833</v>
+        <v>4.917294097361918</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>7.133812220840817</v>
+        <v>7.203666568548094</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.007579</t>
+          <t>X &lt; -0.007573</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>144</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.39825933678528</v>
+        <v>-5.364985044466451</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.974814161774432</v>
+        <v>-2.941141153161091</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.365664051147924</v>
+        <v>-3.689505029778289</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-2.690568475452196</v>
+        <v>-3.023148704393449</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.3613938160318</v>
+        <v>-2.669284004526929</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.6035485747527645</v>
+        <v>0.2763028712256315</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5251268871431805</v>
+        <v>0.5915189382931274</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.329905574957955</v>
+        <v>2.396640826873387</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.065866084425032</v>
+        <v>3.132572453232534</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.292030673655603</v>
+        <v>2.359656777196044</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.4830566074376108</v>
+        <v>0.5503830860246381</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.8984071484071521</v>
+        <v>0.9660781270210848</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.857249263253344</v>
+        <v>1.926249393498303</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.191448007774532</v>
+        <v>7.260726072607255</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.14362787984836</v>
+        <v>5.213693886137825</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>6.433132373914169</v>
+        <v>6.502525252525245</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.604594235320818</v>
+        <v>5.674163671103344</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>3.416277485892195</v>
+        <v>3.485989633948819</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>2.937956204379567</v>
+        <v>3.007436570428702</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.513888888888886</v>
+        <v>4.583171269285614</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>3.970688479890931</v>
+        <v>4.040625101319584</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.589177868692779</v>
+        <v>4.65922358435494</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>6.25284192406378</v>
+        <v>6.322587185725865</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.565789473684212</v>
+        <v>7.63564382139149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.006777</t>
+          <t>X &lt; -0.006771</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.394791796812243</v>
+        <v>-3.08529155787641</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.07671265073220468</v>
+        <v>0.4688205326626615</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.08176574606318354</v>
+        <v>0.1419125947427844</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.3343844435685241</v>
+        <v>0.5400696864111509</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.5340864099568989</v>
+        <v>0.2042792138638774</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.981138028613401</v>
+        <v>2.942455828266667</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>2.208271896559374</v>
+        <v>1.941394094348063</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4.189604256690536</v>
+        <v>3.910373660830949</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.796092073125607</v>
+        <v>4.513658595554631</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>4.022256662356178</v>
+        <v>3.740742919518141</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.9067854209969326</v>
+        <v>0.644016044826131</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>1.757635020346889</v>
+        <v>2.050659899805105</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>2.893030807509469</v>
+        <v>3.174688844184935</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.061504504949674</v>
+        <v>6.324396484592285</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.707658011675093</v>
+        <v>3.419062175775771</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.737746309884052</v>
+        <v>3.45165134490977</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.603652615735129</v>
+        <v>3.317734207932297</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>2.368725696814991</v>
+        <v>2.089297998493137</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>2.01987710833437</v>
+        <v>1.743391626608485</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.336864406779661</v>
+        <v>3.053832942194475</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.228692246369285</v>
+        <v>2.511286774228445</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>3.847652444963956</v>
+        <v>4.120834071246314</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>4.687399362858507</v>
+        <v>4.395308783728368</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>5.176429775002482</v>
+        <v>5.443072036123077</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.005975</t>
+          <t>X &lt; -0.005969</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.449906159114022</v>
+        <v>-3.640847113431967</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.657945569043775</v>
+        <v>-2.18990962606749</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.412798289458628</v>
+        <v>-3.181500103669912</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.864148163737767</v>
+        <v>-1.662311265969805</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-0.4194631976305914</v>
+        <v>-1.105244595659926</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.6726787909418022</v>
+        <v>0.2268208857609579</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.614744785584612</v>
+        <v>2.412089508863701</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.788678827848855</v>
+        <v>2.584328514561072</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.377706205088685</v>
+        <v>2.625815696475776</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.9662730978980321</v>
+        <v>0.9519991195383852</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.486640362259365</v>
+        <v>-1.476643941002386</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.05244755244755339</v>
+        <v>0.04640845735141141</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.200683606687683</v>
+        <v>1.175498642747556</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.252054068380609</v>
+        <v>3.48998700775055</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.229486465706941</v>
+        <v>1.47437764682158</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>1.824546515328322</v>
+        <v>2.068764568764571</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.235907366633946</v>
+        <v>1.482358744004294</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.130923950538666</v>
+        <v>1.377518040183112</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.01658925016588597</v>
+        <v>0.2359433577590195</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.625</v>
+        <v>0.8752778555098502</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.3727458635434076</v>
+        <v>-0.1197570002389838</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.369480898995803</v>
+        <v>1.614351789483138</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.2806197018415659</v>
+        <v>0.5313604386167725</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.568314726209465</v>
+        <v>1.812994248741916</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.005172</t>
+          <t>X &lt; -0.005167</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.8651326417058556</v>
+        <v>-0.6557724865662991</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.877921124717659</v>
+        <v>1.248256685233144</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.3546577618397535</v>
+        <v>-0.1897623637978469</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.44580956559895</v>
+        <v>-1.2758507115988</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.3016453883588426</v>
+        <v>-0.8653725274296562</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.39495318691209</v>
+        <v>1.402481355017436</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.508879507688256</v>
+        <v>2.727066139629812</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>2.985041843301772</v>
+        <v>3.200734394124851</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1.894482436626291</v>
+        <v>2.114402027167372</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2086973403222743</v>
+        <v>0.2136668022587074</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.168458544077545</v>
+        <v>-2.519792352571848</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.689976689976682</v>
+        <v>-1.670722207147669</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9205285145244346</v>
+        <v>-0.9141850258834836</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.50962982595636</v>
+        <v>1.726134877638707</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>0.8506985869190586</v>
+        <v>1.067991580058148</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.066970757752564</v>
+        <v>1.285020011435101</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.5540891848157585</v>
+        <v>0.7737443838915965</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.4491057687204787</v>
+        <v>0.6689036800704145</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.387138852654658</v>
+        <v>-1.379355882401491</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2146946564885468</v>
+        <v>-0.8151515818674255</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-1.521253844112458</v>
+        <v>-2.112414730965533</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.07049134250315348</v>
+        <v>-0.6788267301104796</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.5590749546469809</v>
+        <v>-0.9375138243751309</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.5100218740234794</v>
+        <v>0.3505783376568061</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.00437</t>
+          <t>X &lt; -0.004365</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.5397930475418349</v>
+        <v>-0.6646566372414924</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.57752942691026</v>
+        <v>2.571995135837263</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1937421292260098</v>
+        <v>-0.1897623637978469</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9075354424191673</v>
+        <v>-0.9027163832405876</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.5289965743585938</v>
+        <v>0.2540304576449728</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.217662688866881</v>
+        <v>2.10781226622872</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.645997758014055</v>
+        <v>2.712389809164002</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.169244914297295</v>
+        <v>4.235980166212727</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.191368092457161</v>
+        <v>3.076266146926237</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.694095124813714</v>
+        <v>1.402449569988839</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.052693644324727</v>
+        <v>-1.32649379085224</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-0.727557940548877</v>
+        <v>-1.004642593699636</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.3414751409091323</v>
+        <v>-0.4499219585766667</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.9477420661834017</v>
+        <v>1.017020131016125</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.195155238022238</v>
+        <v>1.265221244311704</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.02247353410864861</v>
+        <v>0.04691934450242741</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.1565672282575719</v>
+        <v>-0.0869977924750458</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.04056415927252743</v>
+        <v>0.1102763073291513</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.683255916832557</v>
+        <v>-1.78863593712417</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.4084346504559235</v>
+        <v>-0.6954457162800054</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-1.863489162797343</v>
+        <v>-2.144336295122173</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.1157360117530217</v>
+        <v>-0.4074934347790062</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.6464733603781525</v>
+        <v>0.350364963503651</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.485166167451148</v>
+        <v>1.368757634292528</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003568</t>
+          <t>X &lt; -0.003564</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.498292387352649</v>
+        <v>1.279061353387256</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.211901236286906</v>
+        <v>2.31728226670792</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.132988758705807</v>
+        <v>1.008375387811078</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.342982974381009</v>
+        <v>1.212852561028889</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.7467663071398789</v>
+        <v>0.4183464921513433</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.243399742317564</v>
+        <v>3.034923560880799</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.62526802134898</v>
+        <v>3.78212313696185</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.732394669132965</v>
+        <v>4.655985424927664</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.29734756590652</v>
+        <v>3.084569381035919</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.736152870097989</v>
+        <v>1.389994718824312</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.5416920391207825</v>
+        <v>-0.870507850995331</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1072883033439851</v>
+        <v>-0.2275982682682169</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.8389455767361937</v>
+        <v>0.6303807766135137</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.545663011641523</v>
+        <v>1.473689035570224</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.582787457058977</v>
+        <v>1.509990182434109</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.249773260740675</v>
+        <v>1.178451178451184</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.115679566591751</v>
+        <v>1.04453404147371</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.5466590275266441</v>
+        <v>0.4767303746895593</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.4922763537599693</v>
+        <v>-0.6962671332750077</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>0.2986596736596709</v>
+        <v>-0.04645836034401896</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.4776409684385143</v>
+        <v>-0.820486009791523</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.544306073820977</v>
+        <v>1.187001362132712</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.729217832682693</v>
+        <v>1.371246634037298</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.354211072853474</v>
+        <v>2.134997826559449</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002765</t>
+          <t>X &lt; -0.002762</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.5811977431853705</v>
+        <v>0.6801405408890204</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.230489935732756</v>
+        <v>1.050831114673244</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.9566965656966744</v>
+        <v>0.7701026222260978</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.776711081685022</v>
+        <v>0.7638623837020901</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.225950212488698</v>
+        <v>0.9581072468438521</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.839139780932207</v>
+        <v>2.662631830639725</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.95753924602613</v>
+        <v>2.88170806358864</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.213743958796343</v>
+        <v>3.135411512452578</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.292056560615507</v>
+        <v>2.21857008496729</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.446025903232233</v>
+        <v>1.268034515502741</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.6051962250012721</v>
+        <v>-0.766964456900169</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.1687266222149901</v>
+        <v>-0.3352342866359095</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>1.0323635546467</v>
+        <v>0.9574870368355803</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.168788496742934</v>
+        <v>1.200120012001207</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5098572577056331</v>
+        <v>0.5419767144206489</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>1.104917307327014</v>
+        <v>0.9581105169340418</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.328605366308686</v>
+        <v>1.358952738245343</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.9745212134907675</v>
+        <v>0.897605795564985</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4020495616506636</v>
+        <v>0.4004846987709456</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.8767985611510838</v>
+        <v>0.7655836281685637</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.2059701931706215</v>
+        <v>-0.3117218980862404</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.516635902265904</v>
+        <v>1.504461679593028</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.262601683823547</v>
+        <v>2.067717378530489</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>2.006480164374899</v>
+        <v>1.923278229993642</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001963</t>
+          <t>X &lt; -0.00196</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.285664117037413</v>
+        <v>1.305676950739155</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.8900319386652811</v>
+        <v>0.9709001523893406</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.282330717814595</v>
+        <v>-1.196775490933256</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.324081020255065</v>
+        <v>-1.240385467537969</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.211775152954189</v>
+        <v>-1.308438322950046</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5904634842787146</v>
+        <v>0.5610398592999601</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.451581651813008</v>
+        <v>-0.4030746485823329</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.07740071478148991</v>
+        <v>-0.01014515373809388</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.3427143288723613</v>
+        <v>-0.429255503756707</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.03961575009609</v>
+        <v>-1.202171179793197</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-1.844878615234464</v>
+        <v>-2.003380354835585</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.31425591951907</v>
+        <v>-1.475678145380343</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.6843611730939401</v>
+        <v>-0.7730178414351485</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6358124510648651</v>
+        <v>-0.6458327773478061</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.024838157038737</v>
+        <v>-1.034434295952629</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.9695891735442146</v>
+        <v>-0.979130931961123</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.9687301011614196</v>
+        <v>-0.9782771794507283</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.588977769363062</v>
+        <v>-0.6788052148082926</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.510622956648852</v>
+        <v>-1.675851839274799</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.5674119241192415</v>
+        <v>-0.8151515818674255</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.246113688130741</v>
+        <v>-1.492468639321324</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1025565486513997</v>
+        <v>-0.1400341754291432</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.2534826597791522</v>
+        <v>0.08009469323338436</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.1775413205106844</v>
+        <v>0.2204055113629195</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001161</t>
+          <t>X &lt; -0.001158</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.5379697736347424</v>
+        <v>0.3039260621104347</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3557824446842375</v>
+        <v>0.2198351207947269</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3603372729169507</v>
+        <v>0.2187681063809066</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.05554144246090686</v>
+        <v>-0.09892899606579419</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.3650386139111887</v>
+        <v>-0.4347194686130678</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.120336734682077</v>
+        <v>0.1044006917515716</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1555115047278122</v>
+        <v>-0.1166768812888321</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2617588994554154</v>
+        <v>0.2981809808887874</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1616372287036398</v>
+        <v>0.1985618817095727</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.05690690934572018</v>
+        <v>-0.07881365557567932</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.6789619848598605</v>
+        <v>-0.696726263165985</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.356462262836757</v>
+        <v>-1.371907777614965</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.5885232024394398</v>
+        <v>-0.6531156858667799</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.9094816070992948</v>
+        <v>-0.915374556323556</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.9708032843836065</v>
+        <v>-0.8783837923351001</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.471360764642704</v>
+        <v>-1.475655261653273</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.605454458791627</v>
+        <v>-1.609572398630746</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.054338444095613</v>
+        <v>-1.118583906821343</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.178810262686305</v>
+        <v>-1.200607123712317</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.033341658341655</v>
+        <v>-1.113066179682718</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-0.9771414679390134</v>
+        <v>-1.059783152018156</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.5535960240811235</v>
+        <v>-0.4807697887398277</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.6193802981584398</v>
+        <v>-0.5451574245560522</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.2953216374269019</v>
+        <v>-0.1637143016718099</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003582</t>
+          <t>X &lt; -0.0003561</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1374</v>
+        <v>1379</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.0666177982471936</v>
+        <v>-0.1541468977597873</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.1423276283413415</v>
+        <v>0.05315306663548824</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.4634482515332863</v>
+        <v>-0.5540317297112622</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6714612179056374</v>
+        <v>-0.6910318254679026</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.213526860138806</v>
+        <v>-1.314799259858226</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.3756030280430807</v>
+        <v>-0.4396863963884101</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.931549420400799</v>
+        <v>-0.9550844423044822</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3011444330819302</v>
+        <v>-0.3681192468268506</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5079330949136107</v>
+        <v>-0.5741375034774165</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.2260852683733887</v>
+        <v>-0.3369521694129034</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.9662187548812327</v>
+        <v>-1.072993537351984</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.245312658356134</v>
+        <v>-1.310797123680885</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.06448478013353309</v>
+        <v>-0.008561139578134203</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6644862440987893</v>
+        <v>-0.7653042961563017</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.5257380052535794</v>
+        <v>-0.6280752148503765</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.5108084850012986</v>
+        <v>-0.6121409320975459</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.8624511276636326</v>
+        <v>-0.9205460893083028</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.8521872778555846</v>
+        <v>-0.9530278929847711</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3027845363611803</v>
+        <v>-0.3753420113368549</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.07267441860464885</v>
+        <v>-0.1884962013688281</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.5000185908161399</v>
+        <v>-0.7310423693348582</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.00584453535943652</v>
+        <v>-0.1847904151623254</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.251507620327736</v>
+        <v>0.06050989103988513</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.4666870961975462</v>
+        <v>0.3180424999830649</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0004442</t>
+          <t>X &lt; 0.0004458</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.68649924700469</v>
+        <v>0.6326571600723057</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8086902316391402</v>
+        <v>0.8079143030765792</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1482173985931965</v>
+        <v>0.1478543653904367</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1307283167872839</v>
+        <v>0.1601873964165037</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7402791322161519</v>
+        <v>-0.7641531028830499</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5186968419910727</v>
+        <v>0.5232939367207123</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.1164429668931604</v>
+        <v>-0.1111085686996702</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.149827376878001</v>
+        <v>-0.1750725576412862</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3518295841566541</v>
+        <v>0.3257664510889171</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.3071577771285803</v>
+        <v>0.2495281598327068</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3314797334145254</v>
+        <v>-0.356676788863652</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.0338946767518209</v>
+        <v>0.03915871834202278</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3914901134533508</v>
+        <v>0.3964587332728584</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.04480490284698391</v>
+        <v>-0.007444353457898956</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.220125180035815</v>
+        <v>-0.1822364158075231</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.162410643579399</v>
+        <v>-0.1249064218989062</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.5651770943108119</v>
+        <v>-0.4956076585282858</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.4233282488748316</v>
+        <v>-0.3855101570834805</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.06769199357632516</v>
+        <v>-0.0621496735261573</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.06391280947255495</v>
+        <v>-0.09024206882411789</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.359772837646311</v>
+        <v>-0.4178500315241607</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4357278932889201</v>
+        <v>-0.4617441575805543</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.1288630567791174</v>
+        <v>-0.1552832344522415</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1509250857027666</v>
+        <v>-0.1452735329919648</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001247</t>
+          <t>X &lt; 0.001248</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3916225388858834</v>
+        <v>0.3548332321403862</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8154542695659259</v>
+        <v>0.8212645929718931</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.09212815664428575</v>
+        <v>0.09867869936881135</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.09532970076646308</v>
+        <v>0.1017767221666261</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4188750407573849</v>
+        <v>-0.4502767261591956</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4861522447426552</v>
+        <v>0.4532676125676289</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.04148517952056352</v>
+        <v>0.008907105681302596</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.09141437225851234</v>
+        <v>0.05856758689456854</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3748938622028106</v>
+        <v>0.3415556999107565</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.4077131168456489</v>
+        <v>0.3738527026403489</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.117591272367406</v>
+        <v>0.109504219300149</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2546432715850599</v>
+        <v>0.2463263796120714</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.676603167353008</v>
+        <v>0.6675688379427456</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.02280666410725729</v>
+        <v>-0.005159004827966385</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.1874494067207237</v>
+        <v>0.2051301769662075</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.3739536299528297</v>
+        <v>0.3912934733959972</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.2833381966734621</v>
+        <v>0.3268509085363362</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.01305169104463744</v>
+        <v>0.004713377248833694</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.05501451595485918</v>
+        <v>0.04676729620010178</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.03673269481932806</v>
+        <v>-0.04484805438588069</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.1621028480223501</v>
+        <v>-0.1960898745258177</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.2380579036649593</v>
+        <v>-0.2459888268383352</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.1063277628437476</v>
+        <v>0.0979715779510002</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.03038642357527976</v>
+        <v>0.04815047257902449</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.002049</t>
+          <t>X &lt; 0.00205</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2622</v>
+        <v>2624</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.02045987503738189</v>
+        <v>-0.007236212599259773</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6533262789983567</v>
+        <v>0.6627706357380916</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1444800519995937</v>
+        <v>0.1545388573690403</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.01711543212054067</v>
+        <v>-0.006854653616635176</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5887815453170546</v>
+        <v>-0.6078971155538255</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2270616094275368</v>
+        <v>0.2067622056221126</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.007392574782969064</v>
+        <v>-0.01286103895374424</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.2064675472646087</v>
+        <v>0.1857994847725664</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3839010521179347</v>
+        <v>0.3629646100952755</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3924742731486361</v>
+        <v>0.3712361241968054</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3246282170700496</v>
+        <v>0.3256710971652907</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.5241097814319602</v>
+        <v>0.5249264890609382</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5634897503157461</v>
+        <v>0.5642830942458019</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.03771893623725475</v>
+        <v>0.06174001430561304</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.2539779559518536</v>
+        <v>0.2781214315539629</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.1487670226474123</v>
+        <v>0.1727526309116243</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.06145914200016733</v>
+        <v>-0.01457301078402651</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.06758051529254061</v>
+        <v>-0.04331021384417966</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.01918665276328824</v>
+        <v>-0.01767758482243664</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.03810975609756184</v>
+        <v>0.039543134108186</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.3680669739998592</v>
+        <v>-0.3888043281098419</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.5583948851514222</v>
+        <v>-0.5562498860690326</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.1846739671134259</v>
+        <v>-0.1829683698296805</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3750317823544407</v>
+        <v>-0.3504672897196244</v>
       </c>
     </row>
     <row r="24">
@@ -7304,735 +7304,735 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2839</v>
+        <v>2842</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1370674054380174</v>
+        <v>0.1139555411261881</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4503043387864096</v>
+        <v>0.4618324124669968</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.0606138995267429</v>
+        <v>-0.04838605763206516</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.05498530740489826</v>
+        <v>-0.04268089633942651</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.3305814911018246</v>
+        <v>-0.343506333921674</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.05139835097381962</v>
+        <v>0.03797502570452593</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2111691496083594</v>
+        <v>-0.2244168365299828</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.01411825960216362</v>
+        <v>-0.02771650210416965</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2329885205305473</v>
+        <v>-0.2462790873837122</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1800551441860847</v>
+        <v>-0.1936123413094961</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2011539188781839</v>
+        <v>-0.2146250896352555</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.0388125388125431</v>
+        <v>-0.05258643659615814</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1562505116927895</v>
+        <v>0.1419265011810111</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1496127579437641</v>
+        <v>-0.1635694961990026</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1552321185899999</v>
+        <v>-0.1693470495346929</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1366293913660357</v>
+        <v>-0.1506376506376483</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.4113206250580248</v>
+        <v>-0.4041759044272553</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.4251430485663121</v>
+        <v>-0.4179736022061959</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.2233170984695292</v>
+        <v>-0.2163863389177507</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.1561400422237824</v>
+        <v>-0.1493028568616239</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.4321039640841917</v>
+        <v>-0.4458033306272924</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.5432578933628491</v>
+        <v>-0.535924094969964</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.2827605798485777</v>
+        <v>-0.2757342274917747</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.6195555225977358</v>
+        <v>-0.6121667971087845</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003654</t>
+          <t>X &lt; 0.003653</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2981</v>
+        <v>2985</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1609678925972844</v>
+        <v>-0.1810999411099417</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.3544605746082041</v>
+        <v>0.3671381514461771</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.0991532319799191</v>
+        <v>0.1123224186812379</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2372093023255744</v>
+        <v>0.2503593967008655</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1425986620916007</v>
+        <v>-0.1520311424464751</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.07004863820401397</v>
+        <v>-0.07955184631899215</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.01002845537808383</v>
+        <v>0.0002808324765553039</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.08431886675442968</v>
+        <v>0.07441860465116434</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.08869707639855307</v>
+        <v>-0.09836563724206826</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.04180366168173322</v>
+        <v>-0.05167299820978144</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1823849784850964</v>
+        <v>-0.1920259897177701</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2082476347182194</v>
+        <v>-0.2179079284602921</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.07632925006438995</v>
+        <v>-0.08636422178643954</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3113390602299191</v>
+        <v>-0.3211042547140437</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.3817243375413355</v>
+        <v>-0.3915145632069468</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4025436635690838</v>
+        <v>-0.4122103386809286</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4697029534342079</v>
+        <v>-0.4595151431171089</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4879091748227538</v>
+        <v>-0.4776855797263906</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.3523987855735484</v>
+        <v>-0.3423459655365022</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.2460217755443921</v>
+        <v>-0.2361058391481166</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.4342861998826706</v>
+        <v>-0.4439799856951439</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.5908701813686861</v>
+        <v>-0.6003735588210546</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.3967780178096731</v>
+        <v>-0.4065004082311106</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.7211854415194878</v>
+        <v>-0.7304924153477614</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.004456</t>
+          <t>X &lt; 0.004455</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3084</v>
+        <v>3088</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.02838986276175604</v>
+        <v>0.009844427256354038</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2258077494921551</v>
+        <v>0.2393053031474395</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.004409755615277788</v>
+        <v>0.009594889203320633</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2342444296217536</v>
+        <v>0.2481615516182814</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.04834183838470807</v>
+        <v>0.04115407971492147</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.06026504614192163</v>
+        <v>0.05308114875352743</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.2733347724478392</v>
+        <v>0.265774379301142</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.2391773830680961</v>
+        <v>0.2316213117088495</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.02349264163478892</v>
+        <v>-0.03070930047474718</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1898619081836443</v>
+        <v>0.1822677628995848</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.09545970821280747</v>
+        <v>0.08801749462678998</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.06798129172926792</v>
+        <v>-0.07525240971119018</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1191181133574872</v>
+        <v>0.1114584889720831</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.01395043260480833</v>
+        <v>0.006393923215377129</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.04359362367328146</v>
+        <v>-0.05116399499913626</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.07613287645428102</v>
+        <v>-0.08359034611054028</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.1455225913084703</v>
+        <v>-0.1336722837914408</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.3930536899438337</v>
+        <v>-0.3809410697908078</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.2871975670675084</v>
+        <v>-0.2752283713565475</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.1457253886010363</v>
+        <v>-0.1339285545757676</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.281012200381177</v>
+        <v>-0.2882508467734439</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4672598068311018</v>
+        <v>-0.4742715612761401</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.3352636044793442</v>
+        <v>-0.3424158717181029</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5865019227706085</v>
+        <v>-0.5933429373880159</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.005258</t>
+          <t>X &lt; 0.005257</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3145</v>
+        <v>3149</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.185014995899202</v>
+        <v>-0.2023613090155649</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2231730732877608</v>
+        <v>0.2370614779310642</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.06195157089516101</v>
+        <v>-0.04748134465116038</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2215329432863911</v>
+        <v>0.2358911788856304</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.03106396040949733</v>
+        <v>-0.03674804642450624</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.01584037319257448</v>
+        <v>0.01011252988335087</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.2098697603548985</v>
+        <v>0.203814883527464</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.2342656312167435</v>
+        <v>0.2281480610354976</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.009123444349057763</v>
+        <v>0.003291180179523678</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2350853496108556</v>
+        <v>0.2288851136919376</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1794983770501091</v>
+        <v>0.1733926821440122</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.07721999166866311</v>
+        <v>0.0712117416483693</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.2707023359774112</v>
+        <v>0.264331064913307</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1633355579753442</v>
+        <v>0.1570739721217222</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.09420405069093363</v>
+        <v>0.08795918723239282</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.137306090778246</v>
+        <v>0.1310634865767923</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.03493828495419393</v>
+        <v>0.04773296147135397</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.1463040578857928</v>
+        <v>-0.1333121345285946</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.06998030355693885</v>
+        <v>-0.05710513588275035</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.02282470625595323</v>
+        <v>-0.01003234041545653</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.07067817265742349</v>
+        <v>-0.07669018350838996</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.2547210826894997</v>
+        <v>-0.2605108914728547</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.08810248506243568</v>
+        <v>-0.09407948094079899</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.240472670813233</v>
+        <v>-0.246267543768532</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.006061</t>
+          <t>X &lt; 0.006059</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3196</v>
+        <v>3200</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3179995909589977</v>
+        <v>-0.3199284293847882</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.07836238952094732</v>
+        <v>0.07591287803504088</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1318332053767861</v>
+        <v>-0.1341398552227062</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.07360121523382901</v>
+        <v>0.07097990697654666</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.180829617732698</v>
+        <v>-0.1851966510625829</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.03837486128831813</v>
+        <v>-0.04290650139611074</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.1091520704834323</v>
+        <v>0.104371342936588</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1598477874912589</v>
+        <v>0.1549784802343694</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.06108095607341113</v>
+        <v>-0.06567479837501367</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1801318474376714</v>
+        <v>0.1751718721229025</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.09860107959056563</v>
+        <v>0.09376208145842213</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.03769616725649882</v>
+        <v>-0.04239102416061513</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1347844403518437</v>
+        <v>0.1297800269354781</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1815676125587302</v>
+        <v>0.1764838372276074</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.0718426114338655</v>
+        <v>0.06683880162687217</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.123726261588935</v>
+        <v>0.1187034044845134</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.02085329800509328</v>
+        <v>0.03456430879654704</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.06548738328678638</v>
+        <v>-0.05166853904476909</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.01308897538863363</v>
+        <v>0.02678738191433894</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.09375</v>
+        <v>0.1073326457729422</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.100555452208674</v>
+        <v>0.09553889741352606</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.1442492732709582</v>
+        <v>-0.1489692118141264</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.0384294066976878</v>
+        <v>-0.04326202806148416</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.189564440931278</v>
+        <v>-0.1942172897196244</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006863</t>
+          <t>X &lt; 0.006861</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3239</v>
+        <v>3243</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2855902803291528</v>
+        <v>-0.2870951991899986</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.02156685904542854</v>
+        <v>-0.0234180294288393</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2173312292189138</v>
+        <v>-0.2190367701906411</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.03733207703398733</v>
+        <v>0.03526690693025358</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1264639214457759</v>
+        <v>-0.1299740826709268</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1676771964730079</v>
+        <v>-0.1711267881778014</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.05981710731727219</v>
+        <v>0.05603600215048488</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.07541537486235228</v>
+        <v>0.07159478635773553</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.08058847034492089</v>
+        <v>-0.08421702583817847</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08569611030997493</v>
+        <v>0.08181074935001931</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.03960331101599479</v>
+        <v>0.03579015207686354</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.006293706293703849</v>
+        <v>-0.01007088615927643</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1182526489104632</v>
+        <v>0.1142467976039114</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1614808484970354</v>
+        <v>0.1574050393969344</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1060718452181035</v>
+        <v>0.1020188459792379</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.1035472434972533</v>
+        <v>0.09953379953380193</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.03106784386466188</v>
+        <v>0.04550870034309895</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1171500093997011</v>
+        <v>-0.1025434804463572</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.005940219788122647</v>
+        <v>0.008514488506925488</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.04528985507246119</v>
+        <v>0.05965514687855489</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.0169049123909204</v>
+        <v>-0.02078381221502212</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2286509907127652</v>
+        <v>-0.2322761588397242</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.1206148660596682</v>
+        <v>-0.124357601231246</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.270777024892169</v>
+        <v>-0.2743417886403776</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.007665</t>
+          <t>X &lt; 0.007663</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3268</v>
+        <v>3271</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2394709498237475</v>
+        <v>-0.2548768735291418</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.01928319514151866</v>
+        <v>0.003719952130730064</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1874402068656877</v>
+        <v>-0.1720750483241602</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.09342653582470462</v>
+        <v>-0.1083598981886453</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1677439884805665</v>
+        <v>-0.1838833482117224</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1156295074390101</v>
+        <v>-0.1318689552698871</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.01875591161172707</v>
+        <v>-0.0348965706140163</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.005779943030326251</v>
+        <v>-0.02186867471584009</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.129594000888801</v>
+        <v>-0.1455858420490443</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.03259088481234329</v>
+        <v>-0.04848370189449724</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.01491087223718779</v>
+        <v>-0.03089420100958051</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.001892739770141816</v>
+        <v>-0.01782396519910634</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.08109849381398249</v>
+        <v>0.09584538388063635</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1830053264603322</v>
+        <v>0.1672301376479126</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.1222603584808297</v>
+        <v>0.1066998839013635</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.1250322890965379</v>
+        <v>0.1093146227374504</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.0825416483827226</v>
+        <v>0.08512559427155253</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.06527752666465148</v>
+        <v>-0.06254516458597692</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.0142283357976396</v>
+        <v>-0.01164739903695278</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.007640586797066362</v>
+        <v>0.01010400532036471</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.002313195404369139</v>
+        <v>-0.01319964584664035</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2388037826833695</v>
+        <v>-0.2540822512698782</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.09870119139795719</v>
+        <v>-0.1141827137579554</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2787977696178459</v>
+        <v>-0.2941007351491578</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.008468</t>
+          <t>X &lt; 0.008465</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3295</v>
+        <v>3299</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1317638537459658</v>
+        <v>-0.1328675891922799</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06187316404395915</v>
+        <v>0.06052066653146682</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1850456499412871</v>
+        <v>-0.1861648047416651</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.0976126650853999</v>
+        <v>-0.09886943354062083</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.17430255936614</v>
+        <v>-0.1765870307346518</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.1210891064066502</v>
+        <v>-0.123430916886349</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.0917142820235668</v>
+        <v>-0.09412711499998494</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.02071543880505544</v>
+        <v>-0.02322774417200435</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1129643779503056</v>
+        <v>-0.1153649650187987</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.08352353835567783</v>
+        <v>-0.08599539671699574</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06376326959091472</v>
+        <v>-0.06624834456028594</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.05314558399857106</v>
+        <v>-0.05565735468417898</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.01996568618156402</v>
+        <v>0.0173141663400429</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1192123338439544</v>
+        <v>0.1164294180324958</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.1141092604114746</v>
+        <v>0.1113016541719531</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.1217217810075226</v>
+        <v>0.1189297695649856</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.07848211472050082</v>
+        <v>0.09381403250861098</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.0386940715483064</v>
+        <v>-0.02322478628254743</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.04689228046892424</v>
+        <v>-0.03146745621373981</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.05399363443467564</v>
+        <v>-0.03860677768927445</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.09406456909498218</v>
+        <v>-0.09659813039183263</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2428664139884518</v>
+        <v>-0.2452245626712184</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1926812690322137</v>
+        <v>-0.1950895819508887</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2809058559397926</v>
+        <v>-0.2832120608623896</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.00927</t>
+          <t>X &lt; 0.009266</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3315</v>
+        <v>3319</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.123027608927309</v>
+        <v>-0.1239360089722226</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1273937270868899</v>
+        <v>0.1261724954038499</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2166135763853063</v>
+        <v>-0.2174764438915417</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1040024553228847</v>
+        <v>-0.1050271779786982</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1824259192421138</v>
+        <v>-0.1842933563089275</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.06838686609023625</v>
+        <v>-0.0703852954823887</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.01622899194988747</v>
+        <v>0.01409931477155624</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.05513080018318561</v>
+        <v>0.05294289979214284</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.06633077148764954</v>
+        <v>-0.06837264127690901</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.01165522378028783</v>
+        <v>-0.0137926025558599</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0203999600405993</v>
+        <v>-0.0225179446968653</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.01855480658849018</v>
+        <v>0.01637842732138495</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.114559204773812</v>
+        <v>0.1122244944628861</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.09156834471798447</v>
+        <v>0.08925171363291184</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.05242849508892533</v>
+        <v>0.05013312068345499</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.09366150629761449</v>
+        <v>0.09133730570891885</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.04987485609811415</v>
+        <v>0.06555882565638171</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.03712510368924882</v>
+        <v>-0.02133086344387891</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.04397150646379799</v>
+        <v>-0.02822397726915682</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.01977252184393308</v>
+        <v>-0.00409209281217926</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.06286587011911138</v>
+        <v>-0.06500069304792788</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.1509236286441862</v>
+        <v>-0.1529564818901719</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1295129881463666</v>
+        <v>-0.1315627473397143</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2176444126908521</v>
+        <v>-0.2195920260859978</v>
       </c>
     </row>
     <row r="33">
@@ -8042,79 +8042,79 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3328</v>
+        <v>3332</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1218825997806405</v>
+        <v>-0.1226598743144933</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.006827295788816912</v>
+        <v>0.005885184549867972</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2817333462494815</v>
+        <v>-0.2823780443449877</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2321065028731013</v>
+        <v>-0.2328339244512776</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2519098550834045</v>
+        <v>-0.2534322289221933</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1675027456259031</v>
+        <v>-0.1691208785298315</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.003462878637073175</v>
+        <v>0.001614517743547594</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.07103961956193672</v>
+        <v>0.06910040925230021</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.01986102509022913</v>
+        <v>-0.02169134433670195</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>0.001673495166137684</v>
+        <v>-0.0002086936559777541</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.005965348650221358</v>
+        <v>-0.007830630083816459</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.03175545628376142</v>
+        <v>0.02983489904887193</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1230105308120955</v>
+        <v>0.1209431896283633</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.06928238995413949</v>
+        <v>0.06727101923003431</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.02772060566770307</v>
+        <v>0.02573646764147242</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.07110505424068236</v>
+        <v>0.06908709738898722</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.02696638258051109</v>
+        <v>0.04288080045557763</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.03011656863023404</v>
+        <v>-0.01411858034878577</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.03609120036090729</v>
+        <v>-0.02014136722117854</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.0412665066026463</v>
+        <v>-0.02535779951331563</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.08631809137562385</v>
+        <v>-0.08814384753931392</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1743356448207436</v>
+        <v>-0.1760593590563886</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1819816799547738</v>
+        <v>-0.1836884418368783</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2099850989653618</v>
+        <v>-0.2116617675107406</v>
       </c>
     </row>
     <row r="34">
@@ -8124,161 +8124,161 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3338</v>
+        <v>3342</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1483850177710266</v>
+        <v>-0.1490194759876857</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.008560222462016043</v>
+        <v>0.007729239228922324</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2242281079108537</v>
+        <v>-0.2248234544196706</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2068645511586311</v>
+        <v>-0.2075012039318977</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.168215382906979</v>
+        <v>-0.1696174438768665</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.1132439030647419</v>
+        <v>-0.114706980991123</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.0248371040665134</v>
+        <v>0.02318676271177367</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.06146987628969924</v>
+        <v>0.05976702633073927</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.0289992103358756</v>
+        <v>-0.03059406449162339</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.01007752045735799</v>
+        <v>-0.01171787516788214</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.01679418337111116</v>
+        <v>-0.01841969589290215</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.01988310197265974</v>
+        <v>0.01820494077580292</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.07728177710490769</v>
+        <v>0.07550213565291841</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.05285780466820711</v>
+        <v>0.05109997873296379</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.03913961506728469</v>
+        <v>0.03737835843463699</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.08434111403504829</v>
+        <v>0.08254183627317957</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.05775816157891001</v>
+        <v>0.05598577388692405</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>0.0005411754190447482</v>
+        <v>-0.001166877401232114</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.004759918863030066</v>
+        <v>-0.006456468113277936</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.009350688210652436</v>
+        <v>-0.01103740442096779</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.05588373734276075</v>
+        <v>-0.05753135109695506</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1438560634429606</v>
+        <v>-0.1454016150071098</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.150647144519624</v>
+        <v>-0.1521776628798364</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1787847890146779</v>
+        <v>-0.1802847642857515</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01168</t>
+          <t>X &lt; 0.01167</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3350</v>
+        <v>3354</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04233960913057899</v>
+        <v>-0.04297918331648276</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.08322976999634335</v>
+        <v>0.08243296025613489</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1538327449084349</v>
+        <v>-0.1543837015535061</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.168725415775306</v>
+        <v>-0.1692762926443692</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1018212425678584</v>
+        <v>-0.1030634089249318</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.0760502639909717</v>
+        <v>-0.07731925009805707</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02909514111143352</v>
+        <v>0.02768196278305624</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.06460551554025074</v>
+        <v>0.06314264025947125</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.004325717906951354</v>
+        <v>0.002934578492258311</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.009297110728063274</v>
+        <v>-0.01069159968439237</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01501059446545128</v>
+        <v>-0.01639248075093036</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.05028433791075315</v>
+        <v>0.04881728328965096</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1034722788902229</v>
+        <v>0.1019139138879339</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.07835276967930582</v>
+        <v>0.0768180266302565</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.06233715178774446</v>
+        <v>0.06080460077752292</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.1095105090475172</v>
+        <v>0.1079353919924984</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.08255074410841701</v>
+        <v>0.08100356663707231</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.05496772559554586</v>
+        <v>0.05344995140913511</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.0206685739771828</v>
+        <v>0.01919602264663212</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.04658616577221153</v>
+        <v>0.04508643042650817</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.001707715887306449</v>
+        <v>-0.003163996088808574</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.119453793996172</v>
+        <v>-0.1207724426613623</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09538746019961764</v>
+        <v>-0.09672892621319562</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.09382910011347434</v>
+        <v>-0.09517510128790008</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/nasdaq_hourly_24hrs/roc/roc_1.xlsx
+++ b/workspaces/nasdaq_hourly_24hrs/roc/roc_1.xlsx
@@ -618,2379 +618,2379 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.01118</t>
+          <t>X ≈ -0.01112</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.902114124438292</v>
+        <v>8.896657309032186</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>1.57059173514574</v>
+        <v>8.655764438407886</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-10.90335489497062</v>
+        <v>-5.011252157100706</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-0.5669320738858019</v>
+        <v>-5.601599782610947</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-0.9014206666333351</v>
+        <v>-5.877437536752424</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>10.33922616475456</v>
+        <v>6.710310830564858</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-12.53886339323879</v>
+        <v>-18.95340629078873</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>9.296849854902362</v>
+        <v>5.619255347713178</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>9.340768094102174</v>
+        <v>5.74812310396009</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>8.57403789918736</v>
+        <v>4.957252094845202</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>8.849779397136636</v>
+        <v>5.230095081365192</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>8.574435597647877</v>
+        <v>4.955820471711505</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>7.457467937909179</v>
+        <v>3.84598536838481</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>7.238735932454446</v>
+        <v>3.599100795792374</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>6.584587378873699</v>
+        <v>2.9199030512302</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>18.26420180230923</v>
+        <v>15.95121319102495</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>18.13591915708564</v>
+        <v>15.85218071348701</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>18.03698989976712</v>
+        <v>15.72453980495925</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>18.25802215729519</v>
+        <v>15.94342377453962</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>18.45003670394826</v>
+        <v>16.16242405828551</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>6.812276224699325</v>
+        <v>3.111344976399721</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>6.738499702414906</v>
+        <v>3.037158000306484</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>7.014918719801059</v>
+        <v>3.281626526917925</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.941199376949577</v>
+        <v>3.120469701362715</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.01038</t>
+          <t>X ≈ -0.01032</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-3.617087062328984</v>
+        <v>-0.2080091012166889</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>10.24600899461139</v>
+        <v>6.171671709369562</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>8.819982072337048</v>
+        <v>4.9267618940587</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>1.011397798974571</v>
+        <v>-2.287787626998387</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>7.781866899689604</v>
+        <v>4.066479552983765</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.8634035980876718</v>
+        <v>-2.407679583427395</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>14.30872828777255</v>
+        <v>10.0668704172288</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>21.14441534238247</v>
+        <v>16.40098899172204</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>21.19189004403007</v>
+        <v>16.53306248302908</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>13.31577353352301</v>
+        <v>9.106464974619314</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>13.59294415503056</v>
+        <v>9.380544064535925</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>13.31904218976655</v>
+        <v>9.10751790094902</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>19.32289028772148</v>
+        <v>14.64383094836975</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>19.10772482935528</v>
+        <v>14.40016446904594</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>18.45715630211266</v>
+        <v>13.72419771923298</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>19.05564947515991</v>
+        <v>14.28825077767803</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>18.9276426732918</v>
+        <v>14.18875683080386</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>25.95900930775842</v>
+        <v>27.3701877767749</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>26.1824509927914</v>
+        <v>27.59256798089038</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>26.37687660352555</v>
+        <v>27.81506652676931</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>18.70628694542616</v>
+        <v>20.59569154866057</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>18.63609218912794</v>
+        <v>20.52671958123093</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>18.91609425827262</v>
+        <v>20.77640525460827</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>18.84596128170732</v>
+        <v>20.62046970136424</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.009578</t>
+          <t>X ≈ -0.009517</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-27.14482481105204</v>
+        <v>-23.38151169692778</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-17.02537414193409</v>
+        <v>-13.69767378227144</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-2.764737195973481</v>
+        <v>-0.04226384057042765</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>6.992087802237329</v>
+        <v>9.309482460926006</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>1.425014168239258</v>
+        <v>4.0662465072215</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.624884007565697</v>
+        <v>-0.7498219081482773</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.8432671465619137</v>
+        <v>3.433487533071123</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.671766410400302</v>
+        <v>-1.845623878679149</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.631989603468519</v>
+        <v>-1.718953835887646</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-5.402674646340827</v>
+        <v>-7.490924428834219</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-10.37368739558718</v>
+        <v>-12.20236888932894</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-15.89891229960379</v>
+        <v>-12.48180630486193</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-17.02323105455405</v>
+        <v>-13.59685721742395</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-1.507317567013189</v>
+        <v>1.106238389113813</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-17.91071312338433</v>
+        <v>-14.53326824077353</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-12.07265062118315</v>
+        <v>-8.989604428379408</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-17.4620355448284</v>
+        <v>-14.08554491294088</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-7.0643569566206</v>
+        <v>-4.240123128386237</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-6.850792970869378</v>
+        <v>-4.027124116394916</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-6.666250721771341</v>
+        <v>-3.814012443403165</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-12.46865903721814</v>
+        <v>-9.377539602162244</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-7.288219208582078</v>
+        <v>-4.458425432861866</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-7.015984764248827</v>
+        <v>-4.216165824660102</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-7.093888342350006</v>
+        <v>-4.379530298639558</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.008776</t>
+          <t>X ≈ -0.008717</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-6.537371938989764</v>
+        <v>-12.2801975191562</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>4.818058838483317</v>
+        <v>5.002874840531355</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-2.456818860041103</v>
+        <v>-2.088128114022446</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>2.682139183893362</v>
+        <v>3.169410484974719</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>8.199085241186708</v>
+        <v>8.745084602516215</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>20.09200615610169</v>
+        <v>20.60496699078494</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>19.32375570711822</v>
+        <v>19.81992718843421</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>7.344448723089485</v>
+        <v>7.813775361616379</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>7.387836113420136</v>
+        <v>7.943329539172488</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>6.620806698492956</v>
+        <v>13.01115496530888</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>6.896104913446983</v>
+        <v>13.28653306225277</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>18.34237619074082</v>
+        <v>18.87587351720337</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>23.09118563108694</v>
+        <v>23.63315629740747</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>17.0123878457546</v>
+        <v>17.52729221416453</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>16.36155414714258</v>
+        <v>16.85261847296295</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>16.95936316353611</v>
+        <v>17.41754903191898</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>16.83085540571982</v>
+        <v>17.31911258668431</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>10.85980718617883</v>
+        <v>11.32005630764219</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>11.07877570931402</v>
+        <v>11.53772159723445</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>17.14394884769212</v>
+        <v>17.63077226419867</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>16.60716565122627</v>
+        <v>17.06922936511805</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>10.65759478057249</v>
+        <v>11.12044833794888</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>16.81581662510426</v>
+        <v>17.24796707906156</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>16.74512094557316</v>
+        <v>17.09105793665817</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.007974</t>
+          <t>X ≈ -0.007916</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-6.536912031101735</v>
+        <v>1.036141592548567</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-1.027168458670872</v>
+        <v>0.7824690963256131</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.4566575931606</v>
+        <v>-0.5234121058513779</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.16647763373463</v>
+        <v>-1.13913846272952</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-15.20232546699345</v>
+        <v>-15.63270700339763</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.534902591180305</v>
+        <v>1.380906251145404</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-4.085322843883851</v>
+        <v>-4.147296634117041</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>7.344078775905103</v>
+        <v>5.025748671956094</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.387485667491418</v>
+        <v>5.154479701410487</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>18.33520583369987</v>
+        <v>13.84731008506671</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>18.614075285166</v>
+        <v>14.12297688057001</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>6.619880897636477</v>
+        <v>4.362088999635652</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>5.502334484431294</v>
+        <v>3.252074864115123</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>5.282911585104486</v>
+        <v>3.004897214665469</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>10.49483772353936</v>
+        <v>7.074858037694817</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>11.09089731334127</v>
+        <v>7.636871818463121</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.7789844965737913</v>
+        <v>-1.968094229215197</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.8836173740464375</v>
+        <v>-2.101136185099229</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>5.205203917782363</v>
+        <v>2.867195526017866</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>5.393360383374329</v>
+        <v>3.082349814773856</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>10.73003259418693</v>
+        <v>7.274042018251961</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>10.65752710425721</v>
+        <v>7.201179259730758</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>16.81576338013329</v>
+        <v>12.20741882371349</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>10.86276800439803</v>
+        <v>7.287136368030467</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.007172</t>
+          <t>X ≈ -0.007116</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>34</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>6.499044269785337</v>
+        <v>2.325251400866094</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>14.93039192626598</v>
+        <v>7.925995600355307</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>16.38650846041653</v>
+        <v>6.68130537934934</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>15.66229928565954</v>
+        <v>11.9424380955458</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>12.39772131009262</v>
+        <v>8.747197516851514</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>14.23808993176586</v>
+        <v>11.82735147422057</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7.618397263619123</v>
+        <v>8.114107727277641</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>10.27025795891392</v>
+        <v>7.812785702020605</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>10.31459248374637</v>
+        <v>5.014662652795167</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>9.548354057296905</v>
+        <v>4.223742254119706</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.036279833906462</v>
+        <v>-4.291986338185282</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>6.619500365843706</v>
+        <v>1.291878714583682</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>8.433281859541388</v>
+        <v>6.043598154436175</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>2.350504154712574</v>
+        <v>-0.06708943119102884</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-4.170830141524227</v>
+        <v>-6.613211523024397</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-9.447139336206043</v>
+        <v>-11.92333674553164</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-6.648658292392177</v>
+        <v>-9.09559976416346</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-3.819345130985248</v>
+        <v>-6.295046542253878</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-3.604878176513083</v>
+        <v>-6.08275249598703</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-3.419412766216468</v>
+        <v>-5.870328148040421</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-3.962422799847069</v>
+        <v>-6.438954425640063</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>1.839328933126573</v>
+        <v>2.302146050492304</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-3.766210806608512</v>
+        <v>-9.214650858562834</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-3.843114348543821</v>
+        <v>-6.438353828049713</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.00637</t>
+          <t>X ≈ -0.006314</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-6.016172676644025</v>
+        <v>-3.517520321749615</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-13.29084885496825</v>
+        <v>-6.021662149714878</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-17.07110473217384</v>
+        <v>-9.52911138459902</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-10.86179554526786</v>
+        <v>-7.862124205629378</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-6.579349811022269</v>
+        <v>-1.357875657431016</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-11.01429408419392</v>
+        <v>-7.983243760255291</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4.396848920878973</v>
+        <v>4.788396966976727</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-2.827329154293942</v>
+        <v>-0.03683949907028961</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-5.100707395206236</v>
+        <v>0.09050966739344801</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-10.52307134448424</v>
+        <v>-5.227581195025316</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-10.25017713698954</v>
+        <v>-4.95733701944787</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-8.218471161471449</v>
+        <v>-2.970426172888004</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-7.047126731040244</v>
+        <v>-4.082726624822506</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-8.218601862916884</v>
+        <v>-6.597622678555972</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-6.557839582040621</v>
+        <v>-5.012980605785756</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-3.647134349431788</v>
+        <v>-2.187482807511607</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-6.102325667743429</v>
+        <v>-4.559549268126929</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-1.56622267185675</v>
+        <v>-0.156483326744393</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-5.994998565592077</v>
+        <v>-4.480742858864041</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-8.132991682764931</v>
+        <v>-6.53778041747681</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-11.00088812028978</v>
+        <v>-9.377253598156308</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-8.755998780906872</v>
+        <v>-9.455291978253157</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-15.45883981010128</v>
+        <v>-11.48660593189851</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-13.21383938274236</v>
+        <v>-11.65225757136456</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.005568</t>
+          <t>X ≈ -0.005514</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>15.13716562708782</v>
+        <v>14.53987163665837</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>19.53366902780714</v>
+        <v>18.81516034228875</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>15.66897013042068</v>
+        <v>15.31603485413064</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7167402866493759</v>
+        <v>1.175980009030049</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3683665744273341</v>
+        <v>0.9022560611598678</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7.678709508509172</v>
+        <v>10.09728291166592</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4.50958690290242</v>
+        <v>4.787682849573834</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>6.592510420999666</v>
+        <v>9.008465762883574</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.477759287450823</v>
+        <v>2.352513053210927</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.662545578387316</v>
+        <v>-0.70147256305318</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-8.131783684915682</v>
+        <v>-4.956782737230391</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-10.79506909918678</v>
+        <v>-9.762636042524498</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-11.96865200140309</v>
+        <v>-10.87699680309154</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-7.442651473235912</v>
+        <v>-6.597083831008767</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-1.012102387216046</v>
+        <v>-0.479999293202404</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-2.765437773068435</v>
+        <v>-2.187343514379201</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-2.908191006486298</v>
+        <v>-2.291556782694556</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-3.019102398377349</v>
+        <v>-2.42492170746636</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-9.933811129108207</v>
+        <v>-9.018862071064191</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-9.739251600411372</v>
+        <v>-8.807429022765668</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-12.69396205080557</v>
+        <v>-13.9181788753453</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-12.77174068649727</v>
+        <v>-11.7264296916648</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-8.687739194799782</v>
+        <v>-11.48650860419883</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-7.344514908766698</v>
+        <v>-11.65225757136456</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004766</t>
+          <t>X ≈ -0.004712</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.7181820528568679</v>
+        <v>0.4019420670784228</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>7.989430376847459</v>
+        <v>6.691572198449279</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1917283748033469</v>
+        <v>0.2183933023463993</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.5950674185745157</v>
+        <v>2.245721954437727</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>4.782589146003424</v>
+        <v>4.588793965151787</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4.973677834660911</v>
+        <v>4.743376422237219</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.68570280222751</v>
+        <v>3.953905406789822</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>8.442946556435132</v>
+        <v>8.887676685856135</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>6.976887714451834</v>
+        <v>6.399443157762441</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>6.19520161836472</v>
+        <v>5.609834003587267</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>3.450300656567137</v>
+        <v>3.263123092854244</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>1.658753370488874</v>
+        <v>2.98845767748336</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>1.417698377210023</v>
+        <v>1.878217449566691</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-1.825868434683649</v>
+        <v>0.3191735536889553</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>2.052254408196497</v>
+        <v>3.575251782571243</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-4.91494458780911</v>
+        <v>-1.113360466479307</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-3.537416790356289</v>
+        <v>-1.21724081777618</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-2.130032368358798</v>
+        <v>-0.03703144414023285</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-3.428533363634244</v>
+        <v>-1.136295495511526</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.2146339455359367</v>
+        <v>0.3916492311347426</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.27171884617411</v>
+        <v>-0.1749933945154254</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.6819508570822066</v>
+        <v>2.379582831130833</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>5.501880115018807</v>
+        <v>7.885370602654568</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>5.426047861795176</v>
+        <v>9.041522332941362</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.003965</t>
+          <t>X ≈ -0.003912</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>7.704409403160227</v>
+        <v>6.410333120077524</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>1.461130641025072</v>
+        <v>-0.7851013172529804</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.957581364780957</v>
+        <v>3.93039031281031</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>8.191909444129365</v>
+        <v>6.324359610650959</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.9590098619340779</v>
+        <v>-0.9060869778051526</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>6.07339147140695</v>
+        <v>3.224493556108683</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>7.276139292568693</v>
+        <v>3.429209759682529</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.014763989664488</v>
+        <v>2.13145823003309</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.099291652121266</v>
+        <v>0.2703190451332915</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.343892744692354</v>
+        <v>-0.5209480154756037</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.6313799147811565</v>
+        <v>-3.235787115779686</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>2.328368580367602</v>
+        <v>-0.5244550550044025</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.170421324640841</v>
+        <v>1.353446185459539</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>2.962054697319793</v>
+        <v>-0.8874174921326627</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>2.306413541849928</v>
+        <v>-0.5708247647111406</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>4.876925757414739</v>
+        <v>2.981133314172176</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>4.744888640429437</v>
+        <v>3.876286397477472</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>1.675411568821929</v>
+        <v>0.7508606298616769</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.880964993314898</v>
+        <v>1.963914702991943</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>2.079072604576091</v>
+        <v>2.178712472864945</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>3.516970068446334</v>
+        <v>3.610713482580593</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>6.41252391438794</v>
+        <v>5.535285232573308</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>4.706800607068004</v>
+        <v>3.781329125759548</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>4.630968353844729</v>
+        <v>2.62046970136295</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.003163</t>
+          <t>X ≈ -0.003111</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.345251484549593</v>
+        <v>0.7100224618199604</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-3.237898720364832</v>
+        <v>-0.9929318368534865</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.02757112769747039</v>
+        <v>-0.1122866879316149</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.7482629106030672</v>
+        <v>-0.3192194388053338</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>2.80176635016165</v>
+        <v>1.978660722844729</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.438848378693045</v>
+        <v>1.418809677362262</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.1191735790828403</v>
+        <v>-1.567404435597886</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.956133735651122</v>
+        <v>-2.919273032010068</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.6959594619436373</v>
+        <v>-2.066363075244723</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.8627132305721901</v>
+        <v>-2.146618432925592</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.4212644292568868</v>
+        <v>-2.603462855231768</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.7011951562301064</v>
+        <v>-1.735793123498738</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.067017624892877</v>
+        <v>2.236535185222223</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.2867116354031154</v>
+        <v>0.9603425676726332</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-2.713831638505035</v>
+        <v>-2.629945079199402</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>0.2226693627794631</v>
+        <v>-0.6153291321274992</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>2.428394430270885</v>
+        <v>1.465368656841228</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>2.32319607635705</v>
+        <v>0.6050424754755497</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>4.101669552941601</v>
+        <v>2.276981319839216</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>3.511032365397348</v>
+        <v>1.762997532038547</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>1.402101526391718</v>
+        <v>-0.2614235589755154</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>2.575890251021598</v>
+        <v>1.122005410007887</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>4.41286496350348</v>
+        <v>2.095680754379536</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>1.212032710280376</v>
+        <v>-0.255442707396405</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002361</t>
+          <t>X ≈ -0.002311</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3.247508237947237</v>
+        <v>3.972453577939227</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.7159607256656102</v>
+        <v>0.952929511087774</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-7.312733861948765</v>
+        <v>-4.738300041640329</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-7.475131651518971</v>
+        <v>-6.438716821689553</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.362650766236477</v>
+        <v>-7.823449016196236</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-5.976888818432904</v>
+        <v>-5.447394319272689</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-10.59747516776448</v>
+        <v>-9.018486399374702</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-9.777686686758059</v>
+        <v>-8.766564645975372</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-8.634812288547273</v>
+        <v>-7.529499350100672</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-8.856921978025468</v>
+        <v>-6.655121813007867</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.83146300180038</v>
+        <v>-2.490018918410122</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-5.00982644430357</v>
+        <v>-2.209796378933703</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-6.13072418014395</v>
+        <v>-4.435685214895656</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-6.351350190387492</v>
+        <v>-5.23972824219382</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-5.907499288271673</v>
+        <v>-5.921013587053615</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-6.970898293531135</v>
+        <v>-6.477899703188619</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-8.210579305610999</v>
+        <v>-7.698486117547382</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-5.558807081920314</v>
+        <v>-4.489153826090053</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-8.105377107918031</v>
+        <v>-8.179868458657957</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-5.71249017304828</v>
+        <v>-5.737433646612821</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-5.152131190884091</v>
+        <v>-4.073944133556331</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-5.227977152293313</v>
+        <v>-4.709093369705904</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-6.058474815501746</v>
+        <v>-4.467232213932405</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-5.029334693034535</v>
+        <v>-4.072267728804881</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001559</t>
+          <t>X ≈ -0.001509</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>265</v>
+        <v>284</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.509630506441404</v>
+        <v>-3.544980952879285</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.891525747798845</v>
+        <v>-3.604167480641017</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>4.188183291848091</v>
+        <v>1.445003772267164</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>3.104907624375365</v>
+        <v>0.8541368499191933</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>2.020566129282365</v>
+        <v>0.5796022274603132</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.176511635301146</v>
+        <v>-1.015518785717994</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.6857947804725626</v>
+        <v>-0.05772819676813867</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.160134829137341</v>
+        <v>0.3381310744978592</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1.953537518609075</v>
+        <v>0.4661668065450115</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3.06484044652467</v>
+        <v>1.976404783861412</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.963744431341993</v>
+        <v>1.547903514295747</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.076317443614215</v>
+        <v>-2.934405862898792</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.3154506143148268</v>
+        <v>-1.592143000235836</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-1.664802340844808</v>
+        <v>-2.891251116453979</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-0.4396809034894318</v>
+        <v>-0.4142243226091153</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-2.859485614215295</v>
+        <v>-3.013866844570323</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-3.371202783101538</v>
+        <v>-4.172092665749538</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-2.346839862736424</v>
+        <v>-3.604293382433795</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.1303406080407612</v>
+        <v>-0.2286887412585941</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-1.946335591535856</v>
+        <v>-2.475856060565583</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.1517362124306061</v>
+        <v>-0.9335309275384844</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-1.433543711242557</v>
+        <v>-1.713073072317862</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-2.291144470458612</v>
+        <v>-3.230135491777517</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-1.234901251983779</v>
+        <v>-2.337276777510525</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.000757</t>
+          <t>X ≈ -0.0007085</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.386145647175184</v>
+        <v>-1.424861829709108</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3947084083029395</v>
+        <v>0.7081116986838794</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-2.628376121268651</v>
+        <v>-0.8099347397157857</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-2.281453987234578</v>
+        <v>-0.8731043374023102</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-3.680798223083116</v>
+        <v>-1.941527048681451</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.900465041515169</v>
+        <v>-1.784972031338192</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-3.204209371243579</v>
+        <v>-2.051720773476205</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-2.156011831563205</v>
+        <v>-0.7695117868368868</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-2.645778710727036</v>
+        <v>-0.6419480688890289</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-1.029816714659532</v>
+        <v>0.678884029527417</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-2.085656562777274</v>
+        <v>-1.166831519260867</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.146350459408161</v>
+        <v>0.1447601049721641</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>1.719001069671272</v>
+        <v>2.472379634784239</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.3631926936042973</v>
+        <v>0.8990320612668441</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.04223178661394655</v>
+        <v>1.169751365750663</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>1.701297942294239</v>
+        <v>2.791299659515943</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.929177327841991</v>
+        <v>2.158204358538896</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-0.5070524238888439</v>
+        <v>0.9648051387530359</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.839442321669353</v>
+        <v>2.77220285314722</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>2.293378745245477</v>
+        <v>3.253701158244226</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>1.092540214498626</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.6092235843548721</v>
+        <v>1.283882040297513</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>1.683698296836923</v>
+        <v>2.592227489978484</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>1.607866043613704</v>
+        <v>2.588554807745759</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ 4.485e-05</t>
+          <t>X ≈ 9.245e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>2.903582359445025</v>
+        <v>3.697842189617674</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>2.9842595569324</v>
+        <v>3.244443826830867</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>2.171860703886537</v>
+        <v>1.365554665948565</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2.615472343856297</v>
+        <v>2.428759718492287</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8293967625628866</v>
+        <v>0.07830511519864558</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>3.298789676942349</v>
+        <v>3.139170215553733</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>2.322505231448815</v>
+        <v>2.666123196839798</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.382384532332928</v>
+        <v>0.08151273043713303</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2.918166801295236</v>
+        <v>2.60736531606792</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.939970768685967</v>
+        <v>1.397394113894251</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>1.71214409869846</v>
+        <v>1.582798911788082</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>3.930722642288366</v>
+        <v>3.38001924980108</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>1.560666485939265</v>
+        <v>1.852684391450858</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>2.174265901485605</v>
+        <v>2.228431445311294</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>1.102787254917416</v>
+        <v>0.7180298813081833</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>1.279604204641139</v>
+        <v>1.070978901295568</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.7300863736489376</v>
+        <v>0.8840039680974385</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>1.250677419161633</v>
+        <v>1.582409758779427</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.8406901323608196</v>
+        <v>1.172722966225969</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.1931837796579146</v>
+        <v>0.3477003612059093</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.4857654399881071</v>
+        <v>1.030008321285912</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-1.260226659207994</v>
+        <v>-1.126913803579711</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.7769836795025853</v>
+        <v>-0.2590579710144851</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-1.479120734396034</v>
+        <v>-1.046196965304006</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0008469</t>
+          <t>X ≈ 0.0008935</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.8193500895722607</v>
+        <v>-0.4259443577655375</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8863328164735833</v>
+        <v>0.481408328193524</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.1084603716550561</v>
+        <v>-0.3087647872882826</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.1443141964715835</v>
+        <v>-0.4392327269448941</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.8739206844003746</v>
+        <v>1.59415387294063</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.1624589203890636</v>
+        <v>-0.5580510092523738</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5169787737981864</v>
+        <v>0.03257288186670593</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.048286570732273</v>
+        <v>0.4203600789794066</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.4109014294179119</v>
+        <v>-0.1446124000639699</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.9011290263927663</v>
+        <v>0.906201274395336</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>2.082679535309758</v>
+        <v>1.409597166781694</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>1.123168781126836</v>
+        <v>0.6713715754680294</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.815179382005638</v>
+        <v>0.9429041823410103</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.004511748495026779</v>
+        <v>-0.4603407516746927</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>1.843790683274619</v>
+        <v>1.629125955009151</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>2.57481213183928</v>
+        <v>1.730128800276972</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>3.80422690959157</v>
+        <v>2.78164628974681</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>1.655794216309417</v>
+        <v>0.7055718654145835</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.5080745867677123</v>
+        <v>-0.236674311495463</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.1475264864982364</v>
+        <v>-0.7169288151585533</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.7439913377154284</v>
+        <v>-0.3589143721680372</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.6681453763063274</v>
+        <v>-0.2956236143445281</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>1.170410521590242</v>
+        <v>0.1793604357913878</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.8667878355651055</v>
+        <v>0.01722144150192406</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001649</t>
+          <t>X ≈ 0.001695</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-2.559296624812099</v>
+        <v>-4.647757067689355</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.4666537034863083</v>
+        <v>-0.858349616818991</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.5447413278042319</v>
+        <v>0.5163414717075412</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.7716310027064495</v>
+        <v>-0.3893791056244567</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.709349595424214</v>
+        <v>-1.603407905813356</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.532522379339717</v>
+        <v>-0.8163737666436646</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.1660859857286638</v>
+        <v>-0.06762584364427227</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>1.078019509528261</v>
+        <v>2.107775007626444</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5078468017833444</v>
+        <v>1.309109061074942</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3470318401896293</v>
+        <v>0.1997391873318506</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>1.839562189056039</v>
+        <v>2.951305846294382</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>2.473673959874255</v>
+        <v>3.295422746943643</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.1696009230759827</v>
+        <v>0.3196394140098207</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.5301162208406254</v>
+        <v>0.6825375438171051</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.7875243940764136</v>
+        <v>0.6200383771594815</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-1.363731463859352</v>
+        <v>-1.117585705678138</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-2.410654033882309</v>
+        <v>-2.154681157776039</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.3803989748961456</v>
+        <v>-0.4254367699903412</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.4707320404540098</v>
+        <v>-0.02674577325808514</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.6323981731837094</v>
+        <v>1.614263804017682</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-1.744288252401105</v>
+        <v>-0.8172799018736256</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-2.73756540647075</v>
+        <v>-1.203121788026216</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-2.157280296435189</v>
+        <v>-0.9619395909521842</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-3.150543742319009</v>
+        <v>-2.058658024493987</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00245</t>
+          <t>X ≈ 0.002495</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>218</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.57919235749042</v>
+        <v>2.624639937819239</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.936392088460217</v>
+        <v>-0.3620601829835266</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-2.492103984725269</v>
+        <v>-1.16266251764204</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.4749969618729466</v>
+        <v>0.0724519899205518</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>2.824088194162009</v>
+        <v>2.994256599361762</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-1.991720021371478</v>
+        <v>-2.331359913752451</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-2.781630762095212</v>
+        <v>-3.127956074279297</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-2.597424267437319</v>
+        <v>-3.889583631974453</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-7.585654572403577</v>
+        <v>-9.703389652897734</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-6.993769001249056</v>
+        <v>-9.129044505567627</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-6.718212521017698</v>
+        <v>-8.399551777297063</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-6.992471410257338</v>
+        <v>-8.218738368257199</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-4.922116205251157</v>
+        <v>-5.684301575103532</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-2.876010526726631</v>
+        <v>-4.106236213771233</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-5.552533391176816</v>
+        <v>-5.704581232013908</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-4.04043617358046</v>
+        <v>-3.76881238071811</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-5.095774496707918</v>
+        <v>-4.790672208197741</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-4.92825595993844</v>
+        <v>-4.465997628999617</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-2.607329027477903</v>
+        <v>-3.334271497858062</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-2.421127547406776</v>
+        <v>-3.576528225399962</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-1.132667457294069</v>
+        <v>-2.323264805989901</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.2910822260426258</v>
+        <v>-1.483892067079616</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-1.392754302551403</v>
+        <v>-2.336657359393691</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-3.762164537426052</v>
+        <v>-4.792374335334536</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.003252</t>
+          <t>X ≈ 0.003295</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-6.063630162287012</v>
+        <v>-7.859013157321584</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.531789872750444</v>
+        <v>-3.783359949248819</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.313221941009282</v>
+        <v>-0.6934117269934603</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6.083996885569924</v>
+        <v>1.601858942569578</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>3.672770503081779</v>
+        <v>0.6137348886308374</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-2.424329853676127</v>
+        <v>-4.28574380265492</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4.48320352371119</v>
+        <v>2.862463410065118</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>2.110303231339607</v>
+        <v>2.55595108525165</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2.851846527442873</v>
+        <v>4.132094102984674</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>2.777812788106253</v>
+        <v>4.78186889370707</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.2606500009272494</v>
+        <v>1.445905719076542</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-3.507812376065324</v>
+        <v>-1.71834910376608</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-4.630583050425216</v>
+        <v>-3.562008652062708</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-3.452332483487254</v>
+        <v>-1.636920350606722</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-4.80661797029412</v>
+        <v>-3.763827334613481</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-5.60921213675833</v>
+        <v>-6.819399546667981</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-1.553751578498975</v>
+        <v>-2.582229325252847</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-1.65820088982391</v>
+        <v>-3.438089098543713</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-2.840464774795578</v>
+        <v>-3.949000007800663</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-1.957085383104982</v>
+        <v>-2.289261382574381</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.4077043470098616</v>
+        <v>0.03442658740159033</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-1.882151707020363</v>
+        <v>-0.7653736157131945</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-3.006278393139745</v>
+        <v>-2.695652173913039</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-3.082110646362942</v>
+        <v>-2.133153487043081</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.004054</t>
+          <t>X ≈ 0.004097</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5.556040957156071</v>
+        <v>5.309360250019544</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-3.484975152284512</v>
+        <v>-2.811632943324447</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.973887159010381</v>
+        <v>-3.102820947005554</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1722577186740679</v>
+        <v>1.242070132679004</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>5.65944936162748</v>
+        <v>5.883319531115554</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>3.908413142392732</v>
+        <v>5.056261298946275</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>7.977063811674405</v>
+        <v>8.209753248587319</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4.794221575931459</v>
+        <v>4.946553986074385</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>1.935145653156269</v>
+        <v>2.105173293600529</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>6.971491559099604</v>
+        <v>7.228831088890828</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>8.215569325502578</v>
+        <v>8.483482115511976</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>4.066238693123658</v>
+        <v>3.269606882547926</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>5.847707417257432</v>
+        <v>6.686491610902173</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>9.503989246908588</v>
+        <v>10.39230871249314</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>9.817219969002444</v>
+        <v>10.70072107179541</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>9.442266714421024</v>
+        <v>12.2491685810835</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>9.309705472876885</v>
+        <v>11.15951397917757</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>2.429652749134817</v>
+        <v>5.104453581349063</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>1.674170110384743</v>
+        <v>3.341205576839059</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>2.826288410577149</v>
+        <v>4.540196911791362</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>4.22940611534333</v>
+        <v>4.970572375893383</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>3.182686367526458</v>
+        <v>2.91521183413618</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>1.515413507193024</v>
+        <v>2.168747309513599</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>3.3813288267852</v>
+        <v>3.986806335026102</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.004856</t>
+          <t>X ≈ 0.004897</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-10.93971142355451</v>
+        <v>-9.958032859453155</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.1048649093327541</v>
+        <v>1.038465788943206</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-2.934815973567012</v>
+        <v>3.013070072825634</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.4035913818240289</v>
+        <v>2.414107270441875</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.99066791550942</v>
+        <v>-1.067787142917126</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-2.171400970062201</v>
+        <v>0.6950481845339169</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.94767865828149</v>
+        <v>-1.71140271879802</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.04304041999431263</v>
+        <v>-0.4082345728950969</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>1.726568620999181</v>
+        <v>1.335436963605275</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>2.582706951065909</v>
+        <v>2.142006888051135</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>4.492314105824477</v>
+        <v>4.023423925896239</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>7.486824229734395</v>
+        <v>6.967392885764966</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>7.994880671145928</v>
+        <v>5.848127032597183</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>7.778130799028375</v>
+        <v>5.604266706881084</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>7.124316505776811</v>
+        <v>4.926486060713039</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>10.98438719750197</v>
+        <v>8.700686956368003</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>9.219251552256793</v>
+        <v>8.600086846430706</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>12.38983487795798</v>
+        <v>11.68884708953844</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>10.96801424412111</v>
+        <v>10.2930338595142</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>6.24929976738126</v>
+        <v>5.681167668780091</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>10.64353949111922</v>
+        <v>9.968975442006553</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>10.56769352971012</v>
+        <v>9.893812920051225</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>12.48151250448726</v>
+        <v>10.13744740532955</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>17.32371303814919</v>
+        <v>16.42692131426589</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.005658</t>
+          <t>X ≈ 0.005699</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-7.632190027409145</v>
+        <v>-8.596543899374716</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-9.848081590505458</v>
+        <v>-12.92712031719716</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-5.500924250140066</v>
+        <v>-10.09878010646256</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-10.07975433015194</v>
+        <v>-12.73269946158383</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-9.360401203757746</v>
+        <v>-10.96183463689295</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-3.320589333932233</v>
+        <v>-6.744760491162403</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-6.051062336641145</v>
+        <v>-5.513042772513842</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-4.377242969069272</v>
+        <v>-3.786257676563842</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-4.324392150790885</v>
+        <v>-5.678587419791462</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-3.153393897619381</v>
+        <v>-4.451109723114207</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-4.829741691158922</v>
+        <v>-6.208944978376039</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-7.054028400438398</v>
+        <v>-8.510691394236382</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-8.182060597164565</v>
+        <v>-9.632124589656705</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.363508094506969</v>
+        <v>0.284710123672788</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.240172508905097</v>
+        <v>-2.422608719601236</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-0.6506557168322047</v>
+        <v>-1.866210509258792</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.7797027239395788</v>
+        <v>-1.965185112506582</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>4.981289268954399</v>
+        <v>1.973518208511109</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>5.192310520008498</v>
+        <v>6.248120975389227</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>7.327940389054802</v>
+        <v>8.491142420822115</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>10.73997150654835</v>
+        <v>10.00189183436984</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>5.845096659353395</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>3.095463002719391</v>
+        <v>4.047914818101219</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>3.019630749496059</v>
+        <v>3.885775823811699</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.00646</t>
+          <t>X ≈ 0.0065</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2.185381296472457</v>
+        <v>1.237265998210709</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-7.429924493635937</v>
+        <v>-6.139233459157218</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-6.530546101357231</v>
+        <v>-5.001528293649571</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.630366643073728</v>
+        <v>-0.8704545636246692</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>3.994239628198017</v>
+        <v>3.60935098021114</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-9.707523742798024</v>
+        <v>-8.082878155810761</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-3.548673157218218</v>
+        <v>-4.152031334971738</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-6.14208393751948</v>
+        <v>-6.827274907632081</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-1.457865803529707</v>
+        <v>0.4238879110002785</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-6.871045975445512</v>
+        <v>-5.122621459676935</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-4.27932054153969</v>
+        <v>-2.477610411582297</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.392460974048312</v>
+        <v>4.361682830178729</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-1.050833340747488</v>
+        <v>0.8691088707603853</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-1.274378673389805</v>
+        <v>0.6184219050886242</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>2.705276068713239</v>
+        <v>4.68427249442292</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.33320213663589</v>
+        <v>0.5024773505005413</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.8530129743263615</v>
+        <v>2.773825876504446</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-3.869894119612582</v>
+        <v>-2.087439965967476</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-1.34866922792299</v>
+        <v>-1.882789355776133</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-3.481955665894645</v>
+        <v>-6.411302073459275</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-8.685473089894877</v>
+        <v>-11.7668156486233</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-6.435737655955151</v>
+        <v>-9.461025789626234</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-6.161262943473162</v>
+        <v>-9.217391304347885</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-6.237095196696373</v>
+        <v>-9.379530298637285</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.007262</t>
+          <t>X ≈ 0.0073</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.511295511573742</v>
+        <v>1.653439319882409</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>3.147630546539233</v>
+        <v>4.804541155020921</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>5.290196586055693</v>
+        <v>3.582167673685248</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-16.73654998539868</v>
+        <v>-17.58980145357432</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-6.406416629851208</v>
+        <v>-7.5665981792935</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>4.428418280163058</v>
+        <v>2.871140940775774</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-10.55754013284911</v>
+        <v>-11.64844059717353</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-10.83575157760218</v>
+        <v>-11.95336104058214</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-7.228123390482551</v>
+        <v>-8.381738119252645</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-15.11165495191554</v>
+        <v>-16.04363055739213</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-7.737812486863895</v>
+        <v>-8.916328140053089</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.9131680465865344</v>
+        <v>-2.334251511727757</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.04355215511378</v>
+        <v>-6.885655280700341</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.279843848631046</v>
+        <v>-0.2860042995222614</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.6325336135573778</v>
+        <v>2.468352970114495</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>1.22330951466472</v>
+        <v>3.026065808872346</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>4.644700320385496</v>
+        <v>6.355105868607488</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>4.557914720742332</v>
+        <v>6.240177663754594</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-2.336809783729898</v>
+        <v>-0.4112010520196776</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-5.705271916460177</v>
+        <v>-0.2002057870224121</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.8660219267164067</v>
+        <v>6.131378111639478</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-2.781252606121264</v>
+        <v>2.607939727615225</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>1.064650677789359</v>
+        <v>6.299850074962528</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-2.582610146862528</v>
+        <v>2.689435218604096</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.008064</t>
+          <t>X ≈ 0.008101</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>14.14402683614789</v>
+        <v>16.74128930743949</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6.681705686724257</v>
+        <v>5.425769441338169</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-1.800197582661504</v>
+        <v>0.5434514503848717</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1.024476782583008</v>
+        <v>3.62017122135218</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.70437258454551</v>
+        <v>3.360174861520406</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.8808812543030768</v>
+        <v>3.50673394734013</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-6.987239231641503</v>
+        <v>-4.647341044800569</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1797363906803184</v>
+        <v>2.39635697152039</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>3.425522966771268</v>
+        <v>6.2193441514261</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-4.443564511319352</v>
+        <v>-1.93570032370117</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-4.174733627327278</v>
+        <v>-1.668652569186094</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-4.453483030775274</v>
+        <v>-1.94523452365739</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-9.129959756828519</v>
+        <v>-3.070501161286664</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-5.818639006757806</v>
+        <v>-3.33429700298732</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.6246182558856717</v>
+        <v>-0.3317676348292409</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>1.2137764196587</v>
+        <v>0.2243491239012201</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>1.08508804085119</v>
+        <v>0.1256559722654131</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>4.549248270736797</v>
+        <v>3.693017397414714</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-2.331032150392964</v>
+        <v>-3.451513355347501</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-5.692272241452002</v>
+        <v>-6.916423400242508</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-9.848263787569302</v>
+        <v>-11.23771511952282</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>0.7901759653073057</v>
+        <v>-0.2017665303669887</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-9.649635036496349</v>
+        <v>-11.06924315619968</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>0.9888184245661407</v>
+        <v>-0.1202710393780322</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.008866</t>
+          <t>X ≈ 0.008901</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>20</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.376295743710934</v>
+        <v>1.477588905312508</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>10.90056656440871</v>
+        <v>6.139588628458682</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-5.318404865574649</v>
+        <v>-9.898723323088511</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-1.094216027874623</v>
+        <v>-5.553269876493871</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.407149357564705</v>
+        <v>-5.806366201678536</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>8.669340638056411</v>
+        <v>4.241253238401612</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>17.802153858928</v>
+        <v>13.35183160352734</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>12.55632336655592</v>
+        <v>8.079106428163044</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>7.668286738946804</v>
+        <v>3.276666964082509</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>11.84775201529128</v>
+        <v>7.433445657542435</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>7.161811657453121</v>
+        <v>2.745363211829378</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>11.83544320638612</v>
+        <v>7.421611446037303</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>15.65704304429196</v>
+        <v>11.24457497398935</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.396416784535525</v>
+        <v>-8.837441657075431</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-9.999321986878073</v>
+        <v>-14.46493895600151</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-4.460173160173092</v>
+        <v>-8.958292020140824</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-4.586471249531542</v>
+        <v>-9.054685160227628</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.2915451895044043</v>
+        <v>-4.204789990157074</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.5074365704287302</v>
+        <v>-3.990327763011301</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>5.646663332777663</v>
+        <v>1.177088870726955</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>5.151736212430698</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>15.07589025102153</v>
+        <v>10.53897421037387</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>10.35036496350365</v>
+        <v>5.78260869565225</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>10.27453271028045</v>
+        <v>5.620469701362786</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.009668</t>
+          <t>X ≈ 0.009701</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.241140464207767</v>
+        <v>-0.004890879054030961</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-30.61123467782733</v>
+        <v>-24.70048324934897</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-16.69728685315234</v>
+        <v>-10.31052326319034</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-32.65868807756388</v>
+        <v>-27.33374307206144</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-17.74603134514236</v>
+        <v>-11.1784836020979</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-25.20916867871359</v>
+        <v>-19.04041792062814</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-3.175734339829702</v>
+        <v>5.321732771541718</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.144397900717415</v>
+        <v>13.42876201366765</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.83598860230096</v>
+        <v>21.57555884788001</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.444025307216819</v>
+        <v>12.52479037152857</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>3.718084949378742</v>
+        <v>12.7970253861329</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>3.428983579056954</v>
+        <v>12.59905978386296</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>2.285117578453438</v>
+        <v>3.386683389682588</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-5.534304983293346</v>
+        <v>-5.27350035728508</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-6.171744347126449</v>
+        <v>-6.112887443572646</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-5.598061358930913</v>
+        <v>-5.394350720350474</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-5.721626529034708</v>
+        <v>-5.576847484276769</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>1.813284319939157</v>
+        <v>2.387752687291226</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>2.029175700863483</v>
+        <v>2.602214914436999</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-5.403026108216025</v>
+        <v>-5.437915621636122</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-6.002109941415455</v>
+        <v>-1.052529934337578</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-6.077955902824392</v>
+        <v>-1.127692456292863</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-13.49578888265015</v>
+        <v>-9.217391304347935</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>1.812994248741859</v>
+        <v>7.287136368029316</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.01047</t>
+          <t>X ≈ 0.0105</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-9.401716678649315</v>
+        <v>-8.088081273565081</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.6982891316965052</v>
+        <v>0.7569209816400146</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>18.06461790875246</v>
+        <v>17.68404506156661</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>7.460359541483555</v>
+        <v>8.000733771849298</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>27.01587341676245</v>
+        <v>25.90699381356822</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>17.52892655938147</v>
+        <v>16.97301832865721</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.300456136360729</v>
+        <v>7.087027225515392</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.760364004044533</v>
+        <v>-2.308802308802321</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-3.04496377865155</v>
+        <v>-2.180873399118141</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-3.81787945468804</v>
+        <v>-2.976924894337479</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-3.543819812526117</v>
+        <v>-2.704689879733145</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-3.713873563800206</v>
+        <v>-2.981271834204513</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-14.61964432630851</v>
+        <v>-13.18707304256437</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-5.058114507102914</v>
+        <v>-4.344398013088394</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>4.066350890968714</v>
+        <v>4.064356695935643</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>4.878129117259519</v>
+        <v>4.625660714755305</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>4.635516328108139</v>
+        <v>4.521780303030368</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>4.313284319939214</v>
+        <v>4.388896197868696</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>4.52917570086354</v>
+        <v>4.60335842501447</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>4.716021510831567</v>
+        <v>4.817944870073454</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>10.1517362124307</v>
+        <v>4.25050036869272</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>10.07589025102153</v>
+        <v>4.175337846737435</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>10.35036496350358</v>
+        <v>4.418972332015812</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>10.27453271028038</v>
+        <v>4.256833337726285</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.01127</t>
+          <t>X ≈ 0.0113</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>12</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>29.6924862199013</v>
+        <v>29.79070660522274</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>21.02437608821816</v>
+        <v>21.21146643618553</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>19.58635703918723</v>
+        <v>19.95677233429401</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>10.54006968641121</v>
+        <v>11.03103680215246</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>18.53761254719716</v>
+        <v>19.08881199538639</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>10.39124539996125</v>
+        <v>10.91241226805113</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>1.285963382737577</v>
+        <v>1.783996922485095</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.007751937984438</v>
+        <v>1.479076479076475</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>9.382572453232527</v>
+        <v>9.940338722093976</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>0.2763234438627151</v>
+        <v>0.8109538935412459</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>1.08318890814558</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.604967015909963</v>
+        <v>9.139940287007605</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>7.481804949053789</v>
+        <v>8.025048169556833</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>7.776814108123723</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>6.602582775026697</v>
+        <v>7.094659726238739</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>7.196969696969632</v>
+        <v>7.65596374505833</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>7.063052559992215</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>15.29154518950432</v>
+        <v>15.75253256150512</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>7.174103237095302</v>
+        <v>7.633661455317494</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>15.69428238039667</v>
+        <v>16.18158123370988</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>15.1517362124307</v>
+        <v>15.61413673232909</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>6.742556917688255</v>
+        <v>7.205640877040459</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>15.35036496350371</v>
+        <v>15.78260869565218</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>23.60786604361372</v>
+        <v>23.95380303469606</v>
       </c>
     </row>
   </sheetData>
@@ -3180,2461 +3180,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.01158</t>
+          <t>X &gt; -0.01152</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3355</v>
+        <v>3378</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01336710158713572</v>
+        <v>0.0004488378994054187</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.08243296025613489</v>
+        <v>0.1232311420678798</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1122829651131525</v>
+        <v>0.120055652917074</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1567462325482794</v>
+        <v>0.1324690171808456</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.1044669794533633</v>
+        <v>0.1088296580298973</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.100616692962447</v>
+        <v>0.07613429396398175</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07006777182417068</v>
+        <v>0.06332927398239008</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.04611839699765596</v>
+        <v>0.04026288646205956</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.01560905066082796</v>
+        <v>0.008125341604667824</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.06112605591376763</v>
+        <v>0.05427150360413435</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.1149119854703997</v>
+        <v>0.1075671643138705</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.06125847220143044</v>
+        <v>0.05439456429375156</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.05459163948760448</v>
+        <v>0.04826052325016406</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-0.1191649625586564</v>
+        <v>-0.1236187923091663</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-0.1057010141132082</v>
+        <v>-0.1093556265809283</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-0.08819236071689573</v>
+        <v>-0.09162436283691733</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>-0.1449585445090662</v>
+        <v>-0.1485567454455961</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>0.005915912503489551</v>
+        <v>0.001941544956601149</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>0.06100799900013243</v>
+        <v>0.05656026308182049</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>0.02741724196266659</v>
+        <v>0.02250376475653582</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>-0.02098564581826423</v>
+        <v>-0.02472750901962684</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>-0.04922145585954496</v>
+        <v>-0.02315596714098689</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>-0.05487937499456308</v>
+        <v>-0.02828210044134494</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>-0.1427549201220089</v>
+        <v>-0.1136925248066163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.01078</t>
+          <t>X &gt; -0.01072</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3346</v>
+        <v>3370</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.01851932245809707</v>
+        <v>-0.02066975787776926</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.07843014227227485</v>
+        <v>0.1029758701477874</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>0.1322367990536151</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1586927671441885</v>
+        <v>0.1460810499400012</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.1071725947596391</v>
+        <v>0.1230403813409495</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.0730770978500459</v>
+        <v>0.06038550693347844</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1039830080720989</v>
+        <v>0.108472859892828</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.02123597526389887</v>
+        <v>0.0270189874442579</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.009473564817646718</v>
+        <v>-0.005500765843059696</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.03822820576748143</v>
+        <v>0.04263238053887619</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.09141712393274304</v>
+        <v>0.09540686065321324</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.03835990850476634</v>
+        <v>0.04275913187258595</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.03467953946196189</v>
+        <v>0.03924515269792295</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-0.1389560886958705</v>
+        <v>-0.1324561088387881</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>-0.1236964102688773</v>
+        <v>-0.1165467451039248</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-0.1375562422074026</v>
+        <v>-0.1297082502051268</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>-0.1941300625348674</v>
+        <v>-0.1865406919356403</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>-0.04258368877724905</v>
+        <v>-0.03538213043806593</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>0.01206205535857663</v>
+        <v>0.01884664050269436</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>-0.02213553005103819</v>
+        <v>-0.01581058608863373</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>-0.03936560900853436</v>
+        <v>-0.0321721914776063</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>-0.06747892460564486</v>
+        <v>-0.03042080741979447</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>-0.07389556831589061</v>
+        <v>-0.03613945029857746</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>-0.1618091904966761</v>
+        <v>-0.1213700612485624</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.009979</t>
+          <t>X &gt; -0.009918</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3332</v>
+        <v>3355</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.003399289937632943</v>
+        <v>-0.01983217512066204</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.03570922272463406</v>
+        <v>0.07584310186512511</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.1054501179461766</v>
+        <v>0.1108007703129061</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1551099728928023</v>
+        <v>0.1569627280783195</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.07492598003303641</v>
+        <v>0.1054095057598374</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.06975639826921309</v>
+        <v>0.07142007514671178</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.04429920437587498</v>
+        <v>0.06394947290027631</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-0.0675168792197951</v>
+        <v>-0.04618803194893673</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.09855492451868741</v>
+        <v>-0.07944367157571719</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.01755979981132327</v>
+        <v>0.002108538836580465</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.03468801876006467</v>
+        <v>0.05389357956283192</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.01744127755095803</v>
+        <v>0.002231149298474122</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-0.04636336284164599</v>
+        <v>-0.02605105801297469</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.2198244959145796</v>
+        <v>-0.197430567458234</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>-0.2017672199847667</v>
+        <v>-0.1784278678952944</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-0.2181999637089476</v>
+        <v>-0.1941700640406765</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>-0.2744736454585066</v>
+        <v>-0.2508117687884237</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-0.1518340795189985</v>
+        <v>-0.1579107589352873</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>-0.09789756202559374</v>
+        <v>-0.1044337827777326</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>-0.1330557490996753</v>
+        <v>-0.1402407371148229</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>-0.1181288550355717</v>
+        <v>-0.1243981098388787</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>-0.146065357856628</v>
+        <v>-0.1223305259979597</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>-0.1536854415368509</v>
+        <v>-0.1291910659688043</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>-0.2416737723126658</v>
+        <v>-0.2141055594420607</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.009177</t>
+          <t>X &gt; -0.009117</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3313</v>
+        <v>3335</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.1522563348438908</v>
+        <v>0.1202678519966156</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.1335542525853413</v>
+        <v>0.1584429032692398</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.1219105945427614</v>
+        <v>0.1117186990138563</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.1159000185440036</v>
+        <v>0.1020750535185115</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.06718324668685227</v>
+        <v>0.08165636032378387</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.09094509966096354</v>
+        <v>0.0763450645517878</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.03971713649132624</v>
+        <v>0.04374234810163813</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-0.04111158459485154</v>
+        <v>-0.03539681247828952</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.07255575189567054</v>
+        <v>-0.06961152666230674</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.01332374443379081</v>
+        <v>0.04704426877763268</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.09437987896911437</v>
+        <v>0.1273944039639758</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.07363869510796661</v>
+        <v>0.0770979406277732</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.05099869153280423</v>
+        <v>0.05533308687104466</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.2124407445258498</v>
+        <v>-0.2052486721453235</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>-0.1002067092197265</v>
+        <v>-0.09234186865764826</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-0.1502148859872392</v>
+        <v>-0.1414238309711777</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>-0.1759032633009454</v>
+        <v>-0.1678448533812116</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-0.1121908755754646</v>
+        <v>-0.1334297252354304</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>-0.05916981896250206</v>
+        <v>-0.08090940296592919</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>-0.09558798439073257</v>
+        <v>-0.1182091226843056</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>-0.04729876947521205</v>
+        <v>-0.06890700643663905</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>-0.105105224091524</v>
+        <v>-0.09632695834061167</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>-0.1143302688439647</v>
+        <v>-0.1046814722135281</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>-0.2023764355089455</v>
+        <v>-0.1891255010360808</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.008375</t>
+          <t>X &gt; -0.008317</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3296</v>
+        <v>3318</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1867598787319906</v>
+        <v>0.1838024846999389</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.109392669466331</v>
+        <v>0.1336221248082836</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.1352110802004987</v>
+        <v>0.1229897646623215</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.1026639548877739</v>
+        <v>0.0863593505845941</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.02524079101134191</v>
+        <v>0.03726869301900138</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.01221571282675171</v>
+        <v>-0.02883473434693684</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-0.05974544108776314</v>
+        <v>-0.05758228790971032</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-0.07920458375463113</v>
+        <v>-0.07561258311108787</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.1110347147932345</v>
+        <v>-0.1106663784161341</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.02075611303557423</v>
+        <v>-0.01937823931189087</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.05929816610925087</v>
+        <v>0.0599726567696095</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.02058719610131021</v>
+        <v>-0.01921887215154783</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.06783722411417159</v>
+        <v>-0.06546950341802216</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.3012823968422182</v>
+        <v>-0.296102558542934</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>-0.185112635966739</v>
+        <v>-0.1791605322524532</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-0.2384621028688798</v>
+        <v>-0.2313884297261879</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>-0.2636201617758687</v>
+        <v>-0.2574404761904816</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-0.1687818849959228</v>
+        <v>-0.1921124445117783</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>-0.1166167467479085</v>
+        <v>-0.140438253780701</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>-0.1845054983911538</v>
+        <v>-0.2091472431113743</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>-0.1331986163052861</v>
+        <v>-0.1567154206368855</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>-0.1606167229019917</v>
+        <v>-0.1537968739635502</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>-0.2016520216343523</v>
+        <v>-0.1935889542423652</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>-0.2897876780691391</v>
+        <v>-0.2776617030977988</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.007573</t>
+          <t>X &gt; -0.007516</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3279</v>
+        <v>3297</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.2216188059863882</v>
+        <v>0.1783735731849774</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.1152851791273051</v>
+        <v>0.1294893415502116</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.1486486427034421</v>
+        <v>0.1271069740286492</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.1196128438803257</v>
+        <v>0.09416506914073608</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.1041882220531463</v>
+        <v>0.1370774554165592</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-0.02542126670540767</v>
+        <v>-0.03781397629274608</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-0.03887480496469209</v>
+        <v>-0.03153315194660422</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-0.1176906517980001</v>
+        <v>-0.1081053299586472</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.1499108497425681</v>
+        <v>-0.14420234070802</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.115922734900316</v>
+        <v>-0.107701094881179</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-0.0368992145019007</v>
+        <v>-0.02960061854122387</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.05501475254946797</v>
+        <v>-0.04712529171707303</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-0.09671582095628395</v>
+        <v>-0.08660035926217802</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.3302336922655442</v>
+        <v>-0.3171280348054069</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-0.2404829184039485</v>
+        <v>-0.2253644721884243</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-0.2971992514128203</v>
+        <v>-0.2815047370394979</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>-0.260948251531417</v>
+        <v>-0.2465445924132439</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-0.165075815061833</v>
+        <v>-0.1799530576290564</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>-0.1442077657466925</v>
+        <v>-0.159595156836744</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>-0.2134239857318079</v>
+        <v>-0.2301121925246576</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>-0.1895191196838724</v>
+        <v>-0.2040450858527336</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>-0.216703470404795</v>
+        <v>-0.2006438557068293</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>-0.2898789389353738</v>
+        <v>-0.2725762649299881</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>-0.3476081863344476</v>
+        <v>-0.3258451303024401</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.006771</t>
+          <t>X &gt; -0.006715</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3245</v>
+        <v>3263</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.1558460892624538</v>
+        <v>0.156003408875705</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.03994244164395155</v>
+        <v>0.04825084544253144</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-0.02148609806766899</v>
+        <v>0.05881315062047321</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-0.04323810805202299</v>
+        <v>-0.02929226548928909</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-0.02461921245944154</v>
+        <v>0.04736121818432082</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.1748694579990939</v>
+        <v>-0.1614473276005839</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1191050824167235</v>
+        <v>-0.1164095815799513</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-0.2265320239903588</v>
+        <v>-0.1906398978677188</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.2595543361335118</v>
+        <v>-0.1979569866715849</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.2171817213208769</v>
+        <v>-0.1528341239544346</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.04814361747444451</v>
+        <v>0.01481283976950465</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.1249480388438897</v>
+        <v>-0.06107752469721817</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.1860902188413149</v>
+        <v>-0.1504761635728613</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.3583215464403509</v>
+        <v>-0.3197334018059905</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-0.1993020846331959</v>
+        <v>-0.1588040064426579</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-0.2013293090760016</v>
+        <v>-0.160198488713192</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>-0.1940200107334888</v>
+        <v>-0.154338685015297</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-0.126787631166188</v>
+        <v>-0.1162346455919021</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>-0.1079480449559185</v>
+        <v>-0.09787669237731933</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>-0.1798327319455311</v>
+        <v>-0.1713419373951695</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>-0.1499879255003407</v>
+        <v>-0.1390782094957785</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>-0.2382458746328595</v>
+        <v>-0.2267225736997034</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>-0.2534551227563639</v>
+        <v>-0.1794011082693956</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>-0.3109834684561363</v>
+        <v>-0.2621536513801601</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.005969</t>
+          <t>X &gt; -0.005914</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3202</v>
+        <v>3219</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.2387307884923047</v>
+        <v>0.2062162215962786</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.138005395886637</v>
+        <v>0.131219522605285</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.2074750516095847</v>
+        <v>0.1898689690577626</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.1020454552834735</v>
+        <v>0.0777734708779505</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.06340496484792624</v>
+        <v>0.06656917796285455</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-0.02930566695400927</v>
+        <v>-0.05453243383332307</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-0.1797503110681049</v>
+        <v>-0.1834526036788944</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-0.1916056415409386</v>
+        <v>-0.1927421711038448</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.1945419746281587</v>
+        <v>-0.2018999915733701</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.07878282881743104</v>
+        <v>-0.08346821183044995</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.08886058032042143</v>
+        <v>0.08277636689145851</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.01625925237512149</v>
+        <v>-0.02131009986951682</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-0.09395262670371807</v>
+        <v>-0.09672685624295241</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.2527650025276458</v>
+        <v>-0.2339219298653248</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-0.1139126054362833</v>
+        <v>-0.09245303708226515</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-0.1550552251486792</v>
+        <v>-0.1324878611806852</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>-0.1146767430097455</v>
+        <v>-0.09412456085968302</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-0.1074573042612172</v>
+        <v>-0.1156844927585041</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>-0.02889021472876863</v>
+        <v>-0.03796799050549282</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>-0.0730289109320239</v>
+        <v>-0.08432010045089555</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.004270027818911615</v>
+        <v>-0.01280305662187686</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>-0.1238600610882656</v>
+        <v>-0.1005787234976694</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>-0.04926038772956076</v>
+        <v>-0.02484472049688691</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>-0.1377096382517919</v>
+        <v>-0.1064641290193933</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.005167</t>
+          <t>X &gt; -0.005113</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3160</v>
+        <v>3175</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.04071361658692041</v>
+        <v>0.007576587497780451</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.1197850701072483</v>
+        <v>-0.1277075312737921</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.001974167650708125</v>
+        <v>-0.01975348730229598</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.09387546068936814</v>
+        <v>0.06255423066419041</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.05935167763199445</v>
+        <v>0.05498800540831184</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-0.1317539699190178</v>
+        <v>-0.1952190087000787</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.2420769449246833</v>
+        <v>-0.2523439296452281</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-0.2817742727519246</v>
+        <v>-0.3202549739685523</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1907776938881085</v>
+        <v>-0.2372997314066012</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.03115053910795496</v>
+        <v>-0.07490374208121153</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.1981223078963481</v>
+        <v>0.152615926129684</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.1270034101457966</v>
+        <v>0.1136878029578341</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.06387565612455859</v>
+        <v>0.05266901073700581</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1572032203220317</v>
+        <v>-0.145739528715616</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>-0.1019746399822381</v>
+        <v>-0.08708231731241511</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-0.1203602672332948</v>
+        <v>-0.1040111214198234</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>-0.07754775596353625</v>
+        <v>-0.06367195684055815</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-0.06875822389638131</v>
+        <v>-0.08368246521609279</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>0.1027574683104575</v>
+        <v>0.08649164399674447</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>0.05544620076358342</v>
+        <v>0.03656707831504491</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>0.1643904357777402</v>
+        <v>0.1799013641730198</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>0.04424468140134508</v>
+        <v>0.06053543165172925</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>0.06555483692137187</v>
+        <v>0.1339940860803921</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>-0.04192298592216304</v>
+        <v>0.05354056750444869</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.004365</t>
+          <t>X &gt; -0.004312</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3094</v>
+        <v>3099</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.05690208270950592</v>
+        <v>-0.002094847303169445</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.2927676879155854</v>
+        <v>-0.2949438202247237</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.006106154658446883</v>
+        <v>-0.02559380870059158</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.08318422952569193</v>
+        <v>0.00901413805147655</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-0.0414025799350668</v>
+        <v>-0.05619923335919452</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-0.2406610478447746</v>
+        <v>-0.31633332065595</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-0.304531199388812</v>
+        <v>-0.3554981566762265</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-0.467886611060365</v>
+        <v>-0.5460706584302102</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.343675533885019</v>
+        <v>-0.4000594795759653</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-0.1639686523572124</v>
+        <v>-0.2143164780188798</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1287481091205649</v>
+        <v>0.07633372391249793</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.09432871803763021</v>
+        <v>0.04318683152706626</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.03499643841556122</v>
+        <v>0.007899187777638872</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.1216079054714001</v>
+        <v>-0.157141075751035</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>-0.1479278129556718</v>
+        <v>-0.1768975453185959</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>-0.01808406647116811</v>
+        <v>-0.07925779769458785</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.003743180569252047</v>
+        <v>-0.03538178793732527</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-0.02478792863635704</v>
+        <v>-0.08482653672360385</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>0.1780855856046841</v>
+        <v>0.1164793247333122</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>0.06120744499621367</v>
+        <v>0.02785902939142204</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>0.2163565678426593</v>
+        <v>0.1886048174354684</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>0.03064138224331714</v>
+        <v>0.003663020435077158</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>-0.05041073138968954</v>
+        <v>-0.05610098176718026</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>-0.1585636051688795</v>
+        <v>-0.1668810569464085</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003564</t>
+          <t>X &gt; -0.003511</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2993</v>
+        <v>2999</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.2011661563033584</v>
+        <v>-0.2159137191731517</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.351953699015823</v>
+        <v>-0.2785997889800313</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.1609833863446823</v>
+        <v>-0.157503916120092</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.190447994555484</v>
+        <v>-0.2015675716050538</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-0.07516190390058597</v>
+        <v>-0.02786019553172991</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-0.4537313132789293</v>
+        <v>-0.4344002388541739</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-0.5603440024919593</v>
+        <v>-0.4816971535538102</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.6866462871957566</v>
+        <v>-0.6353513816200476</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4598598592397281</v>
+        <v>-0.4224128815335959</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2148520473127817</v>
+        <v>-0.2040920186171817</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.1117865947965697</v>
+        <v>0.1867745655161031</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.0189401359810617</v>
+        <v>0.06211453697994074</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-0.1045551531343065</v>
+        <v>-0.03696733431912236</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.2256673518068197</v>
+        <v>-0.1327904116502765</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>-0.2307505583066245</v>
+        <v>-0.1637622595769272</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>-0.1832681600937747</v>
+        <v>-0.1813048504410588</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>-0.1639876890626937</v>
+        <v>-0.1658142049234854</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-0.08216185086933336</v>
+        <v>-0.1126920641189031</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>0.08687582276515116</v>
+        <v>0.05487761155362847</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.006886233960536003</v>
+        <v>-0.04385999173140931</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>0.104976025389945</v>
+        <v>0.07449649248898282</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>-0.1847178345113107</v>
+        <v>-0.1807858695995392</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>-0.2109447591826168</v>
+        <v>-0.1840579710144823</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>-0.3201883054229313</v>
+        <v>-0.2598237297809973</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.002762</t>
+          <t>X &gt; -0.002711</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2865</v>
+        <v>2862</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.1500516983572879</v>
+        <v>-0.2602370094582866</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.2230179354093025</v>
+        <v>-0.2444056972404596</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-0.1669438642179202</v>
+        <v>-0.1596684025847424</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-0.1655264206448095</v>
+        <v>-0.1959357386887604</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-0.2036948241518814</v>
+        <v>-0.1239095895979645</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.5382863571087455</v>
+        <v>-0.5231108463040854</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.5800542343231569</v>
+        <v>-0.4297258406117948</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.6299292214357877</v>
+        <v>-0.5260231963987181</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.449311604738476</v>
+        <v>-0.3437192489205856</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.2629945797976916</v>
+        <v>-0.1111059533620278</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.1356017888904049</v>
+        <v>0.3203393896399547</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.0511137197168452</v>
+        <v>0.1481779015800697</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2015748095348187</v>
+        <v>-0.1457967700903211</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2485589784605224</v>
+        <v>-0.1851171824983666</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>-0.1198136025420808</v>
+        <v>-0.04570948309604717</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>-0.201404286770142</v>
+        <v>-0.1605287055804538</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>-0.2798079024220925</v>
+        <v>-0.243896682932494</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-0.1896263586127773</v>
+        <v>-0.1470490284530896</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>-0.09249367024099087</v>
+        <v>-0.05149143388143074</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>-0.1640567682424958</v>
+        <v>-0.1303517739663818</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>0.04702417054588182</v>
+        <v>0.09057652290500329</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>-0.3080539025560682</v>
+        <v>-0.2431486946541241</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>-0.4175233436516663</v>
+        <v>-0.2931859253747149</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>-0.3886435549901321</v>
+        <v>-0.2600334432913769</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.00196</t>
+          <t>X &gt; -0.00191</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>2684</v>
+        <v>2683</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.3791717983837799</v>
+        <v>-0.5426267281105979</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.2863395217187517</v>
+        <v>-0.3242875467711173</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.3149443584308358</v>
+        <v>0.1458012445978767</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3274089544625838</v>
+        <v>0.2205599056858745</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.3465179275311669</v>
+        <v>0.3897756721840295</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.17152516280931</v>
+        <v>-0.1945805661470317</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.09548719226138047</v>
+        <v>0.1432850203716285</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.01303499594275337</v>
+        <v>0.02375575234306382</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.1026912357121219</v>
+        <v>0.1356898595815537</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.3165511948219901</v>
+        <v>0.3254869795028981</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.5380007185159741</v>
+        <v>0.5078362726593113</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3924066294365502</v>
+        <v>0.3054933679281788</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.1982672307335278</v>
+        <v>0.1404089815385205</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.1629928879175608</v>
+        <v>0.1521080801499721</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>0.2704885990663541</v>
+        <v>0.3462694340148005</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>0.2551077904369095</v>
+        <v>0.260943306559632</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>0.2550168457065141</v>
+        <v>0.253446406443615</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>0.1724532654254745</v>
+        <v>0.1426404082882513</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.4478684393788157</v>
+        <v>0.4908043124603623</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>0.2101110582365848</v>
+        <v>0.2437323315884967</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>0.3976378517749524</v>
+        <v>0.3684181917482974</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>0.02372929722130124</v>
+        <v>0.05480288821365775</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>-0.03711640758427848</v>
+        <v>-0.01470874100951391</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>-0.07569083666448506</v>
+        <v>-0.005695039598897722</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001158</t>
+          <t>X &gt; -0.001109</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2419</v>
+        <v>2399</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.1457813239582819</v>
+        <v>-0.1872000503972586</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.1104923328344114</v>
+        <v>0.063993362448997</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.1093666450233073</v>
+        <v>-0.008001805780644133</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.02313564006534818</v>
+        <v>0.1455553820667532</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.1631269504893922</v>
+        <v>0.3673034997378153</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-0.06142949715808754</v>
+        <v>-0.09739571647710221</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.03081934981575785</v>
+        <v>0.1670814995995187</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.1415550470573521</v>
+        <v>-0.01346083435636558</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1000678651426483</v>
+        <v>0.09656711971592813</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.01547775468093704</v>
+        <v>0.1300469393037247</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2722619488182048</v>
+        <v>0.3847103465964707</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.5533044712548474</v>
+        <v>0.6890412551957255</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.2545447127251919</v>
+        <v>0.345513092761486</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.3632267596091907</v>
+        <v>0.5123890354794867</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>0.3482872423806569</v>
+        <v>0.43629870741254</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>0.5963096309631055</v>
+        <v>0.6486240414161912</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>0.652267032409334</v>
+        <v>0.7773534912718176</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>0.44844031749777</v>
+        <v>0.5862123951848943</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.4826534229689727</v>
+        <v>0.5759798136092442</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>0.4463484960992119</v>
+        <v>0.5656844380377422</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>0.4245762289664512</v>
+        <v>0.522546390946907</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>0.1833726817781098</v>
+        <v>0.2640887459839618</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>0.209811015591292</v>
+        <v>0.3659420289855149</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>0.05129996947839288</v>
+        <v>0.2703238072401675</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003561</t>
+          <t>X &gt; -0.000308</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2044</v>
+        <v>2023</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.08178062379431594</v>
+        <v>0.04283496147682087</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.05834897260902494</v>
+        <v>-0.05572413355906747</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.3527803968514576</v>
+        <v>0.1410475185691382</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4459444024124508</v>
+        <v>0.3348861060016972</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.8683480562084114</v>
+        <v>0.7964287030030945</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.275966945666724</v>
+        <v>0.2162615719004464</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.6243300006950321</v>
+        <v>0.5794738153071179</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2280248424679314</v>
+        <v>0.1270607465297715</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.366977911322202</v>
+        <v>0.2338294582801765</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.2072514464630686</v>
+        <v>0.02803866153599444</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.7048546307400798</v>
+        <v>0.6730839212689332</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.8651296175359846</v>
+        <v>0.790202754199214</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.01413001029574446</v>
+        <v>-0.04979181074842387</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.4964984303308384</v>
+        <v>0.4405265650415089</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>0.40443733822827</v>
+        <v>0.2999773037866831</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>0.3935842803030312</v>
+        <v>0.2503808222340425</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>0.601464018325558</v>
+        <v>0.5207049860358168</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>0.6237386433392587</v>
+        <v>0.5158461709725231</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>0.23373178059488</v>
+        <v>0.167784132508757</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>0.1074853143820604</v>
+        <v>0.06608271446007308</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>0.4746324942310878</v>
+        <v>0.4166058681315548</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>0.105244458458003</v>
+        <v>0.07454733290344251</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>-0.06059394060593348</v>
+        <v>-0.04784113133744228</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>-0.2342735519505439</v>
+        <v>-0.1605485883060993</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0004458</t>
+          <t>X &gt; 0.0004929</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1565</v>
+        <v>1543</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.7818890448169782</v>
+        <v>-1.094173119863171</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.989601040117229</v>
+        <v>-1.08234799680416</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.203986035781007</v>
+        <v>-0.2398749900129431</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2180836384511906</v>
+        <v>-0.3164809283440562</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.88026988985456</v>
+        <v>1.019824245547575</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.6492292768770511</v>
+        <v>-0.6930035926838585</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.1045690195250302</v>
+        <v>-0.06964588860453347</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.180779927806384</v>
+        <v>0.1412299284639644</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-0.4138652058005405</v>
+        <v>-0.5045355525675959</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3230824547156956</v>
+        <v>-0.3979435919519858</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.3965532536461112</v>
+        <v>0.3900876831294582</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.07315732103040773</v>
+        <v>-0.01544333646111795</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.4961284267152877</v>
+        <v>-0.6416184971098318</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.01701634199066149</v>
+        <v>-0.1156590101558379</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>0.1906931784237287</v>
+        <v>0.1699285434429783</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>0.1223999072947493</v>
+        <v>-0.004892721479208717</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>0.5620965370476725</v>
+        <v>0.4076891004949346</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>0.4318513119533591</v>
+        <v>0.1840571093086822</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>0.04795986334510616</v>
+        <v>-0.1448345584726241</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>0.08125556047335891</v>
+        <v>-0.02152355283610774</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>0.4712250303220742</v>
+        <v>0.2257872177659834</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>0.5231745960695235</v>
+        <v>0.4483006352442729</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>0.1586716727688327</v>
+        <v>0.01786469046747641</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>0.1467371831238253</v>
+        <v>0.1149609521728294</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.001248</t>
+          <t>X &gt; 0.001294</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1126</v>
+        <v>1112</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.7672838950411602</v>
+        <v>-1.353171857690583</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.720982001967457</v>
+        <v>-1.688444198309547</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2412291677093279</v>
+        <v>-0.2131739984430823</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2468445487789452</v>
+        <v>-0.2689035675554123</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8827452905600524</v>
+        <v>0.7972198665849675</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.965686753431072</v>
+        <v>-0.7453098547872585</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.05621950811787713</v>
+        <v>-0.1092648544976171</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.1574398024284847</v>
+        <v>0.03304189350699716</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-0.7354216470624451</v>
+        <v>-0.6440381413527234</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.8003727213290333</v>
+        <v>-0.9034170068761682</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2608263535033899</v>
+        <v>-0.005063924293303046</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.5395757569513862</v>
+        <v>-0.2816458787645999</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.397251098143776</v>
+        <v>-1.255763528443751</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.02540962060807317</v>
+        <v>0.01793616124220421</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>-0.4538093123662676</v>
+        <v>-0.3956416763277204</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>-0.8337359422390378</v>
+        <v>-0.6773695882749919</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>-0.7019312014485806</v>
+        <v>-0.5124327956989205</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-0.04533424311973988</v>
+        <v>-0.0180767574913574</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>-0.1314276709200115</v>
+        <v>-0.109238395205665</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>0.05541813904801529</v>
+        <v>0.2480085227582975</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>0.3648800845443745</v>
+        <v>0.4524116649436394</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>0.4666540165633393</v>
+        <v>0.7366381816226735</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>-0.2357806848089581</v>
+        <v>-0.04472943384422479</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>-0.1339930446041748</v>
+        <v>0.1528438020821383</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.00205</t>
+          <t>X &gt; 0.002095</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>799</v>
+        <v>791</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.03388193930261707</v>
+        <v>-0.01617836539019635</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.234330379443477</v>
+        <v>-2.025309382454267</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.562896692156059</v>
+        <v>-0.509222627922675</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.03206961707143563</v>
+        <v>-0.2200127360507906</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.94359013125699</v>
+        <v>1.771431642741554</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.733702711288224</v>
+        <v>-0.7164710233006559</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.01125538023461559</v>
+        <v>-0.1261626073217883</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.6630658287236741</v>
+        <v>-0.8089168038790291</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.244243653035625</v>
+        <v>-1.43665540049215</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.269961321600128</v>
+        <v>-1.35109480503138</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-1.120434680683537</v>
+        <v>-1.204804374809925</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.772783087867523</v>
+        <v>-1.733275498046957</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.899681144761011</v>
+        <v>-1.895086340741599</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.2527650025276458</v>
+        <v>-0.2517693302957724</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>-0.961839502612527</v>
+        <v>-0.8078203073888943</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>-0.6168291392730296</v>
+        <v>-0.4987230981530999</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.002616600440035199</v>
+        <v>0.1540169188734666</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>0.09179487739451275</v>
+        <v>0.1472362185037994</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>0.007436570428701827</v>
+        <v>-0.1427151735181482</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>-0.1807176196032643</v>
+        <v>-0.3064389428349514</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>1.228081644220431</v>
+        <v>0.9676720858644359</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>1.778017910596063</v>
+        <v>1.523822695222286</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>0.5506152763947654</v>
+        <v>0.327488594514378</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>1.100565250956222</v>
+        <v>1.050305352437306</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002851</t>
+          <t>X &gt; 0.002895</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.639131847565757</v>
+        <v>-1.020887597675809</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-2.34612133888298</v>
+        <v>-2.65809878120578</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.1609711043673343</v>
+        <v>-0.2606189700538764</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1341234314082982</v>
+        <v>-0.3312820384273181</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>1.613213921767667</v>
+        <v>1.306203299734221</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2616755622380538</v>
+        <v>-0.1020804855720456</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>1.028231423974695</v>
+        <v>1.015880980456103</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.06273475585390997</v>
+        <v>0.3631344500909677</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>1.135149772820171</v>
+        <v>1.708454664122904</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.8776980143094519</v>
+        <v>1.608055342816606</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.9799363506294512</v>
+        <v>1.532464270464416</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.1857230296556835</v>
+        <v>0.734143185558338</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.7656177313585104</v>
+        <v>-0.4534651870052926</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.7315164506141372</v>
+        <v>1.214677058181799</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>0.760658376401274</v>
+        <v>1.055170759920443</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>0.6677600749765702</v>
+        <v>0.7453946393672766</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>1.908413384734494</v>
+        <v>2.035242450638783</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>1.975393986755236</v>
+        <v>1.902358345477182</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>0.9885362267860884</v>
+        <v>1.07152440537557</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>0.6599181192283439</v>
+        <v>0.937678794685425</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>2.113870463721575</v>
+        <v>2.219721374562944</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>2.554375621073234</v>
+        <v>2.668119062031735</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>1.279796977273008</v>
+        <v>1.34107291903787</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>2.925135119918934</v>
+        <v>3.273174762444739</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.003653</t>
+          <t>X &gt; 0.003696</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.131880159295306</v>
+        <v>1.148448786763545</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-2.611987548145414</v>
+        <v>-2.301119376171449</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.8681884153582331</v>
+        <v>-0.1233191988868256</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-1.808415162073693</v>
+        <v>-0.9445543496401285</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.9408016132564399</v>
+        <v>1.525882933601501</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.4443965009483506</v>
+        <v>1.225150635709426</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-0.09976175014018196</v>
+        <v>0.430068623476707</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.605763627695076</v>
+        <v>-0.3325177238220789</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.5746757182287396</v>
+        <v>0.9395759455874355</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.2573409077958928</v>
+        <v>0.6011903542582573</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>1.214771848363277</v>
+        <v>1.559924224697824</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>1.391603310518931</v>
+        <v>1.512175222171606</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4962316764646317</v>
+        <v>0.53269342949568</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>2.097476262432629</v>
+        <v>2.119321753383673</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>2.578285128861182</v>
+        <v>2.583956362324301</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>2.71709118520053</v>
+        <v>3.145260381143963</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>3.0387549138267</v>
+        <v>3.500095565749227</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>3.161704642807344</v>
+        <v>3.596569258752773</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>2.238643859722558</v>
+        <v>2.664242495072855</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>1.514327938483284</v>
+        <v>1.961397747471288</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>2.937124340284576</v>
+        <v>2.912987307041725</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>4.002830890291001</v>
+        <v>3.757365014971505</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>2.679132086791327</v>
+        <v>2.621689155422295</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>4.886404856399089</v>
+        <v>4.988285793316741</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.004455</t>
+          <t>X &gt; 0.004497</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2283842054200989</v>
+        <v>-0.1097909072150784</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-2.343576434036976</v>
+        <v>-2.146742519038348</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.2207646225338422</v>
+        <v>0.7776678566820081</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-2.417398167199131</v>
+        <v>-1.605779118245614</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.5100065004218308</v>
+        <v>0.2082149804610225</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.6206593619435026</v>
+        <v>0.06664112377253417</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-2.58308423631005</v>
+        <v>-1.922470739206453</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-2.266057585825024</v>
+        <v>-1.9288837199285</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.1563819770420594</v>
+        <v>0.5871048912481456</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.807009889470621</v>
+        <v>-1.402976454717461</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.9377121520706027</v>
+        <v>-0.5337265147399961</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5692527301956929</v>
+        <v>0.9807363069081134</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-1.14914743189852</v>
+        <v>-1.328185661288927</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1797501178689274</v>
+        <v>-0.3823898719757679</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>0.3525827750267041</v>
+        <v>0.1294855968854378</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>0.6493506493506445</v>
+        <v>0.3922821530185416</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>1.110671607611266</v>
+        <v>1.18392412935323</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>3.386783284742471</v>
+        <v>3.1405922629976</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>2.412198475190607</v>
+        <v>2.459532102083678</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>1.110949047063393</v>
+        <v>1.181581233709821</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>2.539795913923236</v>
+        <v>2.290783438915909</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>4.254994728633541</v>
+        <v>4.012028102589369</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>3.036932127682761</v>
+        <v>2.758656599843789</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>5.349159575952008</v>
+        <v>5.291128383997439</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.005257</t>
+          <t>X &gt; 0.005298</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>2.1562543358434</v>
+        <v>2.135028949545081</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-2.888667390042649</v>
+        <v>-2.872782648063556</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.383458488462594</v>
+        <v>0.2681276456492654</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-2.865727415038116</v>
+        <v>-2.522076750961155</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.2648852744699397</v>
+        <v>0.4990684056428023</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.2754212667054006</v>
+        <v>-0.07659872095984355</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-2.501915405141219</v>
+        <v>-1.970581832093664</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-2.780126849894295</v>
+        <v>-2.275502275502284</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.1931851225250369</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-2.784282616743347</v>
+        <v>-2.211024128436776</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-2.146586610945057</v>
+        <v>-1.572488747532077</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.9707905598476003</v>
+        <v>-0.3838692368019139</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-3.184861717612804</v>
+        <v>-2.963962819454146</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-1.951395139513942</v>
+        <v>-1.746995415685795</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>-1.154992982549047</v>
+        <v>-0.9639483323693767</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>-1.651515151515156</v>
+        <v>-1.501545412450824</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>-0.6945231975835284</v>
+        <v>-0.5065247252747227</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>1.382454280413469</v>
+        <v>1.192093001065501</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>0.6739544956105448</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.03299034687599089</v>
+        <v>0.1559402080687988</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>0.7356778182701191</v>
+        <v>0.5406073205643764</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>2.849612878758826</v>
+        <v>2.671327151550273</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>0.9343065693430717</v>
+        <v>1.076726342710998</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>2.683291834367964</v>
+        <v>2.752822642539186</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.006059</t>
+          <t>X &gt; 0.006099</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>223</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>4.394867172282325</v>
+        <v>4.493087557603694</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.297052483210351</v>
+        <v>-0.6635335638144682</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.729214182044366</v>
+        <v>2.54605804857966</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.215882694541222</v>
+        <v>-0.2784870073714103</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>2.466183975768644</v>
+        <v>3.017383423957824</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.4210073047231617</v>
+        <v>1.388602744241616</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.690227093452897</v>
+        <v>-1.19219355370538</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-2.414867109634542</v>
+        <v>-1.943542568542568</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7516200722801614</v>
+        <v>1.755814912570109</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-2.699867032327759</v>
+        <v>-1.718808011220659</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.532950247308698</v>
+        <v>-0.5537158537591864</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.4204432063861674</v>
+        <v>1.401845048912378</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-1.498761354252686</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-2.709512022630832</v>
+        <v>-2.193423987114365</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>-1.13551246306853</v>
+        <v>-0.6434355118565591</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>-1.880411255411261</v>
+        <v>-1.421417207322619</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>-0.6750426781030114</v>
+        <v>-0.1860119047619051</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>0.5594023323615147</v>
+        <v>1.020389704362202</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>-0.5639920009998676</v>
+        <v>-0.550862354206302</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>-1.716431905317563</v>
+        <v>-1.67556162343304</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>-1.552299662008764</v>
+        <v>-1.538329635383917</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>1.959298322770479</v>
+        <v>1.973951788849135</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>0.4400510621583535</v>
+        <v>0.4238643010333405</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>2.606371275302799</v>
+        <v>2.503877773111597</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.006861</t>
+          <t>X &gt; 0.0069</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>4.922688798170235</v>
+        <v>5.248582063098198</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.16802249705799</v>
+        <v>0.607070831789926</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.702379138634747</v>
+        <v>4.297431674953295</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.8779781957251203</v>
+        <v>-0.1411243700087752</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.101148458799415</v>
+        <v>2.880020786595189</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>2.840600832742112</v>
+        <v>3.586404942043821</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-1.246264978220069</v>
+        <v>-0.5053803668921972</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-1.524476422973144</v>
+        <v>-0.8103008103008165</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>1.279441698168071</v>
+        <v>2.064880846636044</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-1.703418729249627</v>
+        <v>-0.9289728463854985</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.8768728992424002</v>
+        <v>-0.107287282330617</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.05064992699978887</v>
+        <v>0.7150318620991953</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-2.278784369546514</v>
+        <v>-2.048211903703233</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-3.052349433838408</v>
+        <v>-2.84589651458689</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>-2.053034167883055</v>
+        <v>-1.879699248120303</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>-2.011133433785368</v>
+        <v>-1.867845778751189</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>-1.04007819507224</v>
+        <v>-0.8728250915750877</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>1.617512040333104</v>
+        <v>1.741543550516056</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>-0.3765413301237786</v>
+        <v>-0.2417964201403677</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>-1.294667895846366</v>
+        <v>-0.5766605245319312</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>0.1517362124306985</v>
+        <v>0.8351312074672066</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>3.964779139910483</v>
+        <v>4.627372000429055</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>2.017031630170322</v>
+        <v>2.661061734326211</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>4.718977154724818</v>
+        <v>5.261353679263273</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.007663</t>
+          <t>X &gt; 0.007701</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>152</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>5.182682298332743</v>
+        <v>5.93449745489594</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.3808526699517145</v>
+        <v>-0.1937623219844014</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.409886450951937</v>
+        <v>4.433896517300489</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2.043337660267369</v>
+        <v>3.187899547250439</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>3.668331501445579</v>
+        <v>4.873125720876587</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>2.548108145059302</v>
+        <v>3.722869784391015</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.468969918685282</v>
+        <v>1.620598229674641</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>0.1907584739322061</v>
+        <v>1.315677786266022</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2.846624740814235</v>
+        <v>4.057985780917441</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>0.7665195222940895</v>
+        <v>1.954744743214448</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.3869843932141848</v>
+        <v>1.573384986576954</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.1082349897661885</v>
+        <v>1.296803032105657</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-2.322116619573599</v>
+        <v>-1.125278627828784</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-3.850385038503845</v>
+        <v>-3.334297002987377</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>-2.54774402235892</v>
+        <v>-2.709261842388777</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>-2.606951871657756</v>
+        <v>-2.801552594810943</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>-2.087274237393402</v>
+        <v>-2.251838235294123</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>1.075858914994569</v>
+        <v>0.8832515157534289</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.01543924656476037</v>
+        <v>-0.2094757995844532</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>-0.4821882078385613</v>
+        <v>-0.6484841257672969</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>0.02015726506228077</v>
+        <v>-0.175336951881448</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>5.207469198390022</v>
+        <v>5.012658420900117</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>2.192470226661548</v>
+        <v>1.966819221967967</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>6.06400639449091</v>
+        <v>5.75204864873114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.008465</t>
+          <t>X &gt; 0.008501</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.15915288656803</v>
+        <v>3.600230414746541</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-1.975623911781781</v>
+        <v>-1.407581182862081</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>4.586357039187227</v>
+        <v>5.274232651754268</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2.273403019744485</v>
+        <v>3.094528865644463</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>4.33761254719721</v>
+        <v>5.199923106497508</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>2.924578733294588</v>
+        <v>3.769555125194003</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>2.152630049404237</v>
+        <v>2.974473112961284</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>0.2744186046511601</v>
+        <v>1.082251082251084</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2.71590578656587</v>
+        <v>3.591132372887564</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.942990110529379</v>
+        <v>2.795080877668227</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.417049752691298</v>
+        <v>2.27366509862177</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.138300349243302</v>
+        <v>1.997083144150473</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.784861717612813</v>
+        <v>-0.7051105606018808</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-3.405940594059395</v>
+        <v>-3.334297002987377</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>-3.264083891639963</v>
+        <v>-3.222800591221642</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>-3.469696969696962</v>
+        <v>-3.455147366052771</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>-2.803614106674445</v>
+        <v>-2.765376984126988</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>0.2915451895043759</v>
+        <v>0.2763420853145888</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>0.4908043124603623</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>0.6942823803967286</v>
+        <v>0.7053907575193463</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>2.248510405979083</v>
+        <v>2.214136732329088</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>6.20492250908611</v>
+        <v>6.13897421037381</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>4.866493995761715</v>
+        <v>4.782608695652179</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>7.210016581248119</v>
+        <v>7.020469701362721</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.009266</t>
+          <t>X &gt; 0.009302</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>3.502010029425172</v>
+        <v>4.004543083210159</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-4.451814387972256</v>
+        <v>-2.845137337399372</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>6.491118943949132</v>
+        <v>8.164319504105272</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2.921022067363538</v>
+        <v>4.741728626051767</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>5.442374451959118</v>
+        <v>7.296359165197714</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.819816828532694</v>
+        <v>3.67970786553542</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.8568937601195685</v>
+        <v>0.9978334004725156</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-2.087486157253593</v>
+        <v>-0.2504832693512</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.763524834184921</v>
+        <v>3.651030545993287</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.03822820576748143</v>
+        <v>1.911582824358852</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.3122878479294044</v>
+        <v>2.183817838963186</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.918842507899555</v>
+        <v>0.9638396580767932</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.946766479517571</v>
+        <v>-2.981241138619261</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-3.215464403583212</v>
+        <v>-2.286078973637274</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>-1.968845796401858</v>
+        <v>-1.081440902692144</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>-3.279220779220779</v>
+        <v>-2.406929336702667</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>-2.460756963817303</v>
+        <v>-1.567413522012579</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>0.2915451895043759</v>
+        <v>1.129891052071102</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>0.5074365704287018</v>
+        <v>1.344353279216875</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.2580985719842204</v>
+        <v>0.615543497860763</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>1.690197750892239</v>
+        <v>2.518898637090992</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>4.498967174098532</v>
+        <v>5.300878972278561</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>3.811903425042111</v>
+        <v>4.592132505175982</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>6.620686556434215</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.01007</t>
+          <t>X &gt; 0.0101</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.967848538741947</v>
+        <v>4.521889400921665</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.7147543465643835</v>
+        <v>-0.02509270359941951</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>9.803748343535055</v>
+        <v>10.54817018375632</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>8.003837802353175</v>
+        <v>8.880499167743793</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>8.755003851545041</v>
+        <v>9.680209844848761</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>5.681100472425022</v>
+        <v>6.611336999233941</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.525630820160977</v>
+        <v>0.4399109009797186</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-2.977755308392318</v>
+        <v>-2.015547176837508</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>0.3246014387397835</v>
+        <v>1.338188184459511</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.4483142372967066</v>
+        <v>0.5421366892401736</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.1742545951347836</v>
+        <v>0.8143717038445075</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-1.539960520321912</v>
+        <v>-0.537479067831093</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-4.837035630656295</v>
+        <v>-3.802908819690472</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-2.88420146362462</v>
+        <v>-1.900605246714974</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>-1.368431717726914</v>
+        <v>-0.4322219941914298</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>-2.947957839262187</v>
+        <v>-2.021455609780368</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>-1.994918454500528</v>
+        <v>-1.050067204301072</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>0.07415388515654797</v>
+        <v>0.9675863249459269</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>0.2900452660808739</v>
+        <v>1.1820485520917</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>0.4768910760489007</v>
+        <v>1.396634997150684</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>2.789098849793334</v>
+        <v>2.97972813017855</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>6.009956185087525</v>
+        <v>6.130372059836169</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>6.284430897569578</v>
+        <v>6.374006545114547</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>7.307499743247398</v>
+        <v>7.287136368029373</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.01087</t>
+          <t>X &gt; 0.0109</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>5.618412145827286</v>
+        <v>6.213470832865006</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.8892041586953567</v>
+        <v>-0.1299969784486095</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>8.783887903384759</v>
+        <v>9.590918675757372</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>8.070933883942018</v>
+        <v>8.998516476949149</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>6.500575510160175</v>
+        <v>7.503446141727856</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4.218405893788422</v>
+        <v>5.221355357482039</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-1.491814395040201</v>
+        <v>-0.4517754352384813</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-3.004593741027847</v>
+        <v>-1.976208073769051</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.7405971445905664</v>
+        <v>1.810257421280902</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.03231853144592378</v>
+        <v>1.014205926061564</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.2417411107159992</v>
+        <v>1.286440940665898</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.271576193966574</v>
+        <v>-0.2096532089273495</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-3.629306162057254</v>
+        <v>-2.544057521500065</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-2.615817137269282</v>
+        <v>-1.572779387811231</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>-2.039392533615263</v>
+        <v>-1.035421574574336</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>-3.914141414141412</v>
+        <v>-2.913141945998568</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>-2.813490649884322</v>
+        <v>-1.797510162601633</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.4491955512363717</v>
+        <v>0.5086301224806675</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.2333041703120458</v>
+        <v>0.723092349626441</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>0.937678794685425</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>1.880131274159091</v>
+        <v>2.809258683548599</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>5.507989016453699</v>
+        <v>6.392632746959173</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>5.782463728935753</v>
+        <v>6.63626723223755</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>6.941199376947033</v>
+        <v>7.693640433070037</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.01167</t>
+          <t>X &gt; 0.0117</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.431616654683978</v>
+        <v>2.171658986175117</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>6.905197618897368</v>
+        <v>7.813915191436806</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7.641518961773464</v>
+        <v>8.65008442120002</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>4.407177764588525</v>
+        <v>5.517383423957824</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>3.144868588367054</v>
+        <v>4.245745601384478</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>-1.974906182479813</v>
+        <v>-0.8350506965625257</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-3.702392989551726</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.7623550829993491</v>
+        <v>0.4165291982843868</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.08599539671699574</v>
+        <v>1.049049131636487</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.1880642454449273</v>
+        <v>1.321284146240821</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-2.989235882640749</v>
+        <v>-1.812440665373337</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-5.561673311815703</v>
+        <v>-4.35590421139554</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-4.333476825943457</v>
+        <v>-3.175566844257219</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>-3.542344761205179</v>
+        <v>-2.429149797570851</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>-5.84650856389986</v>
+        <v>-4.724988635894043</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>-4.531150338558497</v>
+        <v>-3.40029761904762</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>-3.186715680060843</v>
+        <v>-2.104610295637798</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>-1.521548936817673</v>
+        <v>-0.4615766399205867</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>-2.78397848916849</v>
+        <v>-1.67556162343304</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.4279739324968403</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>5.293281555369425</v>
+        <v>6.25325992465951</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>4.118480905532628</v>
+        <v>5.068322981366471</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>4.042648652309353</v>
+        <v>4.906183987077007</v>
       </c>
     </row>
   </sheetData>
@@ -5824,2461 +5824,2461 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.01158</t>
+          <t>X &lt; -0.01152</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.01765870763485822</v>
+        <v>-0.6854838709677367</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-4.700261592941196</v>
+        <v>-5.217104992385899</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.138280641972187</v>
+        <v>-6.471799094277479</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-8.300510023733771</v>
+        <v>-7.064201293085702</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-5.737749771643365</v>
+        <v>-4.482616576042183</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-5.550783585545986</v>
+        <v>-4.325682970044099</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-4.106193480007519</v>
+        <v>-3.69219355370538</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-2.913816689466486</v>
+        <v>-2.568542568542576</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-1.401741272257659</v>
+        <v>-1.012042230287037</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.645245183588273</v>
+        <v>-3.236665154077805</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-6.312362012014582</v>
+        <v>-5.821572996616332</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-3.649934944874346</v>
+        <v>-3.241012093944768</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-3.302508776436341</v>
+        <v>-2.927332782824109</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5.299941758881772</v>
+        <v>5.395861727171358</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>4.641798461301214</v>
+        <v>4.713707345286302</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>3.765597147950089</v>
+        <v>3.846439935534526</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>6.572856481560848</v>
+        <v>6.599702380952372</v>
       </c>
       <c r="T6" s="4" t="n">
-        <v>-0.884925398730914</v>
+        <v>-0.6760388670663602</v>
       </c>
       <c r="U6" s="4" t="n">
-        <v>-3.610210488394827</v>
+        <v>-3.318719497063448</v>
       </c>
       <c r="V6" s="4" t="n">
-        <v>-1.952776443132684</v>
+        <v>-1.67556162343304</v>
       </c>
       <c r="W6" s="4" t="n">
-        <v>0.4458538594895174</v>
+        <v>0.6141367323290865</v>
       </c>
       <c r="X6" s="4" t="n">
-        <v>1.84059613337454</v>
+        <v>1.967545638945232</v>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>2.115070845856593</v>
+        <v>2.21118012422361</v>
       </c>
       <c r="Z6" s="4" t="n">
-        <v>6.451003298515666</v>
+        <v>6.334755415648424</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.01078</t>
+          <t>X &lt; -0.01072</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.2053067327218798</v>
+        <v>0.3035271180432488</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-3.975623911781781</v>
+        <v>-3.788533563814468</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-6.695694242864057</v>
+        <v>-6.325278947757333</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-7.408648262306798</v>
+        <v>-6.917681146565556</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-5.180336170751509</v>
+        <v>-4.629136722562329</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-3.711318702602838</v>
+        <v>-3.190151834512953</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.099318002543818</v>
+        <v>-5.267285128796964</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.481425551192991</v>
+        <v>-1.726051726051729</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.1412370705769916</v>
+        <v>-0.3160715343163432</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-2.212854045314778</v>
+        <v>-2.394174311586958</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-4.536197000555454</v>
+        <v>-4.686041861085187</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-2.217543806600851</v>
+        <v>-2.398521251453921</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-2.042004574755673</v>
+        <v>-2.231362086853416</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>5.529124341005527</v>
+        <v>5.212711544021168</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>4.870981043424969</v>
+        <v>4.530557162136112</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>5.46536796536796</v>
+        <v>5.091861180955775</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>7.928853425793093</v>
+        <v>7.552083333333321</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>1.33050622846541</v>
+        <v>1.008942817915319</v>
       </c>
       <c r="U7" s="4" t="n">
-        <v>-1.051004988012856</v>
+        <v>-1.340697519041477</v>
       </c>
       <c r="V7" s="4" t="n">
-        <v>0.4345421206564666</v>
+        <v>0.1559402080687988</v>
       </c>
       <c r="W7" s="4" t="n">
-        <v>1.190697251391732</v>
+        <v>0.870546988739342</v>
       </c>
       <c r="X7" s="4" t="n">
-        <v>2.413552588683935</v>
+        <v>2.077435748835342</v>
       </c>
       <c r="Y7" s="4" t="n">
-        <v>2.688027301165988</v>
+        <v>2.321070234113719</v>
       </c>
       <c r="Z7" s="4" t="n">
-        <v>6.508298944046608</v>
+        <v>6.005085085978102</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.009979</t>
+          <t>X &lt; -0.009918</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.3799775482145691</v>
+        <v>0.2208141321044508</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-1.801710868303523</v>
+        <v>-2.17563033800802</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.32668643907364</v>
+        <v>-4.505593257103897</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-6.126596980255513</v>
+        <v>-6.173264273116423</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-3.201517887585389</v>
+        <v>-3.223015961602854</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-3.01455170148801</v>
+        <v>-3.06608235560477</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-2.10231500554081</v>
+        <v>-2.785895550633192</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>2.015077945310509</v>
+        <v>1.210259274775403</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>3.155466226126308</v>
+        <v>2.413457001663808</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1847483522876274</v>
+        <v>-0.5331321279641301</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.738994203352654</v>
+        <v>-2.411434747768403</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.1800585910015542</v>
+        <v>-0.537479067831093</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>1.254698721947626</v>
+        <v>0.4981664491267352</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>7.62702643890762</v>
+        <v>6.701545290919434</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>6.968883141327062</v>
+        <v>6.019390909034378</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>7.563270063270053</v>
+        <v>6.58069492785404</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>9.627155124094784</v>
+        <v>8.627352150537625</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>5.126710024669208</v>
+        <v>5.268661593763127</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>3.144799207791337</v>
+        <v>3.332586186500301</v>
       </c>
       <c r="V8" s="4" t="n">
-        <v>4.430546116660459</v>
+        <v>4.622441448763581</v>
       </c>
       <c r="W8" s="4" t="n">
-        <v>3.887999948694429</v>
+        <v>4.054996947382847</v>
       </c>
       <c r="X8" s="4" t="n">
-        <v>4.91105508618643</v>
+        <v>5.055103242631866</v>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>5.185529798668483</v>
+        <v>5.298737727910243</v>
       </c>
       <c r="Z8" s="4" t="n">
-        <v>8.406400842148507</v>
+        <v>8.362405185233676</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.009177</t>
+          <t>X &lt; -0.009117</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-4.992198464783314</v>
+        <v>-3.985104604216794</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.426074362232235</v>
+        <v>-4.231011439920664</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-4.062291609461425</v>
+        <v>-3.715794037387461</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-3.874344728003265</v>
+        <v>-3.423240483983292</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-2.408333398748731</v>
+        <v>-1.928887119657858</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-3.122268113552252</v>
+        <v>-2.656909265872152</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-1.592824496050305</v>
+        <v>-1.682079773680101</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.8562367864693456</v>
+        <v>0.6678670395484474</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>1.806814877474963</v>
+        <v>1.680751701444947</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.7842826167433472</v>
+        <v>-1.770167050411558</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.237495701854158</v>
+        <v>-4.152799292444385</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-2.607154196211241</v>
+        <v>-2.659469742490913</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-1.912134444885538</v>
+        <v>-2.004450355516902</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>6.048604860486051</v>
+        <v>5.711917352961486</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>2.663188835632774</v>
+        <v>2.374895714439262</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>4.166666666666664</v>
+        <v>3.821155485471316</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>4.941840438780105</v>
+        <v>4.602230825958699</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>3.01881791677711</v>
+        <v>3.584390968584707</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>1.416527479519615</v>
+        <v>2.028941691305697</v>
       </c>
       <c r="V9" s="4" t="n">
-        <v>2.512464198578542</v>
+        <v>3.128483888577072</v>
       </c>
       <c r="W9" s="4" t="n">
-        <v>1.060827121521612</v>
+        <v>1.676083634983947</v>
       </c>
       <c r="X9" s="4" t="n">
-        <v>2.803162978294331</v>
+        <v>3.370832617453445</v>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>3.077637690776385</v>
+        <v>3.614467102731822</v>
       </c>
       <c r="Z9" s="4" t="n">
-        <v>5.729078164825829</v>
+        <v>6.107195365079527</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.008375</t>
+          <t>X &lt; -0.008317</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-5.203347113431967</v>
+        <v>-5.081088266572138</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-3.194373911781781</v>
+        <v>-3.019302794583702</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-3.851142960812773</v>
+        <v>-3.504766127244515</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-3.001596980255513</v>
+        <v>-2.558706787591191</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.9936374528027869</v>
+        <v>-0.5265726199982197</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-0.02542126670540767</v>
+        <v>0.399591755230631</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>1.220346584837309</v>
+        <v>1.142971281459445</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.729536714887381</v>
+        <v>1.607281607281607</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2.558425471605247</v>
+        <v>2.504441286196482</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2107066459624463</v>
+        <v>0.1699282525155965</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-1.877438436285075</v>
+        <v>-1.865529040572369</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.206016884676373</v>
+        <v>0.1655813126486336</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>1.445059542229714</v>
+        <v>1.358381502890175</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>7.523193264208317</v>
+        <v>7.263993595303212</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>4.502845242218307</v>
+        <v>4.27414690572585</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>5.884633738964439</v>
+        <v>5.604681693776286</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>6.538118176790135</v>
+        <v>6.270032051282051</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>4.071072748559494</v>
+        <v>4.598686407658903</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>2.712160979877524</v>
+        <v>3.274687096343143</v>
       </c>
       <c r="V10" s="4" t="n">
-        <v>4.473809939451847</v>
+        <v>5.02773507986366</v>
       </c>
       <c r="W10" s="4" t="n">
-        <v>3.143862196682669</v>
+        <v>3.69105980925216</v>
       </c>
       <c r="X10" s="4" t="n">
-        <v>3.855417810076716</v>
+        <v>4.385128056527641</v>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>4.917294097361918</v>
+        <v>5.397993311036792</v>
       </c>
       <c r="Z10" s="4" t="n">
-        <v>7.203666568548094</v>
+        <v>7.543546624439635</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.007573</t>
+          <t>X &lt; -0.007516</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-5.364985044466451</v>
+        <v>-4.200521464952708</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-2.941141153161091</v>
+        <v>-2.472744090130256</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-3.689505029778289</v>
+        <v>-3.069543455179733</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-3.023148704393449</v>
+        <v>-2.346156180303737</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-2.669284004526929</v>
+        <v>-2.621714320403072</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.2763028712256315</v>
+        <v>0.5371363298612977</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.5915189382931274</v>
+        <v>0.4043059732577206</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2.396640826873387</v>
+        <v>2.086140496736519</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>3.132572453232534</v>
+        <v>2.876321062049769</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>2.359656777196044</v>
+        <v>2.080269566830431</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.5503830860246381</v>
+        <v>0.3657496145473402</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.9660781270210848</v>
+        <v>0.7514193157051849</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>1.926249393498303</v>
+        <v>1.623282165141831</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>7.260726072607255</v>
+        <v>6.673061348741832</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>5.213693886137825</v>
+        <v>4.666403655598494</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>6.502525252525245</v>
+        <v>5.889959330047304</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>5.674163671103344</v>
+        <v>5.123827262693148</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>3.485989633948819</v>
+        <v>3.666439846273278</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>3.007436570428702</v>
+        <v>3.218650417789902</v>
       </c>
       <c r="V11" s="4" t="n">
-        <v>4.583171269285614</v>
+        <v>4.757740174107177</v>
       </c>
       <c r="W11" s="4" t="n">
-        <v>4.040625101319584</v>
+        <v>4.190295672726442</v>
       </c>
       <c r="X11" s="4" t="n">
-        <v>4.65922358435494</v>
+        <v>4.777384806400285</v>
       </c>
       <c r="Y11" s="4" t="n">
-        <v>6.322587185725865</v>
+        <v>6.345522602936946</v>
       </c>
       <c r="Z11" s="4" t="n">
-        <v>7.63564382139149</v>
+        <v>7.507886919905765</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.006771</t>
+          <t>X &lt; -0.006715</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-3.08529155787641</v>
+        <v>-3.004992319508446</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.4688205326626615</v>
+        <v>-0.5627271122015713</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.1419125947427844</v>
+        <v>-1.279786805491</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.5400696864111509</v>
+        <v>0.2783486301093774</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.2042792138638774</v>
+        <v>-0.5348439185921023</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.942455828266667</v>
+        <v>2.624123979762857</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>1.941394094348063</v>
+        <v>1.829041967530138</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.910373660830949</v>
+        <v>3.14574314574314</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>4.513658595554631</v>
+        <v>3.273672055427248</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>3.740742919518141</v>
+        <v>2.47762056020791</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.644016044826131</v>
+        <v>-0.4933876684309979</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>2.050659899805105</v>
+        <v>0.8516519987193263</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.174688844184935</v>
+        <v>2.439462583971256</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>6.324396484592285</v>
+        <v>5.434471765781389</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>3.419062175775771</v>
+        <v>2.590155221734172</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>3.45165134490977</v>
+        <v>2.610918700013301</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>3.317734207932297</v>
+        <v>2.507038288288292</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>2.089297998493137</v>
+        <v>1.833613642586144</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>1.743391626608485</v>
+        <v>1.507535329191384</v>
       </c>
       <c r="V12" s="4" t="n">
-        <v>3.053832942194475</v>
+        <v>2.803202855331449</v>
       </c>
       <c r="W12" s="4" t="n">
-        <v>2.511286774228445</v>
+        <v>2.235758353950715</v>
       </c>
       <c r="X12" s="4" t="n">
-        <v>4.120834071246314</v>
+        <v>4.322757994157591</v>
       </c>
       <c r="Y12" s="4" t="n">
-        <v>4.395308783728368</v>
+        <v>3.485311398354888</v>
       </c>
       <c r="Z12" s="4" t="n">
-        <v>5.443072036123077</v>
+        <v>4.944794025687038</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.005969</t>
+          <t>X &lt; -0.005914</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-3.640847113431967</v>
+        <v>-3.107844119414949</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.18990962606749</v>
+        <v>-1.61462052033621</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.181500103669912</v>
+        <v>-2.86931462222779</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-1.662311265969805</v>
+        <v>-1.287803777557755</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1.105244595659926</v>
+        <v>-0.6937967002657786</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.2268208857609579</v>
+        <v>0.577623330642119</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2.412089508863701</v>
+        <v>2.402628654653945</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>2.584328514561072</v>
+        <v>2.534389433952754</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>2.625815696475776</v>
+        <v>2.662318343636862</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.9519991195383852</v>
+        <v>0.9929044030026759</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.476643941002386</v>
+        <v>-1.354947918637542</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.04640845735141141</v>
+        <v>0.1151950177208647</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>1.175498642747556</v>
+        <v>1.183709013807203</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.48998700775055</v>
+        <v>3.118881065911218</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>1.47437764682158</v>
+        <v>1.126683015903886</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>2.068764568764571</v>
+        <v>1.687987034723548</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>1.482358744004294</v>
+        <v>1.147425400291112</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>1.377518040183112</v>
+        <v>1.451222517836939</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>0.2359433577590195</v>
+        <v>0.3556410768604508</v>
       </c>
       <c r="V13" s="4" t="n">
-        <v>0.8752778555098502</v>
+        <v>1.006908744626848</v>
       </c>
       <c r="W13" s="4" t="n">
-        <v>-0.1197570002389838</v>
+        <v>0.002783020538700498</v>
       </c>
       <c r="X13" s="4" t="n">
-        <v>1.614351789483138</v>
+        <v>1.674345389413098</v>
       </c>
       <c r="Y13" s="4" t="n">
-        <v>0.5313604386167725</v>
+        <v>0.6079362065692067</v>
       </c>
       <c r="Z13" s="4" t="n">
-        <v>1.812994248741916</v>
+        <v>1.755840880402012</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.005167</t>
+          <t>X &lt; -0.005113</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.6557724865662991</v>
+        <v>-0.2579551952638823</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.248256685233144</v>
+        <v>1.685918990930055</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-0.1897623637978469</v>
+        <v>0.06626138538884874</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-1.2758507115988</v>
+        <v>-0.8911043170690149</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-0.8653725274296562</v>
+        <v>-0.436735449869083</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.402481355017436</v>
+        <v>2.121203476842361</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2.727066139629812</v>
+        <v>2.791322929811102</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>3.200734394124851</v>
+        <v>3.585303585303578</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>2.114402027167372</v>
+        <v>2.614331396086591</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.2136668022587074</v>
+        <v>0.7193788019661582</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-2.519792352571848</v>
+        <v>-1.938789113832442</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.670722207147669</v>
+        <v>-1.482770335703009</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.9141850258834836</v>
+        <v>-0.7661606216519417</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>1.726134877638707</v>
+        <v>1.549707881017504</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1.067991580058148</v>
+        <v>0.8675534991324483</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>1.285020011435101</v>
+        <v>1.062557151651745</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>0.7737443838915965</v>
+        <v>0.5923763736263723</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>0.6689036800704145</v>
+        <v>0.8257926347651363</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>-1.379355882401491</v>
+        <v>-1.15754733589128</v>
       </c>
       <c r="V14" s="4" t="n">
-        <v>-0.8151515818674255</v>
+        <v>-0.5766605245319312</v>
       </c>
       <c r="W14" s="4" t="n">
-        <v>-2.112414730965533</v>
+        <v>-2.243006124813775</v>
       </c>
       <c r="X14" s="4" t="n">
-        <v>-0.6788267301104796</v>
+        <v>-0.4866668152672204</v>
       </c>
       <c r="Y14" s="4" t="n">
-        <v>-0.9375138243751309</v>
+        <v>-1.341933428889938</v>
       </c>
       <c r="Z14" s="4" t="n">
-        <v>0.3505783376568061</v>
+        <v>-0.4051713242783066</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.004365</t>
+          <t>X &lt; -0.004312</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>329</v>
+        <v>349</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.6646566372414924</v>
+        <v>-0.1140552995391744</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>2.571995135837263</v>
+        <v>2.782895007614101</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-0.1897623637978469</v>
+        <v>0.09962947715109038</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-0.9027163832405876</v>
+        <v>-0.2070584359428409</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.2540304576449728</v>
+        <v>0.6602405668149629</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.10781226622872</v>
+        <v>2.698467664421734</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2.712389809164002</v>
+        <v>3.049517457346603</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4.235980166212727</v>
+        <v>4.75032767296377</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>3.076266146926237</v>
+        <v>3.445591826200889</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.402449569988839</v>
+        <v>1.789941477113359</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.32649379085224</v>
+        <v>-0.8031530211762998</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.004642593699636</v>
+        <v>-0.5066690730687995</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-0.4499219585766667</v>
+        <v>-0.1888964340725678</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>1.017020131016125</v>
+        <v>1.282067212230707</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>1.265221244311704</v>
+        <v>1.459511684213844</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>0.04691934450242741</v>
+        <v>0.5881509465865165</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>-0.0869977924750458</v>
+        <v>0.1977375835721134</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>0.1102763073291513</v>
+        <v>0.6379193809893096</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>-1.78863593712417</v>
+        <v>-1.153349050890718</v>
       </c>
       <c r="V15" s="4" t="n">
-        <v>-0.6954457162800054</v>
+        <v>-0.3656967032529224</v>
       </c>
       <c r="W15" s="4" t="n">
-        <v>-2.144336295122173</v>
+        <v>-1.792740058501863</v>
       </c>
       <c r="X15" s="4" t="n">
-        <v>-0.4074934347790062</v>
+        <v>0.1378280785686457</v>
       </c>
       <c r="Y15" s="4" t="n">
-        <v>0.350364963503651</v>
+        <v>0.6679955151364254</v>
       </c>
       <c r="Z15" s="4" t="n">
-        <v>1.368757634292528</v>
+        <v>1.651988326004549</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003564</t>
+          <t>X &lt; -0.003511</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>430</v>
+        <v>449</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.279061353387256</v>
+        <v>1.346262160778288</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.31728226670792</v>
+        <v>1.98924421396331</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.008375387811078</v>
+        <v>0.9567723342939587</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.212852561028889</v>
+        <v>1.253259024374614</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.4183464921513433</v>
+        <v>0.3110342176086078</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>3.034923560880799</v>
+        <v>2.820355846373346</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>3.78212313696185</v>
+        <v>3.138859580243079</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4.655985424927664</v>
+        <v>4.170242032157397</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>3.084569381035919</v>
+        <v>2.739150897298067</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>1.389994718824312</v>
+        <v>1.274947954417264</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.870507850995331</v>
+        <v>-1.348139970844777</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.2275982682682169</v>
+        <v>-0.5111361792136222</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.6303807766135137</v>
+        <v>0.1557088970995295</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>1.473689035570224</v>
+        <v>0.7983434325483856</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>1.509990182434109</v>
+        <v>1.007057647545288</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>1.178451178451184</v>
+        <v>1.122927367923964</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>1.04453404147371</v>
+        <v>1.019046956198956</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>0.4767303746895593</v>
+        <v>0.6634457018168689</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>-0.6962671332750077</v>
+        <v>-0.4583949663602951</v>
       </c>
       <c r="V16" s="4" t="n">
-        <v>-0.04645836034401896</v>
+        <v>0.201625777139661</v>
       </c>
       <c r="W16" s="4" t="n">
-        <v>-0.820486009791523</v>
+        <v>-0.5885358734615593</v>
       </c>
       <c r="X16" s="4" t="n">
-        <v>1.187001362132712</v>
+        <v>1.340755947567565</v>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>1.371246634037298</v>
+        <v>1.361673283625457</v>
       </c>
       <c r="Z16" s="4" t="n">
-        <v>2.134997826559449</v>
+        <v>1.867685736997458</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.002762</t>
+          <t>X &lt; -0.002711</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>558</v>
+        <v>586</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.6801405408890204</v>
+        <v>1.187103001619128</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>1.050831114673244</v>
+        <v>1.279034003753097</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7701026222260978</v>
+        <v>0.7000155775371937</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.7638623837020901</v>
+        <v>0.8787525381930053</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.9581072468438521</v>
+        <v>0.6989814869118121</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2.662631830639725</v>
+        <v>2.480041017343737</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.88170806358864</v>
+        <v>2.024517578964996</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.135411512452578</v>
+        <v>2.499484642341784</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.21857008496729</v>
+        <v>1.607005388760584</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>1.268034515502741</v>
+        <v>0.4708178391194764</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.766964456900169</v>
+        <v>-1.637899527228569</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.3352342866359095</v>
+        <v>-0.7975952041905714</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.9574870368355803</v>
+        <v>0.6428789475239043</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>1.200120012001207</v>
+        <v>0.8371098987949495</v>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>0.5419767144206489</v>
+        <v>0.1549555169098937</v>
       </c>
       <c r="R17" s="4" t="n">
-        <v>0.9581105169340418</v>
+        <v>0.7162595357295558</v>
       </c>
       <c r="S17" s="4" t="n">
-        <v>1.358952738245343</v>
+        <v>1.12432451649601</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>0.897605795564985</v>
+        <v>0.6501434830067723</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>0.4004846987709456</v>
+        <v>0.1820118534972579</v>
       </c>
       <c r="V17" s="4" t="n">
-        <v>0.7655836281685637</v>
+        <v>0.5672467627200533</v>
       </c>
       <c r="W17" s="4" t="n">
-        <v>-0.3117218980862404</v>
+        <v>-0.5121431311521434</v>
       </c>
       <c r="X17" s="4" t="n">
-        <v>1.504461679593028</v>
+        <v>1.289827452694624</v>
       </c>
       <c r="Y17" s="4" t="n">
-        <v>2.067717378530489</v>
+        <v>1.533461937973001</v>
       </c>
       <c r="Z17" s="4" t="n">
-        <v>1.923278229993642</v>
+        <v>1.371322943683538</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.00196</t>
+          <t>X &lt; -0.00191</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>739</v>
+        <v>765</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.305676950739155</v>
+        <v>1.839993245949067</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.9709001523893406</v>
+        <v>1.204981351879439</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.196775490933256</v>
+        <v>-0.5685194944998244</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.240385467537969</v>
+        <v>-0.8304350593194698</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.308438322950046</v>
+        <v>-1.294803089138959</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.5610398592999601</v>
+        <v>0.6259539347178134</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.4030746485823329</v>
+        <v>-0.5597530775149053</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.01014515373809388</v>
+        <v>-0.1397848855476056</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.429255503756707</v>
+        <v>-0.5333683617826566</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.202171179793197</v>
+        <v>-1.199041760522206</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-2.003380354835585</v>
+        <v>-1.839453421276417</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-1.475678145380343</v>
+        <v>-1.129859538927981</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-0.7730178414351485</v>
+        <v>-0.547623719041944</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.6458327773478061</v>
+        <v>-0.5891989637716861</v>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>-1.034434295952629</v>
+        <v>-1.271353345656742</v>
       </c>
       <c r="R18" s="4" t="n">
-        <v>-0.979130931961123</v>
+        <v>-0.9714872353338109</v>
       </c>
       <c r="S18" s="4" t="n">
-        <v>-0.9782771794507283</v>
+        <v>-0.9446486928104534</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-0.6788052148082926</v>
+        <v>-0.5546569809785922</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>-1.675851839274799</v>
+        <v>-1.778103250564854</v>
       </c>
       <c r="V18" s="4" t="n">
-        <v>-0.8151515818674255</v>
+        <v>-0.909922034264028</v>
       </c>
       <c r="W18" s="4" t="n">
-        <v>-1.492468639321324</v>
+        <v>-1.346647581396397</v>
       </c>
       <c r="X18" s="4" t="n">
-        <v>-0.1400341754291432</v>
+        <v>-0.1146205608680262</v>
       </c>
       <c r="Y18" s="4" t="n">
-        <v>0.08009469323338436</v>
+        <v>0.1290139244103514</v>
       </c>
       <c r="Z18" s="4" t="n">
-        <v>0.2204055113629195</v>
+        <v>0.0975938843692532</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001158</t>
+          <t>X &lt; -0.001109</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1004</v>
+        <v>1049</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.3039260621104347</v>
+        <v>0.383579515976443</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.2198351207947269</v>
+        <v>-0.09535174563264803</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.2187681063809066</v>
+        <v>-0.02428827176665749</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-0.09892899606579419</v>
+        <v>-0.3749663574052633</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-0.4347194686130678</v>
+        <v>-0.7878483461695822</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.1044006917515716</v>
+        <v>0.1811682034737458</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.1166768812888321</v>
+        <v>-0.4239802854921138</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.2981809808887874</v>
+        <v>-0.01015039037852716</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.1985618817095727</v>
+        <v>-0.2624496175765572</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.07881365557567932</v>
+        <v>-0.3387448061098794</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.696726263165985</v>
+        <v>-0.9228370988319057</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-1.371907777614965</v>
+        <v>-1.621964474897155</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.6531156858667799</v>
+        <v>-0.8320946875860145</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.915374556323556</v>
+        <v>-1.215877344052942</v>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>-0.8783837923351001</v>
+        <v>-1.040071764069552</v>
       </c>
       <c r="R19" s="4" t="n">
-        <v>-1.475655261653273</v>
+        <v>-1.527385476422438</v>
       </c>
       <c r="S19" s="4" t="n">
-        <v>-1.609572398630746</v>
+        <v>-1.821923657451542</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-1.118583906821343</v>
+        <v>-1.382834454700856</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>-1.200607123712317</v>
+        <v>-1.359029996859171</v>
       </c>
       <c r="V19" s="4" t="n">
-        <v>-1.113066179682718</v>
+        <v>-1.33510132110429</v>
       </c>
       <c r="W19" s="4" t="n">
-        <v>-1.059783152018156</v>
+        <v>-1.235243629920681</v>
       </c>
       <c r="X19" s="4" t="n">
-        <v>-0.4807697887398277</v>
+        <v>-0.5477750746595618</v>
       </c>
       <c r="Y19" s="4" t="n">
-        <v>-0.5451574245560522</v>
+        <v>-0.780785012641438</v>
       </c>
       <c r="Z19" s="4" t="n">
-        <v>-0.1637143016718099</v>
+        <v>-0.5616084683226958</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003561</t>
+          <t>X &lt; -0.000308</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1379</v>
+        <v>1425</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1541468977597873</v>
+        <v>-0.09314937619422636</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.05315306663548824</v>
+        <v>0.1166268267015695</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.5540317297112622</v>
+        <v>-0.2315121845344947</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.6910318254679026</v>
+        <v>-0.5065300738652851</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.314799259858226</v>
+        <v>-1.092752250423665</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.4396863963884101</v>
+        <v>-0.3384612469733099</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-0.9550844423044822</v>
+        <v>-0.8540184513793392</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3681192468268506</v>
+        <v>-0.2109002109002134</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.5741375034774165</v>
+        <v>-0.3626915809363922</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3369521694129034</v>
+        <v>-0.06961526904331805</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.072993537351984</v>
+        <v>-0.9870233615068571</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-1.310797123680885</v>
+        <v>-1.154177360051207</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-0.008561139578134203</v>
+        <v>0.04185489224592231</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.7653042961563017</v>
+        <v>-0.6557950953334029</v>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>-0.6280752148503765</v>
+        <v>-0.4555974032610877</v>
       </c>
       <c r="R20" s="4" t="n">
-        <v>-0.6121409320975459</v>
+        <v>-0.3851769749042546</v>
       </c>
       <c r="S20" s="4" t="n">
-        <v>-0.9205460893083028</v>
+        <v>-0.7695622954651711</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-0.9530278929847711</v>
+        <v>-0.7621939462088179</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>-0.3753420113368549</v>
+        <v>-0.2672268102271502</v>
       </c>
       <c r="V20" s="4" t="n">
-        <v>-0.1884962013688281</v>
+        <v>-0.1227665923771326</v>
       </c>
       <c r="W20" s="4" t="n">
-        <v>-0.7310423693348582</v>
+        <v>-0.6200848665489005</v>
       </c>
       <c r="X20" s="4" t="n">
-        <v>-0.1847904151623254</v>
+        <v>-0.0641113436233951</v>
       </c>
       <c r="Y20" s="4" t="n">
-        <v>0.06050989103988513</v>
+        <v>0.1093969144460019</v>
       </c>
       <c r="Z20" s="4" t="n">
-        <v>0.3180424999830649</v>
+        <v>0.2695925083802564</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0004458</t>
+          <t>X &lt; 0.0004929</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1858</v>
+        <v>1905</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.6326571600723057</v>
+        <v>0.8607083422385386</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.8079143030765792</v>
+        <v>0.9038543402522734</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.1478543653904367</v>
+        <v>0.1705366721458859</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.1601873964165037</v>
+        <v>0.2329147364246893</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.7641531028830499</v>
+        <v>-0.7963654576407464</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.5232939367207123</v>
+        <v>0.5381737998178977</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.1111085686996702</v>
+        <v>0.03373568946523875</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1750725576412862</v>
+        <v>-0.1370587361178153</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3257664510889171</v>
+        <v>0.3866427667243215</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.2495281598327068</v>
+        <v>0.3007498119085881</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.356676788863652</v>
+        <v>-0.3391496607898503</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.03915871834202278</v>
+        <v>-0.009701759439039392</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3964587332728584</v>
+        <v>0.4992929748650283</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.007444353457898956</v>
+        <v>0.07241159240046358</v>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>-0.1822364158075231</v>
+        <v>-0.1593168512827319</v>
       </c>
       <c r="R21" s="4" t="n">
-        <v>-0.1249064218989062</v>
+        <v>-0.01751991164503863</v>
       </c>
       <c r="S21" s="4" t="n">
-        <v>-0.4956076585282858</v>
+        <v>-0.3527785064707984</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-0.3855101570834805</v>
+        <v>-0.1708672286313515</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>-0.0621496735261573</v>
+        <v>0.09606089568126208</v>
       </c>
       <c r="V21" s="4" t="n">
-        <v>-0.09024206882411789</v>
+        <v>-0.004148042260794682</v>
       </c>
       <c r="W21" s="4" t="n">
-        <v>-0.4178500315241607</v>
+        <v>-0.2043312634736481</v>
       </c>
       <c r="X21" s="4" t="n">
-        <v>-0.4617441575805543</v>
+        <v>-0.3319596825957731</v>
       </c>
       <c r="Y21" s="4" t="n">
-        <v>-0.1552832344522415</v>
+        <v>0.01660659701629186</v>
       </c>
       <c r="Z21" s="4" t="n">
-        <v>-0.1452735329919648</v>
+        <v>-0.06194499680001542</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.001248</t>
+          <t>X &lt; 0.001294</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2297</v>
+        <v>2336</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.3548332321403862</v>
+        <v>0.6240399385560664</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.8212645929718931</v>
+        <v>0.8265238585589927</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.09867869936881135</v>
+        <v>0.08225085407276822</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.1017767221666261</v>
+        <v>0.1090509865495619</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.4502767261591956</v>
+        <v>-0.3556324490580494</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.4532676125676289</v>
+        <v>0.3360352095616435</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.008907105681302596</v>
+        <v>0.03353534032346062</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.05856758689456854</v>
+        <v>-0.03413750216819977</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.3415556999107565</v>
+        <v>0.2885974285615802</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.3738527026403489</v>
+        <v>0.4127741438256578</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.109504219300149</v>
+        <v>-0.01582944439390133</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2463263796120714</v>
+        <v>0.1163137569763038</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.6675688379427456</v>
+        <v>0.5812679247518275</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.005159004827966385</v>
+        <v>-0.02611911129816491</v>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>0.2051301769662075</v>
+        <v>0.1715828031617548</v>
       </c>
       <c r="R22" s="4" t="n">
-        <v>0.3912934733959972</v>
+        <v>0.305536394630991</v>
       </c>
       <c r="S22" s="4" t="n">
-        <v>0.3268509085363362</v>
+        <v>0.2270156405871475</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>0.004713377248833694</v>
+        <v>-0.008801912404265977</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>0.04676729620010178</v>
+        <v>0.03457391611020455</v>
       </c>
       <c r="V22" s="4" t="n">
-        <v>-0.04484805438588069</v>
+        <v>-0.1357840357512572</v>
       </c>
       <c r="W22" s="4" t="n">
-        <v>-0.1960898745258177</v>
+        <v>-0.2327409408958943</v>
       </c>
       <c r="X22" s="4" t="n">
-        <v>-0.2459888268383352</v>
+        <v>-0.3253818016073708</v>
       </c>
       <c r="Y22" s="4" t="n">
-        <v>0.0979715779510002</v>
+        <v>0.04662238842067978</v>
       </c>
       <c r="Z22" s="4" t="n">
-        <v>0.04815047257902449</v>
+        <v>-0.04733851781536913</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.00205</t>
+          <t>X &lt; 0.002095</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2624</v>
+        <v>2657</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.007236212599259773</v>
+        <v>-0.01255575313860646</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.6627706357380916</v>
+        <v>0.6210329533753622</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>0.1545388573690403</v>
+        <v>0.1343424277518892</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.006854653616635176</v>
+        <v>0.04873812351863904</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.6078971155538255</v>
+        <v>-0.505277043147089</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.2067622056221126</v>
+        <v>0.1963444037796904</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.01286103895374424</v>
+        <v>0.02123640832061113</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>0.1857994847725664</v>
+        <v>0.2243948311363937</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.3629646100952755</v>
+        <v>0.4111767388292691</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3712361241968054</v>
+        <v>0.3861662873443379</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.3256710971652907</v>
+        <v>0.3426564746997656</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.5249264890609382</v>
+        <v>0.5002803720288753</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5642830942458019</v>
+        <v>0.5481789522525133</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.06174001430561304</v>
+        <v>0.05949078104431038</v>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>0.2781214315539629</v>
+        <v>0.2252903568693156</v>
       </c>
       <c r="R23" s="4" t="n">
-        <v>0.1727526309116243</v>
+        <v>0.1331198346815725</v>
       </c>
       <c r="S23" s="4" t="n">
-        <v>-0.01457301078402651</v>
+        <v>-0.06123998246933127</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-0.04331021384417966</v>
+        <v>-0.05919235394026146</v>
       </c>
       <c r="U23" s="4" t="n">
-        <v>-0.01767758482243664</v>
+        <v>0.02714516459068506</v>
       </c>
       <c r="V23" s="4" t="n">
-        <v>0.039543134108186</v>
+        <v>0.07590240708327656</v>
       </c>
       <c r="W23" s="4" t="n">
-        <v>-0.3888043281098419</v>
+        <v>-0.303501477524236</v>
       </c>
       <c r="X23" s="4" t="n">
-        <v>-0.5562498860690326</v>
+        <v>-0.4316804171657012</v>
       </c>
       <c r="Y23" s="4" t="n">
-        <v>-0.1829683698296805</v>
+        <v>-0.07517911473156857</v>
       </c>
       <c r="Z23" s="4" t="n">
-        <v>-0.3504672897196244</v>
+        <v>-0.2903319546403011</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002851</t>
+          <t>X &lt; 0.002895</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2842</v>
+        <v>2875</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.1139555411261881</v>
+        <v>0.1866550398452063</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.4618324124669968</v>
+        <v>0.5465268852356218</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.04838605763206516</v>
+        <v>0.03624710969132394</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.04268089633942651</v>
+        <v>0.05050909158665462</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.343506333921674</v>
+        <v>-0.2403719603535777</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.03797502570452593</v>
+        <v>0.004998455068324859</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.2244168365299828</v>
+        <v>-0.2171564800523953</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.02771650210416965</v>
+        <v>-0.0872094330038351</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-0.2462790873837122</v>
+        <v>-0.3551368088386866</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.1936123413094961</v>
+        <v>-0.3349876836438384</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.2146250896352555</v>
+        <v>-0.3201374951808305</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.05258643659615814</v>
+        <v>-0.1610418042691037</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.1419265011810111</v>
+        <v>0.07588583564580631</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1635694961990026</v>
+        <v>-0.2560106722738666</v>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>-0.1693470495346929</v>
+        <v>-0.2241054489260819</v>
       </c>
       <c r="R24" s="4" t="n">
-        <v>-0.1506376506376483</v>
+        <v>-0.1626807148074931</v>
       </c>
       <c r="S24" s="4" t="n">
-        <v>-0.4041759044272553</v>
+        <v>-0.4196857283350752</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-0.4179736022061959</v>
+        <v>-0.3933007718282724</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>-0.2163863389177507</v>
+        <v>-0.2278645375040824</v>
       </c>
       <c r="V24" s="4" t="n">
-        <v>-0.1493028568616239</v>
+        <v>-0.2013235612866993</v>
       </c>
       <c r="W24" s="4" t="n">
-        <v>-0.4458033306272924</v>
+        <v>-0.4560508979697317</v>
       </c>
       <c r="X24" s="4" t="n">
-        <v>-0.535924094969964</v>
+        <v>-0.5107303429803949</v>
       </c>
       <c r="Y24" s="4" t="n">
-        <v>-0.2757342274917747</v>
+        <v>-0.2465985366148615</v>
       </c>
       <c r="Z24" s="4" t="n">
-        <v>-0.6121667971087845</v>
+        <v>-0.6317042116807627</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.003653</t>
+          <t>X &lt; 0.003696</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2985</v>
+        <v>3013</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.1810999411099417</v>
+        <v>-0.180728244260898</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>0.3671381514461771</v>
+        <v>0.3492837787506531</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.1123224186812379</v>
+        <v>0.002946476774162932</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.2503593967008655</v>
+        <v>0.1215459850403349</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.1520311424464751</v>
+        <v>-0.2016170475178924</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.07955184631899215</v>
+        <v>-0.1913623550367873</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.0002808324765553039</v>
+        <v>-0.07641699208998176</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.07441860465116434</v>
+        <v>0.03375107438535707</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-0.09836563724206826</v>
+        <v>-0.1499895440440042</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.05167299820978144</v>
+        <v>-0.100891836486305</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.1920259897177701</v>
+        <v>-0.2395624146057429</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.2179079284602921</v>
+        <v>-0.2326476499203807</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.08636422178643954</v>
+        <v>-0.09051032641845325</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.3211042547140437</v>
+        <v>-0.3193694347838374</v>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>-0.3915145632069468</v>
+        <v>-0.3863068411231296</v>
       </c>
       <c r="R25" s="4" t="n">
-        <v>-0.4122103386809286</v>
+        <v>-0.4676565639924348</v>
       </c>
       <c r="S25" s="4" t="n">
-        <v>-0.4595151431171089</v>
+        <v>-0.5190218891465221</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-0.4776855797263906</v>
+        <v>-0.533087054134441</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>-0.3423459655365022</v>
+        <v>-0.3986001732318343</v>
       </c>
       <c r="V25" s="4" t="n">
-        <v>-0.2361058391481166</v>
+        <v>-0.2971986071389878</v>
       </c>
       <c r="W25" s="4" t="n">
-        <v>-0.4439799856951439</v>
+        <v>-0.4336086257610958</v>
       </c>
       <c r="X25" s="4" t="n">
-        <v>-0.6003735588210546</v>
+        <v>-0.5223856569562173</v>
       </c>
       <c r="Y25" s="4" t="n">
-        <v>-0.4065004082311106</v>
+        <v>-0.3587317157612304</v>
       </c>
       <c r="Z25" s="4" t="n">
-        <v>-0.7304924153477614</v>
+        <v>-0.7004728807813194</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.004455</t>
+          <t>X &lt; 0.004497</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3088</v>
+        <v>3114</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.009844427256354038</v>
+        <v>-0.003085911784076245</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>0.2393053031474395</v>
+        <v>0.2465541554837785</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.009594889203320633</v>
+        <v>-0.09747144362563631</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.2481615516182814</v>
+        <v>0.1575396216012734</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.04115407971492147</v>
+        <v>-0.004419166810286868</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.05308114875352743</v>
+        <v>-0.02126174451140628</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.265774379301142</v>
+        <v>0.1918776466597407</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.2316213117088495</v>
+        <v>0.1927230115149499</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.03070930047474718</v>
+        <v>-0.07671157628630709</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.1822677628995848</v>
+        <v>0.1367187373745224</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.08801749462678998</v>
+        <v>0.0435216016836506</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.07525240971119018</v>
+        <v>-0.1187263796590514</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.1114584889720831</v>
+        <v>0.1291881610207781</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.006393923215377129</v>
+        <v>0.02785477414999349</v>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>-0.05116399499913626</v>
+        <v>-0.02684358360544081</v>
       </c>
       <c r="R26" s="4" t="n">
-        <v>-0.08359034611054028</v>
+        <v>-0.05523992897775543</v>
       </c>
       <c r="S26" s="4" t="n">
-        <v>-0.1336722837914408</v>
+        <v>-0.1402243589743577</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-0.3809410697908078</v>
+        <v>-0.3503850402903907</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>-0.2752283713565475</v>
+        <v>-0.277392639187525</v>
       </c>
       <c r="V26" s="4" t="n">
-        <v>-0.1339285545757676</v>
+        <v>-0.1402025327322676</v>
       </c>
       <c r="W26" s="4" t="n">
-        <v>-0.2882508467734439</v>
+        <v>-0.2584972105647267</v>
       </c>
       <c r="X26" s="4" t="n">
-        <v>-0.4742715612761401</v>
+        <v>-0.4109616047738172</v>
       </c>
       <c r="Y26" s="4" t="n">
-        <v>-0.3424158717181029</v>
+        <v>-0.2767813525019207</v>
       </c>
       <c r="Z26" s="4" t="n">
-        <v>-0.5933429373880159</v>
+        <v>-0.5484448779564914</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.005257</t>
+          <t>X &lt; 0.005298</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3149</v>
+        <v>3176</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.2023613090155649</v>
+        <v>-0.1967855773914025</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>0.2370614779310642</v>
+        <v>0.2621389416594155</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.04748134465116038</v>
+        <v>-0.03696984342820286</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2358911788856304</v>
+        <v>0.2016158318863575</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.03674804642450624</v>
+        <v>-0.02515168651717659</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.01011252988335087</v>
+        <v>-0.007307953266320055</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.203814883527464</v>
+        <v>0.1549242407808293</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.2281480610354976</v>
+        <v>0.1811552422646017</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.003291180179523678</v>
+        <v>-0.04921195711193604</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.2288851136919376</v>
+        <v>0.175958597210105</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>0.1733926821440122</v>
+        <v>0.1212482975224134</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.0712117416483693</v>
+        <v>0.01955539003031248</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.264331064913307</v>
+        <v>0.2409929278744869</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.1570739721217222</v>
+        <v>0.136835039573235</v>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>0.08795918723239282</v>
+        <v>0.06995285856697819</v>
       </c>
       <c r="R27" s="4" t="n">
-        <v>0.1310634865767923</v>
+        <v>0.115907194634211</v>
       </c>
       <c r="S27" s="4" t="n">
-        <v>0.04773296147135397</v>
+        <v>0.03060836999789984</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-0.1333121345285946</v>
+        <v>-0.1151191203559847</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>-0.05710513588275035</v>
+        <v>-0.07074106040576567</v>
       </c>
       <c r="V27" s="4" t="n">
-        <v>-0.01003234041545653</v>
+        <v>-0.02634578736598314</v>
       </c>
       <c r="W27" s="4" t="n">
-        <v>-0.07669018350838996</v>
+        <v>-0.0590309304579506</v>
       </c>
       <c r="X27" s="4" t="n">
-        <v>-0.2605108914728547</v>
+        <v>-0.2099244680402919</v>
       </c>
       <c r="Y27" s="4" t="n">
-        <v>-0.09407948094079899</v>
+        <v>-0.07354490837677474</v>
       </c>
       <c r="Z27" s="4" t="n">
-        <v>-0.246267543768532</v>
+        <v>-0.2170617847833824</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.006059</t>
+          <t>X &lt; 0.006099</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3200</v>
+        <v>3225</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.3199284293847882</v>
+        <v>-0.3242713231213727</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.07591287803504088</v>
+        <v>0.06235984345601508</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.1341398552227062</v>
+        <v>-0.1896067103901729</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.07097990697654666</v>
+        <v>0.005553859283509155</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.1851966510625829</v>
+        <v>-0.1911756703552001</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.04290650139611074</v>
+        <v>-0.1095906108302032</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.104371342936588</v>
+        <v>0.06899126579477155</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>0.1549784802343694</v>
+        <v>0.12105178771845</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.06567479837501367</v>
+        <v>-0.1347873456224562</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.1751718721229025</v>
+        <v>0.1057860944883302</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.09376208145842213</v>
+        <v>0.02511044042855559</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.04239102416061513</v>
+        <v>-0.1101627208209806</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>0.1297800269354781</v>
+        <v>0.09099355853159352</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>0.1764838372276074</v>
+        <v>0.1392136133803845</v>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>0.06683880162687217</v>
+        <v>0.03207595471583602</v>
       </c>
       <c r="R28" s="4" t="n">
-        <v>0.1187034044845134</v>
+        <v>0.08583173185702009</v>
       </c>
       <c r="S28" s="4" t="n">
-        <v>0.03456430879654704</v>
+        <v>0.0002417982048896761</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-0.05166853904476909</v>
+        <v>-0.0833807511884288</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>0.02678738191433894</v>
+        <v>0.02552684191810073</v>
       </c>
       <c r="V28" s="4" t="n">
-        <v>0.1073326457729422</v>
+        <v>0.1035143192116763</v>
       </c>
       <c r="W28" s="4" t="n">
-        <v>0.09553889741352606</v>
+        <v>0.09369063567481106</v>
       </c>
       <c r="X28" s="4" t="n">
-        <v>-0.1489692118141264</v>
+        <v>-0.1179827155636062</v>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>-0.04326202806148416</v>
+        <v>-0.01094369120460925</v>
       </c>
       <c r="Z28" s="4" t="n">
-        <v>-0.1942172897196244</v>
+        <v>-0.1547240970868984</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.006861</t>
+          <t>X &lt; 0.0069</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3243</v>
+        <v>3267</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.2870951991899986</v>
+        <v>-0.3045604465660574</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.0234180294288393</v>
+        <v>-0.01724402610157227</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.2190367701906411</v>
+        <v>-0.2516243800352314</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.03526690693025358</v>
+        <v>-0.005684642359675252</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.1299740826709268</v>
+        <v>-0.1425426469271542</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-0.1711267881778014</v>
+        <v>-0.2122324741331809</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.05603600215048488</v>
+        <v>0.01478177373902412</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.07159478635773553</v>
+        <v>0.0317882401977343</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.08421702583817847</v>
+        <v>-0.1277299561545888</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.08181074935001931</v>
+        <v>0.03859616996400206</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>0.03579015207686354</v>
+        <v>-0.007082516069125688</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.01007088615927643</v>
+        <v>-0.05265682505258695</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.1142467976039114</v>
+        <v>0.1011340204367102</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.1574050393969344</v>
+        <v>0.1455564768661048</v>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>0.1020188459792379</v>
+        <v>0.09211519697659298</v>
       </c>
       <c r="R29" s="4" t="n">
-        <v>0.09953379953380193</v>
+        <v>0.09131296110395226</v>
       </c>
       <c r="S29" s="4" t="n">
-        <v>0.04550870034309895</v>
+        <v>0.03604300336083099</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-0.1025434804463572</v>
+        <v>-0.1093256292039797</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>0.008514488506925488</v>
+        <v>0.0009293652329205315</v>
       </c>
       <c r="V29" s="4" t="n">
-        <v>0.05965514687855489</v>
+        <v>0.01950172300645647</v>
       </c>
       <c r="W29" s="4" t="n">
-        <v>-0.02078381221502212</v>
+        <v>-0.0586461422886515</v>
       </c>
       <c r="X29" s="4" t="n">
-        <v>-0.2322761588397242</v>
+        <v>-0.2380218128748979</v>
       </c>
       <c r="Y29" s="4" t="n">
-        <v>-0.124357601231246</v>
+        <v>-0.1292640093661817</v>
       </c>
       <c r="Z29" s="4" t="n">
-        <v>-0.2743417886403776</v>
+        <v>-0.2733166469690929</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.007663</t>
+          <t>X &lt; 0.007701</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3271</v>
+        <v>3296</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-0.2548768735291418</v>
+        <v>-0.28765385288456</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.003719952130730064</v>
+        <v>0.02515350281200313</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.1720750483241602</v>
+        <v>-0.2181371952597218</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-0.1083598981886453</v>
+        <v>-0.1605167423423239</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.1838833482117224</v>
+        <v>-0.2081101530746778</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.1318689552698871</v>
+        <v>-0.1852836772149757</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.0348965706140163</v>
+        <v>-0.08798375384341739</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.02186867471584009</v>
+        <v>-0.07382798080473663</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.1455858420490443</v>
+        <v>-0.2006481862645941</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.04848370189449724</v>
+        <v>-0.1032195727627752</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.03089420100958051</v>
+        <v>-0.08569460656623562</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.01782396519910634</v>
+        <v>-0.07284068265270349</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.09584538388063635</v>
+        <v>0.03956722581818184</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.1672301376479126</v>
+        <v>0.1419174868428428</v>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>0.1066998839013635</v>
+        <v>0.1132230837850869</v>
       </c>
       <c r="R30" s="4" t="n">
-        <v>0.1093146227374504</v>
+        <v>0.1173624734870344</v>
       </c>
       <c r="S30" s="4" t="n">
-        <v>0.08512559427155253</v>
+        <v>0.09195815667272456</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-0.06254516458597692</v>
+        <v>-0.05328385776183353</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>-0.01164739903695278</v>
+        <v>-0.002702181046132068</v>
       </c>
       <c r="V30" s="4" t="n">
-        <v>0.01010400532036471</v>
+        <v>0.01759214610751769</v>
       </c>
       <c r="W30" s="4" t="n">
-        <v>-0.01319964584664035</v>
+        <v>-0.004232470459641036</v>
       </c>
       <c r="X30" s="4" t="n">
-        <v>-0.2540822512698782</v>
+        <v>-0.212996681075559</v>
       </c>
       <c r="Y30" s="4" t="n">
-        <v>-0.1141827137579554</v>
+        <v>-0.07271432527593191</v>
       </c>
       <c r="Z30" s="4" t="n">
-        <v>-0.2941007351491578</v>
+        <v>-0.2472487452392258</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.008465</t>
+          <t>X &lt; 0.008501</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3299</v>
+        <v>3323</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-0.1328675891922799</v>
+        <v>-0.1495026623407938</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06052066653146682</v>
+        <v>0.0691219385778723</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-0.1861648047416651</v>
+        <v>-0.2122375370790692</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.09886943354062083</v>
+        <v>-0.129944646082194</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1765870307346518</v>
+        <v>-0.1793711833026208</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.123430916886349</v>
+        <v>-0.1554520034059408</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.09412711499998494</v>
+        <v>-0.1252573452597474</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.02322774417200435</v>
+        <v>-0.05377752531737912</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.1153649650187987</v>
+        <v>-0.1485634854777587</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.08599539671699574</v>
+        <v>-0.1183027011829765</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.06624834456028594</v>
+        <v>-0.09872013733168927</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.05565735468417898</v>
+        <v>-0.08821408211856152</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.0173141663400429</v>
+        <v>0.0142470894488298</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1164294180324958</v>
+        <v>0.1137488820332919</v>
       </c>
       <c r="Q31" s="4" t="n">
-        <v>0.1113016541719531</v>
+        <v>0.1097703036428683</v>
       </c>
       <c r="R31" s="4" t="n">
-        <v>0.1189297695649856</v>
+        <v>0.1184262075208053</v>
       </c>
       <c r="S31" s="4" t="n">
-        <v>0.09381403250861098</v>
+        <v>0.09238572644437681</v>
       </c>
       <c r="T31" s="4" t="n">
-        <v>-0.02322478628254743</v>
+        <v>-0.02270782311032349</v>
       </c>
       <c r="U31" s="4" t="n">
-        <v>-0.03146745621373981</v>
+        <v>-0.03090121375372945</v>
       </c>
       <c r="V31" s="4" t="n">
-        <v>-0.03860677768927445</v>
+        <v>-0.03910427440803943</v>
       </c>
       <c r="W31" s="4" t="n">
-        <v>-0.09659813039183263</v>
+        <v>-0.09542430194632345</v>
       </c>
       <c r="X31" s="4" t="n">
-        <v>-0.2452245626712184</v>
+        <v>-0.2129054888743127</v>
       </c>
       <c r="Y31" s="4" t="n">
-        <v>-0.1950895819508887</v>
+        <v>-0.1620363103646625</v>
       </c>
       <c r="Z31" s="4" t="n">
-        <v>-0.2832120608623896</v>
+        <v>-0.2462170274967548</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.009266</t>
+          <t>X &lt; 0.009302</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3319</v>
+        <v>3343</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-0.1239360089722226</v>
+        <v>-0.1399521367287235</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.1261724954038499</v>
+        <v>0.1056400390392795</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-0.2174764438915417</v>
+        <v>-0.2707031340378947</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.1050271779786982</v>
+        <v>-0.1626970864060056</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.1842933563089275</v>
+        <v>-0.213478989439551</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.0703852954823887</v>
+        <v>-0.1292543986155223</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.01409931477155624</v>
+        <v>-0.04442423460531586</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>0.05294289979214284</v>
+        <v>-0.004941785763705298</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.06837264127690901</v>
+        <v>-0.1281748316743361</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.0137926025558599</v>
+        <v>-0.07303498210436743</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.0225179446968653</v>
+        <v>-0.08173906006108211</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.01637842732138495</v>
+        <v>-0.04312471001087914</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.1122244944628861</v>
+        <v>0.081912669010066</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.08925171363291184</v>
+        <v>0.0600281097148283</v>
       </c>
       <c r="Q32" s="4" t="n">
-        <v>0.05013312068345499</v>
+        <v>0.02214405927358598</v>
       </c>
       <c r="R32" s="4" t="n">
-        <v>0.09133730570891885</v>
+        <v>0.06392394406331192</v>
       </c>
       <c r="S32" s="4" t="n">
-        <v>0.06555882565638171</v>
+        <v>0.03740233403005533</v>
       </c>
       <c r="T32" s="4" t="n">
-        <v>-0.02133086344387891</v>
+        <v>-0.04794533574702342</v>
       </c>
       <c r="U32" s="4" t="n">
-        <v>-0.02822397726915682</v>
+        <v>-0.054815787984964</v>
       </c>
       <c r="V32" s="4" t="n">
-        <v>-0.00409209281217926</v>
+        <v>-0.0318078876290997</v>
       </c>
       <c r="W32" s="4" t="n">
-        <v>-0.06500069304792788</v>
+        <v>-0.09118305248860992</v>
       </c>
       <c r="X32" s="4" t="n">
-        <v>-0.1529564818901719</v>
+        <v>-0.1486192126456274</v>
       </c>
       <c r="Y32" s="4" t="n">
-        <v>-0.1315627473397143</v>
+        <v>-0.1264822134387273</v>
       </c>
       <c r="Z32" s="4" t="n">
-        <v>-0.2195920260859978</v>
+        <v>-0.2111186922956776</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.01007</t>
+          <t>X &lt; 0.0101</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3332</v>
+        <v>3355</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-0.1226598743144933</v>
+        <v>-0.1382454374060345</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.005885184549867972</v>
+        <v>0.01661893840643813</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.2823780443449877</v>
+        <v>-0.3038911728150495</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.2328339244512776</v>
+        <v>-0.2578520867364915</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.2534322289221933</v>
+        <v>-0.250251430813961</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1691208785298315</v>
+        <v>-0.1954047099111094</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.001614517743547594</v>
+        <v>-0.02501849862996863</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>0.06910040925230021</v>
+        <v>0.04280633174136028</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.02169134433670195</v>
+        <v>-0.04977008107126579</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.0002086936559777541</v>
+        <v>-0.02757385950120295</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.007830630083816459</v>
+        <v>-0.0351800546414367</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.02983489904887193</v>
+        <v>0.002231149298474122</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.1209431896283633</v>
+        <v>0.09278435494009329</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>0.06727101923003431</v>
+        <v>0.04031088870818422</v>
       </c>
       <c r="Q33" s="4" t="n">
-        <v>0.02573646764147242</v>
+        <v>-6.877158137541528e-05</v>
       </c>
       <c r="R33" s="4" t="n">
-        <v>0.06908709738898722</v>
+        <v>0.04371277865928391</v>
       </c>
       <c r="S33" s="4" t="n">
-        <v>0.04288080045557763</v>
+        <v>0.01688603014078183</v>
       </c>
       <c r="T33" s="4" t="n">
-        <v>-0.01411858034878577</v>
+        <v>-0.03889856018490434</v>
       </c>
       <c r="U33" s="4" t="n">
-        <v>-0.02014136722117854</v>
+        <v>-0.04490997325392243</v>
       </c>
       <c r="V33" s="4" t="n">
-        <v>-0.02535779951331563</v>
+        <v>-0.05092844178884093</v>
       </c>
       <c r="W33" s="4" t="n">
-        <v>-0.08814384753931392</v>
+        <v>-0.09461847910628762</v>
       </c>
       <c r="X33" s="4" t="n">
-        <v>-0.1760593590563886</v>
+        <v>-0.1521190276363242</v>
       </c>
       <c r="Y33" s="4" t="n">
-        <v>-0.1836884418368783</v>
+        <v>-0.1589884437995437</v>
       </c>
       <c r="Z33" s="4" t="n">
-        <v>-0.2116617675107406</v>
+        <v>-0.1842993001275985</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.01087</t>
+          <t>X &lt; 0.0109</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3342</v>
+        <v>3366</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-0.1490194759876857</v>
+        <v>-0.1640489765614674</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.007729239228922324</v>
+        <v>0.01902251646887976</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-0.2248234544196706</v>
+        <v>-0.2454715393405351</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.2075012039318977</v>
+        <v>-0.2310226583713302</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-0.1696174438768665</v>
+        <v>-0.1652500430183323</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-0.114706980991123</v>
+        <v>-0.139597188213628</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.02318676271177367</v>
+        <v>-0.001893313006085862</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.05976702633073927</v>
+        <v>0.03515769334810415</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.03059406449162339</v>
+        <v>-0.05670357308502361</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.01171787516788214</v>
+        <v>-0.03717233920037444</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.01841969589290215</v>
+        <v>-0.04387037961214446</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.01820494077580292</v>
+        <v>-0.007484224537677164</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.07550213565291841</v>
+        <v>0.04952749045309446</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>0.05109997873296379</v>
+        <v>0.02602421870825111</v>
       </c>
       <c r="Q34" s="4" t="n">
-        <v>0.03737835843463699</v>
+        <v>0.0131782447571922</v>
       </c>
       <c r="R34" s="4" t="n">
-        <v>0.08254183627317957</v>
+        <v>0.05865096102356659</v>
       </c>
       <c r="S34" s="4" t="n">
-        <v>0.05598577388692405</v>
+        <v>0.03157735448166221</v>
       </c>
       <c r="T34" s="4" t="n">
-        <v>-0.001166877401232114</v>
+        <v>-0.02445438985911608</v>
       </c>
       <c r="U34" s="4" t="n">
-        <v>-0.006456468113277936</v>
+        <v>-0.02974208468051387</v>
       </c>
       <c r="V34" s="4" t="n">
-        <v>-0.01103740442096779</v>
+        <v>-0.03503597697267224</v>
       </c>
       <c r="W34" s="4" t="n">
-        <v>-0.05753135109695506</v>
+        <v>-0.08043138877509648</v>
       </c>
       <c r="X34" s="4" t="n">
-        <v>-0.1454016150071098</v>
+        <v>-0.1379854095786897</v>
       </c>
       <c r="Y34" s="4" t="n">
-        <v>-0.1521776628798364</v>
+        <v>-0.1440322309887421</v>
       </c>
       <c r="Z34" s="4" t="n">
-        <v>-0.1802847642857515</v>
+        <v>-0.1697857947751373</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.01167</t>
+          <t>X &lt; 0.0117</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3354</v>
+        <v>3378</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-0.04297918331648276</v>
+        <v>-0.05835739556134456</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.08243296025613489</v>
+        <v>0.09381937736200285</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-0.1543837015535061</v>
+        <v>-0.1741485247822467</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.1692762926443692</v>
+        <v>-0.1912508180163357</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-0.1030634089249318</v>
+        <v>-0.0972345162415138</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.07731925009805707</v>
+        <v>-0.1005441512657015</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.02768196278305624</v>
+        <v>0.004419111979444779</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.06314264025947125</v>
+        <v>0.04026288646205956</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.002934578492258311</v>
+        <v>-0.02134710166087217</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.01069159968439237</v>
+        <v>-0.03417189262227538</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.01639248075093036</v>
+        <v>-0.03988196573627079</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.04881728328965096</v>
+        <v>0.02489603922000327</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>0.1019139138879339</v>
+        <v>0.07776775252133206</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>0.0768180266302565</v>
+        <v>0.05347683933192116</v>
       </c>
       <c r="Q35" s="4" t="n">
-        <v>0.06080460077752292</v>
+        <v>0.03826763884570283</v>
       </c>
       <c r="R35" s="4" t="n">
-        <v>0.1079353919924984</v>
+        <v>0.08557587343006645</v>
       </c>
       <c r="S35" s="4" t="n">
-        <v>0.08100356663707231</v>
+        <v>0.05823793697685886</v>
       </c>
       <c r="T35" s="4" t="n">
-        <v>0.05344995140913511</v>
+        <v>0.03149237237977331</v>
       </c>
       <c r="U35" s="4" t="n">
-        <v>0.01919602264663212</v>
+        <v>-0.002558861955137104</v>
       </c>
       <c r="V35" s="4" t="n">
-        <v>0.04508643042650817</v>
+        <v>0.02250376475653582</v>
       </c>
       <c r="W35" s="4" t="n">
-        <v>-0.003163996088808574</v>
+        <v>-0.02472750901962684</v>
       </c>
       <c r="X35" s="4" t="n">
-        <v>-0.1207724426613623</v>
+        <v>-0.1119133635907019</v>
       </c>
       <c r="Y35" s="4" t="n">
-        <v>-0.09672892621319562</v>
+        <v>-0.08747120964525124</v>
       </c>
       <c r="Z35" s="4" t="n">
-        <v>-0.09517510128790008</v>
+        <v>-0.08408920923527319</v>
       </c>
     </row>
   </sheetData>
